--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -2748,50 +2748,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129040720</v>
+        <v>129037863</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>91975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491296</v>
+        <v>490942</v>
       </c>
       <c r="R21" t="n">
-        <v>6710129</v>
+        <v>6709873</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2833,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2860,45 +2855,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129044129</v>
+        <v>129041584</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491049</v>
+        <v>491362</v>
       </c>
       <c r="R22" t="n">
-        <v>6709893</v>
+        <v>6710143</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,45 +2962,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129037863</v>
+        <v>129040720</v>
       </c>
       <c r="B23" t="n">
-        <v>91975</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490942</v>
+        <v>491296</v>
       </c>
       <c r="R23" t="n">
-        <v>6709873</v>
+        <v>6710129</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,45 +3074,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129041584</v>
+        <v>129044129</v>
       </c>
       <c r="B24" t="n">
-        <v>91540</v>
+        <v>98651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491362</v>
+        <v>491049</v>
       </c>
       <c r="R24" t="n">
-        <v>6710143</v>
+        <v>6709893</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,50 +3181,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129040515</v>
+        <v>129045583</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>98651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491251</v>
+        <v>490946</v>
       </c>
       <c r="R25" t="n">
-        <v>6710165</v>
+        <v>6709935</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3266,12 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,7 +3288,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129045583</v>
+        <v>129043562</v>
       </c>
       <c r="B26" t="n">
         <v>98651</v>
@@ -3333,10 +3323,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490946</v>
+        <v>491129</v>
       </c>
       <c r="R26" t="n">
-        <v>6709935</v>
+        <v>6709987</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3368,7 +3358,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3378,7 +3368,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3405,7 +3395,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129043562</v>
+        <v>129041242</v>
       </c>
       <c r="B27" t="n">
         <v>98651</v>
@@ -3436,14 +3426,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491129</v>
+        <v>491341</v>
       </c>
       <c r="R27" t="n">
-        <v>6709987</v>
+        <v>6710206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3475,7 +3465,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3485,7 +3475,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3512,45 +3502,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129041242</v>
+        <v>129042527</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>92811</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491341</v>
+        <v>491296</v>
       </c>
       <c r="R28" t="n">
-        <v>6710206</v>
+        <v>6710104</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3582,7 +3581,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3592,7 +3591,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3619,54 +3618,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129042527</v>
+        <v>129045240</v>
       </c>
       <c r="B29" t="n">
-        <v>92811</v>
+        <v>91805</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491296</v>
+        <v>491133</v>
       </c>
       <c r="R29" t="n">
-        <v>6710104</v>
+        <v>6710118</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3688,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3698,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,10 +3725,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129045240</v>
+        <v>129040515</v>
       </c>
       <c r="B30" t="n">
-        <v>91805</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,34 +3736,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491133</v>
+        <v>491251</v>
       </c>
       <c r="R30" t="n">
-        <v>6710118</v>
+        <v>6710165</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3800,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3810,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5858,45 +5858,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129044332</v>
+        <v>129038812</v>
       </c>
       <c r="B49" t="n">
-        <v>98651</v>
+        <v>92811</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491049</v>
+        <v>490918</v>
       </c>
       <c r="R49" t="n">
-        <v>6709914</v>
+        <v>6709933</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5928,7 +5937,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5938,7 +5947,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5965,7 +5974,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129045046</v>
+        <v>129044332</v>
       </c>
       <c r="B50" t="n">
         <v>98651</v>
@@ -6000,10 +6009,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491153</v>
+        <v>491049</v>
       </c>
       <c r="R50" t="n">
-        <v>6710121</v>
+        <v>6709914</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6035,7 +6044,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6045,7 +6054,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6072,7 +6081,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129039883</v>
+        <v>129045046</v>
       </c>
       <c r="B51" t="n">
         <v>98651</v>
@@ -6107,10 +6116,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>491128</v>
+        <v>491153</v>
       </c>
       <c r="R51" t="n">
-        <v>6710150</v>
+        <v>6710121</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6142,7 +6151,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6152,7 +6161,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6179,54 +6188,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129038812</v>
+        <v>129039883</v>
       </c>
       <c r="B52" t="n">
-        <v>92811</v>
+        <v>98651</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490918</v>
+        <v>491128</v>
       </c>
       <c r="R52" t="n">
-        <v>6709933</v>
+        <v>6710150</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6621,10 +6621,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129037776</v>
+        <v>129040007</v>
       </c>
       <c r="B56" t="n">
-        <v>91805</v>
+        <v>91520</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490952</v>
+        <v>491180</v>
       </c>
       <c r="R56" t="n">
-        <v>6709889</v>
+        <v>6710139</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6728,32 +6728,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129038411</v>
+        <v>129039941</v>
       </c>
       <c r="B57" t="n">
-        <v>98651</v>
+        <v>91520</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490873</v>
+        <v>491158</v>
       </c>
       <c r="R57" t="n">
-        <v>6709909</v>
+        <v>6710160</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,32 +6835,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129044061</v>
+        <v>129037776</v>
       </c>
       <c r="B58" t="n">
-        <v>98651</v>
+        <v>91805</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491110</v>
+        <v>490952</v>
       </c>
       <c r="R58" t="n">
-        <v>6709915</v>
+        <v>6709889</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,7 +6942,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129045420</v>
+        <v>129038411</v>
       </c>
       <c r="B59" t="n">
         <v>98651</v>
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>491009</v>
+        <v>490873</v>
       </c>
       <c r="R59" t="n">
-        <v>6709991</v>
+        <v>6709909</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7049,7 +7049,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129038173</v>
+        <v>129044061</v>
       </c>
       <c r="B60" t="n">
         <v>98651</v>
@@ -7077,31 +7077,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490877</v>
+        <v>491110</v>
       </c>
       <c r="R60" t="n">
-        <v>6709889</v>
+        <v>6709915</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7133,7 +7119,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7143,7 +7129,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,7 +7156,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129043992</v>
+        <v>129045420</v>
       </c>
       <c r="B61" t="n">
         <v>98651</v>
@@ -7205,10 +7191,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>491095</v>
+        <v>491009</v>
       </c>
       <c r="R61" t="n">
-        <v>6709906</v>
+        <v>6709991</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7240,7 +7226,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7250,7 +7236,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7277,45 +7263,59 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129040007</v>
+        <v>129038173</v>
       </c>
       <c r="B62" t="n">
-        <v>91520</v>
+        <v>98651</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>491180</v>
+        <v>490877</v>
       </c>
       <c r="R62" t="n">
-        <v>6710139</v>
+        <v>6709889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,32 +7384,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129039941</v>
+        <v>129043992</v>
       </c>
       <c r="B63" t="n">
-        <v>91520</v>
+        <v>98651</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491158</v>
+        <v>491095</v>
       </c>
       <c r="R63" t="n">
-        <v>6710160</v>
+        <v>6709906</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8586,50 +8586,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129038223</v>
+        <v>129042724</v>
       </c>
       <c r="B74" t="n">
-        <v>57723</v>
+        <v>92847</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490878</v>
+        <v>491257</v>
       </c>
       <c r="R74" t="n">
-        <v>6709889</v>
+        <v>6710085</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8661,7 +8656,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8671,7 +8666,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8698,7 +8693,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129038053</v>
+        <v>129038223</v>
       </c>
       <c r="B75" t="n">
         <v>57723</v>
@@ -8729,7 +8724,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8738,10 +8733,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490886</v>
+        <v>490878</v>
       </c>
       <c r="R75" t="n">
-        <v>6709872</v>
+        <v>6709889</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8773,7 +8768,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8783,12 +8778,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:46</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8815,45 +8805,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129042724</v>
+        <v>129038053</v>
       </c>
       <c r="B76" t="n">
-        <v>92847</v>
+        <v>57723</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>491257</v>
+        <v>490886</v>
       </c>
       <c r="R76" t="n">
-        <v>6710085</v>
+        <v>6709872</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8885,7 +8880,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8895,7 +8890,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9355,32 +9355,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129039994</v>
+        <v>129044818</v>
       </c>
       <c r="B81" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>491173</v>
+        <v>491116</v>
       </c>
       <c r="R81" t="n">
-        <v>6710152</v>
+        <v>6710020</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9435,7 +9435,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9462,10 +9467,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129044818</v>
+        <v>129042971</v>
       </c>
       <c r="B82" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9473,34 +9478,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>491116</v>
+        <v>491193</v>
       </c>
       <c r="R82" t="n">
-        <v>6710020</v>
+        <v>6710074</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9532,7 +9542,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9542,12 +9552,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9574,7 +9584,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129042971</v>
+        <v>129039011</v>
       </c>
       <c r="B83" t="n">
         <v>57723</v>
@@ -9614,10 +9624,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>491193</v>
+        <v>490936</v>
       </c>
       <c r="R83" t="n">
-        <v>6710074</v>
+        <v>6709979</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9649,7 +9659,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9659,7 +9669,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9691,50 +9701,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129039011</v>
+        <v>129038137</v>
       </c>
       <c r="B84" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490936</v>
+        <v>490876</v>
       </c>
       <c r="R84" t="n">
-        <v>6709979</v>
+        <v>6709883</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9766,7 +9776,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9776,12 +9786,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9808,50 +9813,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129038137</v>
+        <v>129039994</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>98651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490876</v>
+        <v>491173</v>
       </c>
       <c r="R85" t="n">
-        <v>6709883</v>
+        <v>6710152</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129039226</v>
+        <v>129039783</v>
       </c>
       <c r="B2" t="n">
-        <v>92811</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491060</v>
+        <v>491113</v>
       </c>
       <c r="R2" t="n">
-        <v>6710037</v>
+        <v>6710132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129039783</v>
+        <v>129041992</v>
       </c>
       <c r="B3" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491113</v>
+        <v>491353</v>
       </c>
       <c r="R3" t="n">
-        <v>6710132</v>
+        <v>6710077</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129041992</v>
+        <v>129038956</v>
       </c>
       <c r="B4" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491353</v>
+        <v>490939</v>
       </c>
       <c r="R4" t="n">
-        <v>6710077</v>
+        <v>6709966</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,50 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129038956</v>
+        <v>129045855</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490939</v>
+        <v>491030</v>
       </c>
       <c r="R5" t="n">
-        <v>6709966</v>
+        <v>6709895</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,45 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129042946</v>
+        <v>129041481</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491232</v>
+        <v>491361</v>
       </c>
       <c r="R6" t="n">
-        <v>6710086</v>
+        <v>6710143</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På 2 stående.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129045855</v>
+        <v>129039226</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491030</v>
+        <v>491060</v>
       </c>
       <c r="R7" t="n">
-        <v>6709895</v>
+        <v>6710037</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,45 +1327,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129041481</v>
+        <v>129042946</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491361</v>
+        <v>491232</v>
       </c>
       <c r="R8" t="n">
-        <v>6710143</v>
+        <v>6710086</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1407,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129039748</v>
+        <v>129043673</v>
       </c>
       <c r="B9" t="n">
-        <v>92811</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,34 +1450,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491113</v>
+        <v>491125</v>
       </c>
       <c r="R9" t="n">
-        <v>6710132</v>
+        <v>6709976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1551,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129040305</v>
+        <v>129040595</v>
       </c>
       <c r="B10" t="n">
-        <v>75155</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,7 +1586,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491221</v>
+        <v>491251</v>
       </c>
       <c r="R10" t="n">
         <v>6710146</v>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,50 +1658,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129041053</v>
+        <v>129040305</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>75155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491309</v>
+        <v>491221</v>
       </c>
       <c r="R11" t="n">
-        <v>6710192</v>
+        <v>6710146</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,12 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129043673</v>
+        <v>129039748</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>92816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,39 +1776,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491125</v>
+        <v>491113</v>
       </c>
       <c r="R12" t="n">
-        <v>6709976</v>
+        <v>6710132</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,45 +1872,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129043484</v>
+        <v>129041053</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491159</v>
+        <v>491309</v>
       </c>
       <c r="R13" t="n">
-        <v>6709989</v>
+        <v>6710192</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1957,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129040595</v>
+        <v>129043484</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491251</v>
+        <v>491159</v>
       </c>
       <c r="R14" t="n">
-        <v>6710146</v>
+        <v>6709989</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,7 +2099,7 @@
         <v>129045778</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129041291</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129039360</v>
+        <v>129039950</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>91808</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491080</v>
+        <v>491157</v>
       </c>
       <c r="R17" t="n">
-        <v>6710071</v>
+        <v>6710161</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,12 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129039950</v>
+        <v>129039360</v>
       </c>
       <c r="B18" t="n">
-        <v>91805</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,21 +2428,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491157</v>
+        <v>491080</v>
       </c>
       <c r="R18" t="n">
-        <v>6710161</v>
+        <v>6710071</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,7 +2497,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,7 +2532,7 @@
         <v>129043063</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>129040685</v>
       </c>
       <c r="B20" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,45 +2748,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129037863</v>
+        <v>129041584</v>
       </c>
       <c r="B21" t="n">
-        <v>91975</v>
+        <v>91543</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490942</v>
+        <v>491362</v>
       </c>
       <c r="R21" t="n">
-        <v>6709873</v>
+        <v>6710143</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,45 +2855,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129041584</v>
+        <v>129040720</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491362</v>
+        <v>491296</v>
       </c>
       <c r="R22" t="n">
-        <v>6710143</v>
+        <v>6710129</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,50 +2967,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129040720</v>
+        <v>129037863</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>91978</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491296</v>
+        <v>490942</v>
       </c>
       <c r="R23" t="n">
-        <v>6710129</v>
+        <v>6709873</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,7 +3077,7 @@
         <v>129044129</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,32 +3181,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129045583</v>
+        <v>129045240</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>91808</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490946</v>
+        <v>491133</v>
       </c>
       <c r="R25" t="n">
-        <v>6709935</v>
+        <v>6710118</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,45 +3288,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129043562</v>
+        <v>129042527</v>
       </c>
       <c r="B26" t="n">
-        <v>98651</v>
+        <v>92816</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491129</v>
+        <v>491296</v>
       </c>
       <c r="R26" t="n">
-        <v>6709987</v>
+        <v>6710104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3358,7 +3367,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3368,7 +3377,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,45 +3404,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129041242</v>
+        <v>129040515</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491341</v>
+        <v>491251</v>
       </c>
       <c r="R27" t="n">
-        <v>6710206</v>
+        <v>6710165</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3465,7 +3479,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3475,7 +3489,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,54 +3521,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129042527</v>
+        <v>129045583</v>
       </c>
       <c r="B28" t="n">
-        <v>92811</v>
+        <v>98656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491296</v>
+        <v>490946</v>
       </c>
       <c r="R28" t="n">
-        <v>6710104</v>
+        <v>6709935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3581,7 +3591,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3591,7 +3601,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3618,32 +3628,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129045240</v>
+        <v>129043562</v>
       </c>
       <c r="B29" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3653,10 +3663,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491133</v>
+        <v>491129</v>
       </c>
       <c r="R29" t="n">
-        <v>6710118</v>
+        <v>6709987</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3688,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3698,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3725,50 +3735,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129040515</v>
+        <v>129041242</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491251</v>
+        <v>491341</v>
       </c>
       <c r="R30" t="n">
-        <v>6710165</v>
+        <v>6710206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3800,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3810,12 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,45 +3842,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129044587</v>
+        <v>129040867</v>
       </c>
       <c r="B31" t="n">
-        <v>91805</v>
+        <v>105719</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491075</v>
+        <v>491332</v>
       </c>
       <c r="R31" t="n">
-        <v>6709943</v>
+        <v>6710175</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,50 +3949,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129038111</v>
+        <v>129039814</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490874</v>
+        <v>491102</v>
       </c>
       <c r="R32" t="n">
-        <v>6709885</v>
+        <v>6710142</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4034,12 +4034,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4066,45 +4061,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129040867</v>
+        <v>129039825</v>
       </c>
       <c r="B33" t="n">
-        <v>105714</v>
+        <v>98656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491332</v>
+        <v>491126</v>
       </c>
       <c r="R33" t="n">
-        <v>6710175</v>
+        <v>6710148</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4136,7 +4131,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4146,7 +4141,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4173,10 +4168,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129039814</v>
+        <v>129041725</v>
       </c>
       <c r="B34" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4201,22 +4196,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491102</v>
+        <v>491375</v>
       </c>
       <c r="R34" t="n">
-        <v>6710142</v>
+        <v>6710101</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4248,7 +4252,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4258,7 +4262,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4285,32 +4289,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129039825</v>
+        <v>129044587</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>91808</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4320,10 +4324,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491126</v>
+        <v>491075</v>
       </c>
       <c r="R35" t="n">
-        <v>6710148</v>
+        <v>6709943</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4355,7 +4359,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4365,7 +4369,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,59 +4396,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129041725</v>
+        <v>129040534</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491375</v>
+        <v>491261</v>
       </c>
       <c r="R36" t="n">
-        <v>6710101</v>
+        <v>6710156</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4476,7 +4466,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4486,7 +4476,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4513,10 +4503,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129040534</v>
+        <v>129044722</v>
       </c>
       <c r="B37" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,21 +4514,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4548,10 +4538,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491261</v>
+        <v>491088</v>
       </c>
       <c r="R37" t="n">
-        <v>6710156</v>
+        <v>6709977</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4583,7 +4573,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4593,7 +4583,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4620,10 +4615,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129044722</v>
+        <v>129038111</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4631,34 +4626,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491088</v>
+        <v>490874</v>
       </c>
       <c r="R38" t="n">
-        <v>6709977</v>
+        <v>6709885</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4690,7 +4690,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4735,7 +4735,7 @@
         <v>129045013</v>
       </c>
       <c r="B39" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4839,32 +4839,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129044467</v>
+        <v>129040042</v>
       </c>
       <c r="B40" t="n">
-        <v>98651</v>
+        <v>91808</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491036</v>
+        <v>491181</v>
       </c>
       <c r="R40" t="n">
-        <v>6709945</v>
+        <v>6710144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4946,10 +4946,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129040042</v>
+        <v>129038104</v>
       </c>
       <c r="B41" t="n">
-        <v>91805</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4957,34 +4957,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491181</v>
+        <v>490880</v>
       </c>
       <c r="R41" t="n">
-        <v>6710144</v>
+        <v>6709882</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5016,7 +5024,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5026,7 +5034,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5053,53 +5066,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129038104</v>
+        <v>129044467</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490880</v>
+        <v>491036</v>
       </c>
       <c r="R42" t="n">
-        <v>6709882</v>
+        <v>6709945</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5131,7 +5136,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5141,12 +5146,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5173,10 +5173,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129045330</v>
+        <v>129044319</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>91523</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5184,39 +5184,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491085</v>
+        <v>491049</v>
       </c>
       <c r="R43" t="n">
-        <v>6710033</v>
+        <v>6709915</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5248,7 +5243,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5258,12 +5253,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5290,45 +5280,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129041044</v>
+        <v>129045330</v>
       </c>
       <c r="B44" t="n">
-        <v>92811</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491306</v>
+        <v>491085</v>
       </c>
       <c r="R44" t="n">
-        <v>6710197</v>
+        <v>6710033</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5360,7 +5355,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5370,7 +5365,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,45 +5397,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129044319</v>
+        <v>129041044</v>
       </c>
       <c r="B45" t="n">
-        <v>91520</v>
+        <v>92816</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491049</v>
+        <v>491306</v>
       </c>
       <c r="R45" t="n">
-        <v>6709915</v>
+        <v>6710197</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5507,7 +5507,7 @@
         <v>129037802</v>
       </c>
       <c r="B46" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>129039795</v>
       </c>
       <c r="B47" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>129042338</v>
       </c>
       <c r="B48" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>129038812</v>
       </c>
       <c r="B49" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>129044332</v>
       </c>
       <c r="B50" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>129045046</v>
       </c>
       <c r="B51" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>129039883</v>
       </c>
       <c r="B52" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6295,50 +6295,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129038692</v>
+        <v>129040369</v>
       </c>
       <c r="B53" t="n">
-        <v>57883</v>
+        <v>98656</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490892</v>
+        <v>491194</v>
       </c>
       <c r="R53" t="n">
-        <v>6709919</v>
+        <v>6710167</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6370,7 +6365,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6380,7 +6375,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6410,7 +6405,7 @@
         <v>129044552</v>
       </c>
       <c r="B54" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6514,45 +6509,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129040369</v>
+        <v>129038692</v>
       </c>
       <c r="B55" t="n">
-        <v>98651</v>
+        <v>57883</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>491194</v>
+        <v>490892</v>
       </c>
       <c r="R55" t="n">
-        <v>6710167</v>
+        <v>6709919</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6621,32 +6621,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129040007</v>
+        <v>129038411</v>
       </c>
       <c r="B56" t="n">
-        <v>91520</v>
+        <v>98656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>491180</v>
+        <v>490873</v>
       </c>
       <c r="R56" t="n">
-        <v>6710139</v>
+        <v>6709909</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6728,32 +6728,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129039941</v>
+        <v>129044061</v>
       </c>
       <c r="B57" t="n">
-        <v>91520</v>
+        <v>98656</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>491158</v>
+        <v>491110</v>
       </c>
       <c r="R57" t="n">
-        <v>6710160</v>
+        <v>6709915</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,32 +6835,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129037776</v>
+        <v>129045420</v>
       </c>
       <c r="B58" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490952</v>
+        <v>491009</v>
       </c>
       <c r="R58" t="n">
-        <v>6709889</v>
+        <v>6709991</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,10 +6942,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129038411</v>
+        <v>129038173</v>
       </c>
       <c r="B59" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,17 +6970,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490873</v>
+        <v>490877</v>
       </c>
       <c r="R59" t="n">
-        <v>6709909</v>
+        <v>6709889</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7012,7 +7026,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7022,7 +7036,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7049,10 +7063,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129044061</v>
+        <v>129043992</v>
       </c>
       <c r="B60" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7084,10 +7098,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>491110</v>
+        <v>491095</v>
       </c>
       <c r="R60" t="n">
-        <v>6709915</v>
+        <v>6709906</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7119,7 +7133,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7129,7 +7143,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7156,32 +7170,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045420</v>
+        <v>129037776</v>
       </c>
       <c r="B61" t="n">
-        <v>98651</v>
+        <v>91808</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7191,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>491009</v>
+        <v>490952</v>
       </c>
       <c r="R61" t="n">
-        <v>6709991</v>
+        <v>6709889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7226,7 +7240,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7236,7 +7250,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7263,59 +7277,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129038173</v>
+        <v>129040007</v>
       </c>
       <c r="B62" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490877</v>
+        <v>491180</v>
       </c>
       <c r="R62" t="n">
-        <v>6709889</v>
+        <v>6710139</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,32 +7384,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129043992</v>
+        <v>129039941</v>
       </c>
       <c r="B63" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491095</v>
+        <v>491158</v>
       </c>
       <c r="R63" t="n">
-        <v>6709906</v>
+        <v>6710160</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7494,7 +7494,7 @@
         <v>129037762</v>
       </c>
       <c r="B64" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>129039716</v>
       </c>
       <c r="B66" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>129044189</v>
       </c>
       <c r="B67" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>129043659</v>
       </c>
       <c r="B68" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>129045555</v>
       </c>
       <c r="B69" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>129039681</v>
       </c>
       <c r="B70" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>129038944</v>
       </c>
       <c r="B71" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8367,10 +8367,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129040356</v>
+        <v>129038053</v>
       </c>
       <c r="B72" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8378,34 +8378,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>491211</v>
+        <v>490886</v>
       </c>
       <c r="R72" t="n">
-        <v>6710165</v>
+        <v>6709872</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,7 +8442,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8447,7 +8452,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8474,10 +8484,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129043183</v>
+        <v>129038223</v>
       </c>
       <c r="B73" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8485,34 +8495,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>491200</v>
+        <v>490878</v>
       </c>
       <c r="R73" t="n">
-        <v>6709983</v>
+        <v>6709889</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8544,7 +8559,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8554,12 +8569,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8586,32 +8596,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129042724</v>
+        <v>129040356</v>
       </c>
       <c r="B74" t="n">
-        <v>92847</v>
+        <v>79034</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8621,10 +8631,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>491257</v>
+        <v>491211</v>
       </c>
       <c r="R74" t="n">
-        <v>6710085</v>
+        <v>6710165</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8656,7 +8666,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8666,7 +8676,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8693,10 +8703,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129038223</v>
+        <v>129043183</v>
       </c>
       <c r="B75" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8704,39 +8714,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490878</v>
+        <v>491200</v>
       </c>
       <c r="R75" t="n">
-        <v>6709889</v>
+        <v>6709983</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8768,7 +8773,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8778,7 +8783,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8805,50 +8815,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129038053</v>
+        <v>129042724</v>
       </c>
       <c r="B76" t="n">
-        <v>57723</v>
+        <v>92852</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490886</v>
+        <v>491257</v>
       </c>
       <c r="R76" t="n">
-        <v>6709872</v>
+        <v>6710085</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8880,7 +8885,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8890,12 +8895,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:46</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8925,7 +8925,7 @@
         <v>129040051</v>
       </c>
       <c r="B77" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>129040173</v>
       </c>
       <c r="B78" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>129039515</v>
       </c>
       <c r="B79" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>129043352</v>
       </c>
       <c r="B80" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9355,32 +9355,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129044818</v>
+        <v>129039994</v>
       </c>
       <c r="B81" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>491116</v>
+        <v>491173</v>
       </c>
       <c r="R81" t="n">
-        <v>6710020</v>
+        <v>6710152</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9435,12 +9435,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9467,50 +9462,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129042971</v>
+        <v>129038137</v>
       </c>
       <c r="B82" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>491193</v>
+        <v>490876</v>
       </c>
       <c r="R82" t="n">
-        <v>6710074</v>
+        <v>6709883</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9542,7 +9537,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9552,12 +9547,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9584,10 +9574,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129039011</v>
+        <v>129044818</v>
       </c>
       <c r="B83" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9595,39 +9585,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490936</v>
+        <v>491116</v>
       </c>
       <c r="R83" t="n">
-        <v>6709979</v>
+        <v>6710020</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9659,7 +9644,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9669,12 +9654,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9701,50 +9686,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129038137</v>
+        <v>129042971</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>57723</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490876</v>
+        <v>491193</v>
       </c>
       <c r="R84" t="n">
-        <v>6709883</v>
+        <v>6710074</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9776,7 +9761,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9786,7 +9771,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9813,45 +9803,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129039994</v>
+        <v>129039011</v>
       </c>
       <c r="B85" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>491173</v>
+        <v>490936</v>
       </c>
       <c r="R85" t="n">
-        <v>6710152</v>
+        <v>6709979</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9883,7 +9878,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9893,7 +9888,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9923,7 +9923,7 @@
         <v>129045737</v>
       </c>
       <c r="B86" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10027,10 +10027,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129040273</v>
+        <v>129043286</v>
       </c>
       <c r="B87" t="n">
-        <v>79034</v>
+        <v>91543</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10038,34 +10038,43 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491210</v>
+        <v>491185</v>
       </c>
       <c r="R87" t="n">
-        <v>6710152</v>
+        <v>6710038</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10097,7 +10106,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10107,12 +10116,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10139,7 +10143,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129042243</v>
+        <v>129040273</v>
       </c>
       <c r="B88" t="n">
         <v>79034</v>
@@ -10170,14 +10174,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491324</v>
+        <v>491210</v>
       </c>
       <c r="R88" t="n">
-        <v>6710108</v>
+        <v>6710152</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10209,7 +10213,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10219,12 +10223,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10251,7 +10255,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129043457</v>
+        <v>129042243</v>
       </c>
       <c r="B89" t="n">
         <v>79034</v>
@@ -10282,14 +10286,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491159</v>
+        <v>491324</v>
       </c>
       <c r="R89" t="n">
-        <v>6709989</v>
+        <v>6710108</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10321,7 +10325,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10331,7 +10335,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10363,10 +10367,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129043286</v>
+        <v>129043457</v>
       </c>
       <c r="B90" t="n">
-        <v>91540</v>
+        <v>79034</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10374,43 +10378,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491185</v>
+        <v>491159</v>
       </c>
       <c r="R90" t="n">
-        <v>6710038</v>
+        <v>6709989</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10442,7 +10437,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10452,7 +10447,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10482,7 +10482,7 @@
         <v>129039427</v>
       </c>
       <c r="B91" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>129039369</v>
       </c>
       <c r="B92" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>129040090</v>
       </c>
       <c r="B93" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>129041984</v>
       </c>
       <c r="B94" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>129043344</v>
       </c>
       <c r="B96" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>129044713</v>
       </c>
       <c r="B97" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>129044360</v>
       </c>
       <c r="B98" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>129041232</v>
       </c>
       <c r="B99" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>129045097</v>
       </c>
       <c r="B100" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>129044617</v>
       </c>
       <c r="B104" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>129043760</v>
       </c>
       <c r="B105" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12146,54 +12146,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129039218</v>
+        <v>129039623</v>
       </c>
       <c r="B106" t="n">
-        <v>92811</v>
+        <v>91523</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491054</v>
+        <v>491117</v>
       </c>
       <c r="R106" t="n">
-        <v>6710041</v>
+        <v>6710091</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12225,7 +12216,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12235,7 +12226,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12262,10 +12253,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129039623</v>
+        <v>129039646</v>
       </c>
       <c r="B107" t="n">
-        <v>91520</v>
+        <v>91808</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12273,21 +12264,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12332,7 +12323,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12342,7 +12333,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12369,45 +12365,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129039646</v>
+        <v>129039218</v>
       </c>
       <c r="B108" t="n">
-        <v>91805</v>
+        <v>92816</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491117</v>
+        <v>491054</v>
       </c>
       <c r="R108" t="n">
-        <v>6710091</v>
+        <v>6710041</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12439,7 +12444,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12449,12 +12454,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12484,7 +12484,7 @@
         <v>129042566</v>
       </c>
       <c r="B109" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>129044243</v>
       </c>
       <c r="B110" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129039783</v>
+        <v>129042946</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491113</v>
+        <v>491232</v>
       </c>
       <c r="R2" t="n">
-        <v>6710132</v>
+        <v>6710086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129041992</v>
+        <v>129045855</v>
       </c>
       <c r="B3" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491353</v>
+        <v>491030</v>
       </c>
       <c r="R3" t="n">
-        <v>6710077</v>
+        <v>6709895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,50 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129038956</v>
+        <v>129041481</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490939</v>
+        <v>491361</v>
       </c>
       <c r="R4" t="n">
-        <v>6709966</v>
+        <v>6710143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129045855</v>
+        <v>129039226</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>92819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491030</v>
+        <v>491060</v>
       </c>
       <c r="R5" t="n">
-        <v>6709895</v>
+        <v>6710037</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,45 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129041481</v>
+        <v>129039783</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491361</v>
+        <v>491113</v>
       </c>
       <c r="R6" t="n">
-        <v>6710143</v>
+        <v>6710132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,45 +1215,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129039226</v>
+        <v>129041992</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491060</v>
+        <v>491353</v>
       </c>
       <c r="R7" t="n">
-        <v>6710037</v>
+        <v>6710077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,45 +1322,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129042946</v>
+        <v>129038956</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491232</v>
+        <v>490939</v>
       </c>
       <c r="R8" t="n">
-        <v>6710086</v>
+        <v>6709966</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På 2 stående.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129043673</v>
+        <v>129039748</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>92819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,39 +1450,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491125</v>
+        <v>491113</v>
       </c>
       <c r="R9" t="n">
-        <v>6709976</v>
+        <v>6710132</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129040595</v>
+        <v>129040305</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>75155</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,7 +1581,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491251</v>
+        <v>491221</v>
       </c>
       <c r="R10" t="n">
         <v>6710146</v>
@@ -1621,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,45 +1653,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129040305</v>
+        <v>129041053</v>
       </c>
       <c r="B11" t="n">
-        <v>75155</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491221</v>
+        <v>491309</v>
       </c>
       <c r="R11" t="n">
-        <v>6710146</v>
+        <v>6710192</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1738,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129039748</v>
+        <v>129043673</v>
       </c>
       <c r="B12" t="n">
-        <v>92816</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,34 +1781,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491113</v>
+        <v>491125</v>
       </c>
       <c r="R12" t="n">
-        <v>6710132</v>
+        <v>6709976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,50 +1882,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129041053</v>
+        <v>129043484</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491309</v>
+        <v>491159</v>
       </c>
       <c r="R13" t="n">
-        <v>6710192</v>
+        <v>6709989</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,12 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129043484</v>
+        <v>129040595</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491159</v>
+        <v>491251</v>
       </c>
       <c r="R14" t="n">
-        <v>6709989</v>
+        <v>6710146</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2099,7 +2099,7 @@
         <v>129045778</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129041291</v>
       </c>
       <c r="B16" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129039950</v>
+        <v>129039360</v>
       </c>
       <c r="B17" t="n">
-        <v>91808</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491157</v>
+        <v>491080</v>
       </c>
       <c r="R17" t="n">
-        <v>6710161</v>
+        <v>6710071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129039360</v>
+        <v>129039950</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>91811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,21 +2433,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491080</v>
+        <v>491157</v>
       </c>
       <c r="R18" t="n">
-        <v>6710071</v>
+        <v>6710161</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,12 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,7 +2532,7 @@
         <v>129043063</v>
       </c>
       <c r="B19" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,32 +2641,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129040685</v>
+        <v>129037863</v>
       </c>
       <c r="B20" t="n">
-        <v>92816</v>
+        <v>91981</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491251</v>
+        <v>490942</v>
       </c>
       <c r="R20" t="n">
-        <v>6710146</v>
+        <v>6709873</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2751,7 +2751,7 @@
         <v>129041584</v>
       </c>
       <c r="B21" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,50 +2855,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129040720</v>
+        <v>129044129</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491296</v>
+        <v>491049</v>
       </c>
       <c r="R22" t="n">
-        <v>6710129</v>
+        <v>6709893</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,32 +2962,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129037863</v>
+        <v>129040685</v>
       </c>
       <c r="B23" t="n">
-        <v>91978</v>
+        <v>92819</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3002,10 +2997,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490942</v>
+        <v>491251</v>
       </c>
       <c r="R23" t="n">
-        <v>6709873</v>
+        <v>6710146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,45 +3069,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129044129</v>
+        <v>129040720</v>
       </c>
       <c r="B24" t="n">
-        <v>98656</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491049</v>
+        <v>491296</v>
       </c>
       <c r="R24" t="n">
-        <v>6709893</v>
+        <v>6710129</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3184,7 +3184,7 @@
         <v>129045240</v>
       </c>
       <c r="B25" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>129042527</v>
       </c>
       <c r="B26" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>129045583</v>
       </c>
       <c r="B28" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>129043562</v>
       </c>
       <c r="B29" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>129041242</v>
       </c>
       <c r="B30" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3842,45 +3842,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129040867</v>
+        <v>129040534</v>
       </c>
       <c r="B31" t="n">
-        <v>105719</v>
+        <v>91526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491332</v>
+        <v>491261</v>
       </c>
       <c r="R31" t="n">
-        <v>6710175</v>
+        <v>6710156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,50 +3949,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129039814</v>
+        <v>129038111</v>
       </c>
       <c r="B32" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491102</v>
+        <v>490874</v>
       </c>
       <c r="R32" t="n">
-        <v>6710142</v>
+        <v>6709885</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4034,7 +4034,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4061,32 +4066,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129039825</v>
+        <v>129044587</v>
       </c>
       <c r="B33" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4096,10 +4101,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491126</v>
+        <v>491075</v>
       </c>
       <c r="R33" t="n">
-        <v>6710148</v>
+        <v>6709943</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4136,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4141,7 +4146,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4168,59 +4173,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129041725</v>
+        <v>129044722</v>
       </c>
       <c r="B34" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491375</v>
+        <v>491088</v>
       </c>
       <c r="R34" t="n">
-        <v>6710101</v>
+        <v>6709977</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4252,7 +4243,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4262,7 +4253,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4289,45 +4285,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129044587</v>
+        <v>129040867</v>
       </c>
       <c r="B35" t="n">
-        <v>91808</v>
+        <v>105722</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491075</v>
+        <v>491332</v>
       </c>
       <c r="R35" t="n">
-        <v>6709943</v>
+        <v>6710175</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4359,7 +4355,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4369,7 +4365,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4396,45 +4392,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129040534</v>
+        <v>129039814</v>
       </c>
       <c r="B36" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491261</v>
+        <v>491102</v>
       </c>
       <c r="R36" t="n">
-        <v>6710156</v>
+        <v>6710142</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4466,7 +4467,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4476,7 +4477,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4503,32 +4504,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129044722</v>
+        <v>129039825</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4538,10 +4539,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491088</v>
+        <v>491126</v>
       </c>
       <c r="R37" t="n">
-        <v>6709977</v>
+        <v>6710148</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4573,7 +4574,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4583,12 +4584,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4615,50 +4611,59 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129038111</v>
+        <v>129041725</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490874</v>
+        <v>491375</v>
       </c>
       <c r="R38" t="n">
-        <v>6709885</v>
+        <v>6710101</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4690,7 +4695,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4700,12 +4705,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4732,10 +4732,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129045013</v>
+        <v>129040042</v>
       </c>
       <c r="B39" t="n">
-        <v>91523</v>
+        <v>91811</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,21 +4743,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491157</v>
+        <v>491181</v>
       </c>
       <c r="R39" t="n">
-        <v>6710121</v>
+        <v>6710144</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,10 +4839,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129040042</v>
+        <v>129045013</v>
       </c>
       <c r="B40" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4850,21 +4850,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491181</v>
+        <v>491157</v>
       </c>
       <c r="R40" t="n">
-        <v>6710144</v>
+        <v>6710121</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5069,7 +5069,7 @@
         <v>129044467</v>
       </c>
       <c r="B42" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,45 +5173,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129044319</v>
+        <v>129041044</v>
       </c>
       <c r="B43" t="n">
-        <v>91523</v>
+        <v>92819</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491049</v>
+        <v>491306</v>
       </c>
       <c r="R43" t="n">
-        <v>6709915</v>
+        <v>6710197</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,10 +5280,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129045330</v>
+        <v>129044319</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5291,39 +5291,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491085</v>
+        <v>491049</v>
       </c>
       <c r="R44" t="n">
-        <v>6710033</v>
+        <v>6709915</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5355,7 +5350,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5365,12 +5360,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,45 +5387,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129041044</v>
+        <v>129045330</v>
       </c>
       <c r="B45" t="n">
-        <v>92816</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491306</v>
+        <v>491085</v>
       </c>
       <c r="R45" t="n">
-        <v>6710197</v>
+        <v>6710033</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5467,7 +5462,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5477,7 +5472,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5507,7 +5507,7 @@
         <v>129037802</v>
       </c>
       <c r="B46" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>129039795</v>
       </c>
       <c r="B47" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>129042338</v>
       </c>
       <c r="B48" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>129038812</v>
       </c>
       <c r="B49" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>129044332</v>
       </c>
       <c r="B50" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>129045046</v>
       </c>
       <c r="B51" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>129039883</v>
       </c>
       <c r="B52" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6295,45 +6295,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129040369</v>
+        <v>129038692</v>
       </c>
       <c r="B53" t="n">
-        <v>98656</v>
+        <v>57883</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>491194</v>
+        <v>490892</v>
       </c>
       <c r="R53" t="n">
-        <v>6710167</v>
+        <v>6709919</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6365,7 +6370,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6375,7 +6380,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6405,7 +6410,7 @@
         <v>129044552</v>
       </c>
       <c r="B54" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6509,50 +6514,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129038692</v>
+        <v>129040369</v>
       </c>
       <c r="B55" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490892</v>
+        <v>491194</v>
       </c>
       <c r="R55" t="n">
-        <v>6709919</v>
+        <v>6710167</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6621,32 +6621,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129038411</v>
+        <v>129039941</v>
       </c>
       <c r="B56" t="n">
-        <v>98656</v>
+        <v>91526</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490873</v>
+        <v>491158</v>
       </c>
       <c r="R56" t="n">
-        <v>6709909</v>
+        <v>6710160</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6728,32 +6728,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129044061</v>
+        <v>129040007</v>
       </c>
       <c r="B57" t="n">
-        <v>98656</v>
+        <v>91526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>491110</v>
+        <v>491180</v>
       </c>
       <c r="R57" t="n">
-        <v>6709915</v>
+        <v>6710139</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,32 +6835,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129045420</v>
+        <v>129037776</v>
       </c>
       <c r="B58" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491009</v>
+        <v>490952</v>
       </c>
       <c r="R58" t="n">
-        <v>6709991</v>
+        <v>6709889</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,10 +6942,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129038173</v>
+        <v>129038411</v>
       </c>
       <c r="B59" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,31 +6970,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490877</v>
+        <v>490873</v>
       </c>
       <c r="R59" t="n">
-        <v>6709889</v>
+        <v>6709909</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7026,7 +7012,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7036,7 +7022,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7063,10 +7049,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129043992</v>
+        <v>129044061</v>
       </c>
       <c r="B60" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7098,10 +7084,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>491095</v>
+        <v>491110</v>
       </c>
       <c r="R60" t="n">
-        <v>6709906</v>
+        <v>6709915</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7133,7 +7119,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7143,7 +7129,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,32 +7156,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129037776</v>
+        <v>129045420</v>
       </c>
       <c r="B61" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7205,10 +7191,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490952</v>
+        <v>491009</v>
       </c>
       <c r="R61" t="n">
-        <v>6709889</v>
+        <v>6709991</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7240,7 +7226,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7250,7 +7236,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7277,45 +7263,59 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129040007</v>
+        <v>129038173</v>
       </c>
       <c r="B62" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>491180</v>
+        <v>490877</v>
       </c>
       <c r="R62" t="n">
-        <v>6710139</v>
+        <v>6709889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,32 +7384,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129039941</v>
+        <v>129043992</v>
       </c>
       <c r="B63" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491158</v>
+        <v>491095</v>
       </c>
       <c r="R63" t="n">
-        <v>6710160</v>
+        <v>6709906</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7491,45 +7491,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129037762</v>
+        <v>129039716</v>
       </c>
       <c r="B64" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490949</v>
+        <v>491118</v>
       </c>
       <c r="R64" t="n">
-        <v>6709885</v>
+        <v>6710111</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7561,7 +7566,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7571,7 +7576,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7598,32 +7608,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129042106</v>
+        <v>129044189</v>
       </c>
       <c r="B65" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7633,10 +7643,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>491327</v>
+        <v>491025</v>
       </c>
       <c r="R65" t="n">
-        <v>6710067</v>
+        <v>6709886</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7668,7 +7678,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7678,12 +7688,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7710,10 +7715,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129039716</v>
+        <v>129043659</v>
       </c>
       <c r="B66" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7739,21 +7744,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491118</v>
+        <v>491126</v>
       </c>
       <c r="R66" t="n">
-        <v>6710111</v>
+        <v>6709977</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7795,12 +7795,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7827,10 +7822,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129044189</v>
+        <v>129045555</v>
       </c>
       <c r="B67" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7862,10 +7857,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>491025</v>
+        <v>490955</v>
       </c>
       <c r="R67" t="n">
-        <v>6709886</v>
+        <v>6709969</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7897,7 +7892,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7907,7 +7902,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7934,10 +7929,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129043659</v>
+        <v>129039681</v>
       </c>
       <c r="B68" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7963,16 +7958,21 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>491126</v>
+        <v>491120</v>
       </c>
       <c r="R68" t="n">
-        <v>6709977</v>
+        <v>6710111</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8041,10 +8041,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129045555</v>
+        <v>129038944</v>
       </c>
       <c r="B69" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490955</v>
+        <v>490941</v>
       </c>
       <c r="R69" t="n">
-        <v>6709969</v>
+        <v>6709965</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8148,50 +8148,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129039681</v>
+        <v>129037762</v>
       </c>
       <c r="B70" t="n">
-        <v>98656</v>
+        <v>91526</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>491120</v>
+        <v>490949</v>
       </c>
       <c r="R70" t="n">
-        <v>6710111</v>
+        <v>6709885</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8223,7 +8218,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8233,7 +8228,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8260,32 +8255,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129038944</v>
+        <v>129042106</v>
       </c>
       <c r="B71" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8295,10 +8290,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490941</v>
+        <v>491327</v>
       </c>
       <c r="R71" t="n">
-        <v>6709965</v>
+        <v>6710067</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8330,7 +8325,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8340,7 +8335,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8596,32 +8596,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129040356</v>
+        <v>129042724</v>
       </c>
       <c r="B74" t="n">
-        <v>79034</v>
+        <v>92855</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8631,10 +8631,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>491211</v>
+        <v>491257</v>
       </c>
       <c r="R74" t="n">
-        <v>6710165</v>
+        <v>6710085</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8703,10 +8703,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129043183</v>
+        <v>129040356</v>
       </c>
       <c r="B75" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>491200</v>
+        <v>491211</v>
       </c>
       <c r="R75" t="n">
-        <v>6709983</v>
+        <v>6710165</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8783,12 +8783,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8815,32 +8810,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129042724</v>
+        <v>129043183</v>
       </c>
       <c r="B76" t="n">
-        <v>92852</v>
+        <v>79035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8850,10 +8845,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>491257</v>
+        <v>491200</v>
       </c>
       <c r="R76" t="n">
-        <v>6710085</v>
+        <v>6709983</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8885,7 +8880,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8895,7 +8890,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8925,7 +8925,7 @@
         <v>129040051</v>
       </c>
       <c r="B77" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>129040173</v>
       </c>
       <c r="B78" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9136,10 +9136,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129039515</v>
+        <v>129043352</v>
       </c>
       <c r="B79" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9165,21 +9165,16 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>491104</v>
+        <v>491188</v>
       </c>
       <c r="R79" t="n">
-        <v>6710105</v>
+        <v>6709988</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9211,7 +9206,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9221,7 +9216,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9248,10 +9243,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129043352</v>
+        <v>129039515</v>
       </c>
       <c r="B80" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9277,16 +9272,21 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>491188</v>
+        <v>491104</v>
       </c>
       <c r="R80" t="n">
-        <v>6709988</v>
+        <v>6710105</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9355,32 +9355,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129039994</v>
+        <v>129044818</v>
       </c>
       <c r="B81" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>491173</v>
+        <v>491116</v>
       </c>
       <c r="R81" t="n">
-        <v>6710152</v>
+        <v>6710020</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9435,7 +9435,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9462,50 +9467,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129038137</v>
+        <v>129042971</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>57723</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490876</v>
+        <v>491193</v>
       </c>
       <c r="R82" t="n">
-        <v>6709883</v>
+        <v>6710074</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9537,7 +9542,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9547,7 +9552,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9574,10 +9584,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129044818</v>
+        <v>129039011</v>
       </c>
       <c r="B83" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9585,34 +9595,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>491116</v>
+        <v>490936</v>
       </c>
       <c r="R83" t="n">
-        <v>6710020</v>
+        <v>6709979</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9644,7 +9659,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9654,12 +9669,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9686,50 +9701,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129042971</v>
+        <v>129038137</v>
       </c>
       <c r="B84" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>491193</v>
+        <v>490876</v>
       </c>
       <c r="R84" t="n">
-        <v>6710074</v>
+        <v>6709883</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9761,7 +9776,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9771,12 +9786,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9803,50 +9813,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129039011</v>
+        <v>129039994</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490936</v>
+        <v>491173</v>
       </c>
       <c r="R85" t="n">
-        <v>6709979</v>
+        <v>6710152</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9878,7 +9883,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9888,12 +9893,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9923,7 +9923,7 @@
         <v>129045737</v>
       </c>
       <c r="B86" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10027,10 +10027,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129043286</v>
+        <v>129040273</v>
       </c>
       <c r="B87" t="n">
-        <v>91543</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10038,43 +10038,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491185</v>
+        <v>491210</v>
       </c>
       <c r="R87" t="n">
-        <v>6710038</v>
+        <v>6710152</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10106,7 +10097,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10116,7 +10107,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10143,10 +10139,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129040273</v>
+        <v>129042243</v>
       </c>
       <c r="B88" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10174,14 +10170,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491210</v>
+        <v>491324</v>
       </c>
       <c r="R88" t="n">
-        <v>6710152</v>
+        <v>6710108</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10213,7 +10209,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10223,12 +10219,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10255,10 +10251,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129042243</v>
+        <v>129043457</v>
       </c>
       <c r="B89" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10286,14 +10282,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491324</v>
+        <v>491159</v>
       </c>
       <c r="R89" t="n">
-        <v>6710108</v>
+        <v>6709989</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10325,7 +10321,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10335,7 +10331,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10367,10 +10363,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129043457</v>
+        <v>129043286</v>
       </c>
       <c r="B90" t="n">
-        <v>79034</v>
+        <v>91546</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10378,34 +10374,43 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491159</v>
+        <v>491185</v>
       </c>
       <c r="R90" t="n">
-        <v>6709989</v>
+        <v>6710038</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10437,7 +10442,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10447,12 +10452,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10482,7 +10482,7 @@
         <v>129039427</v>
       </c>
       <c r="B91" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>129039369</v>
       </c>
       <c r="B92" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>129040090</v>
       </c>
       <c r="B93" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10814,10 +10814,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129041984</v>
+        <v>129041444</v>
       </c>
       <c r="B94" t="n">
-        <v>91808</v>
+        <v>57723</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10825,34 +10825,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491353</v>
+        <v>491362</v>
       </c>
       <c r="R94" t="n">
-        <v>6710077</v>
+        <v>6710150</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10884,7 +10889,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10894,7 +10899,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10921,10 +10931,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129041444</v>
+        <v>129041984</v>
       </c>
       <c r="B95" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10932,39 +10942,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491362</v>
+        <v>491353</v>
       </c>
       <c r="R95" t="n">
-        <v>6710150</v>
+        <v>6710077</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10996,7 +11001,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11006,12 +11011,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11041,7 +11041,7 @@
         <v>129043344</v>
       </c>
       <c r="B96" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>129044713</v>
       </c>
       <c r="B97" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>129044360</v>
       </c>
       <c r="B98" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>129041232</v>
       </c>
       <c r="B99" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>129045097</v>
       </c>
       <c r="B100" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>129040149</v>
       </c>
       <c r="B101" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>129044617</v>
       </c>
       <c r="B104" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>129043760</v>
       </c>
       <c r="B105" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12146,45 +12146,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129039623</v>
+        <v>129039218</v>
       </c>
       <c r="B106" t="n">
-        <v>91523</v>
+        <v>92819</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491117</v>
+        <v>491054</v>
       </c>
       <c r="R106" t="n">
-        <v>6710091</v>
+        <v>6710041</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12216,7 +12225,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12226,7 +12235,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12253,32 +12262,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129039646</v>
+        <v>129044243</v>
       </c>
       <c r="B107" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12288,10 +12297,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491117</v>
+        <v>491026</v>
       </c>
       <c r="R107" t="n">
-        <v>6710091</v>
+        <v>6709889</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12323,7 +12332,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12333,12 +12342,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12365,54 +12369,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129039218</v>
+        <v>129039646</v>
       </c>
       <c r="B108" t="n">
-        <v>92816</v>
+        <v>91811</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491054</v>
+        <v>491117</v>
       </c>
       <c r="R108" t="n">
-        <v>6710041</v>
+        <v>6710091</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12444,7 +12439,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12454,7 +12449,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12484,7 +12484,7 @@
         <v>129042566</v>
       </c>
       <c r="B109" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12588,32 +12588,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129044243</v>
+        <v>129039623</v>
       </c>
       <c r="B110" t="n">
-        <v>98656</v>
+        <v>91526</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491026</v>
+        <v>491117</v>
       </c>
       <c r="R110" t="n">
-        <v>6709889</v>
+        <v>6710091</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129042946</v>
+        <v>129039783</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491232</v>
+        <v>491113</v>
       </c>
       <c r="R2" t="n">
-        <v>6710086</v>
+        <v>6710132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På 2 stående.</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129045855</v>
+        <v>129041992</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491030</v>
+        <v>491353</v>
       </c>
       <c r="R3" t="n">
-        <v>6709895</v>
+        <v>6710077</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129041481</v>
+        <v>129038956</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491361</v>
+        <v>490939</v>
       </c>
       <c r="R4" t="n">
-        <v>6710143</v>
+        <v>6709966</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1108,32 +1113,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129039783</v>
+        <v>129042946</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491113</v>
+        <v>491232</v>
       </c>
       <c r="R6" t="n">
-        <v>6710132</v>
+        <v>6710086</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,45 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129041992</v>
+        <v>129045855</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491353</v>
+        <v>491030</v>
       </c>
       <c r="R7" t="n">
-        <v>6710077</v>
+        <v>6709895</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,50 +1332,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129038956</v>
+        <v>129041481</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490939</v>
+        <v>491361</v>
       </c>
       <c r="R8" t="n">
-        <v>6709966</v>
+        <v>6710143</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,12 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,45 +1439,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129039748</v>
+        <v>129041053</v>
       </c>
       <c r="B9" t="n">
-        <v>92819</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491113</v>
+        <v>491309</v>
       </c>
       <c r="R9" t="n">
-        <v>6710132</v>
+        <v>6710192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1524,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129040305</v>
+        <v>129039748</v>
       </c>
       <c r="B10" t="n">
-        <v>75155</v>
+        <v>92819</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491221</v>
+        <v>491113</v>
       </c>
       <c r="R10" t="n">
-        <v>6710146</v>
+        <v>6710132</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,50 +1663,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129041053</v>
+        <v>129040305</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>75155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491309</v>
+        <v>491221</v>
       </c>
       <c r="R11" t="n">
-        <v>6710192</v>
+        <v>6710146</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,12 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2422,32 +2422,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129039950</v>
+        <v>129043063</v>
       </c>
       <c r="B18" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491157</v>
+        <v>491227</v>
       </c>
       <c r="R18" t="n">
-        <v>6710161</v>
+        <v>6710010</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,7 +2502,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På stenblock.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,32 +2534,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129043063</v>
+        <v>129039950</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2564,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491227</v>
+        <v>491157</v>
       </c>
       <c r="R19" t="n">
-        <v>6710010</v>
+        <v>6710161</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2609,12 +2614,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På stenblock.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,32 +2641,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129037863</v>
+        <v>129040685</v>
       </c>
       <c r="B20" t="n">
-        <v>91981</v>
+        <v>92819</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490942</v>
+        <v>491251</v>
       </c>
       <c r="R20" t="n">
-        <v>6709873</v>
+        <v>6710146</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129044129</v>
+        <v>129037863</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>91981</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2866,21 +2866,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491049</v>
+        <v>490942</v>
       </c>
       <c r="R22" t="n">
-        <v>6709893</v>
+        <v>6709873</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129040685</v>
+        <v>129040720</v>
       </c>
       <c r="B23" t="n">
-        <v>92819</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,34 +2973,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491251</v>
+        <v>491296</v>
       </c>
       <c r="R23" t="n">
-        <v>6710146</v>
+        <v>6710129</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,50 +3074,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129040720</v>
+        <v>129044129</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491296</v>
+        <v>491049</v>
       </c>
       <c r="R24" t="n">
-        <v>6710129</v>
+        <v>6709893</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,32 +3181,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129045240</v>
+        <v>129045583</v>
       </c>
       <c r="B25" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491133</v>
+        <v>490946</v>
       </c>
       <c r="R25" t="n">
-        <v>6710118</v>
+        <v>6709935</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,54 +3288,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129042527</v>
+        <v>129043562</v>
       </c>
       <c r="B26" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491296</v>
+        <v>491129</v>
       </c>
       <c r="R26" t="n">
-        <v>6710104</v>
+        <v>6709987</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3358,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3377,7 +3368,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3404,50 +3395,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129040515</v>
+        <v>129041242</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491251</v>
+        <v>491341</v>
       </c>
       <c r="R27" t="n">
-        <v>6710165</v>
+        <v>6710206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3479,7 +3465,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3489,12 +3475,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,32 +3502,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129045583</v>
+        <v>129045240</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3556,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490946</v>
+        <v>491133</v>
       </c>
       <c r="R28" t="n">
-        <v>6709935</v>
+        <v>6710118</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3601,7 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3628,45 +3609,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129043562</v>
+        <v>129042527</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491129</v>
+        <v>491296</v>
       </c>
       <c r="R29" t="n">
-        <v>6709987</v>
+        <v>6710104</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3688,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3698,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,45 +3725,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129041242</v>
+        <v>129040515</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491341</v>
+        <v>491251</v>
       </c>
       <c r="R30" t="n">
-        <v>6710206</v>
+        <v>6710165</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3800,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3810,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129040534</v>
+        <v>129044587</v>
       </c>
       <c r="B31" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491261</v>
+        <v>491075</v>
       </c>
       <c r="R31" t="n">
-        <v>6710156</v>
+        <v>6709943</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,10 +3949,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129038111</v>
+        <v>129040534</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,39 +3960,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490874</v>
+        <v>491261</v>
       </c>
       <c r="R32" t="n">
-        <v>6709885</v>
+        <v>6710156</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4034,12 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4066,10 +4056,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129044587</v>
+        <v>129044722</v>
       </c>
       <c r="B33" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4077,21 +4067,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4101,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491075</v>
+        <v>491088</v>
       </c>
       <c r="R33" t="n">
-        <v>6709943</v>
+        <v>6709977</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4136,7 +4126,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4146,7 +4136,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4173,10 +4168,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129044722</v>
+        <v>129038111</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4184,34 +4179,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491088</v>
+        <v>490874</v>
       </c>
       <c r="R34" t="n">
-        <v>6709977</v>
+        <v>6709885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4732,10 +4732,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129040042</v>
+        <v>129045013</v>
       </c>
       <c r="B39" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,21 +4743,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491181</v>
+        <v>491157</v>
       </c>
       <c r="R39" t="n">
-        <v>6710144</v>
+        <v>6710121</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,10 +4839,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129045013</v>
+        <v>129040042</v>
       </c>
       <c r="B40" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4850,21 +4850,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491157</v>
+        <v>491181</v>
       </c>
       <c r="R40" t="n">
-        <v>6710121</v>
+        <v>6710144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5173,45 +5173,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129041044</v>
+        <v>129044319</v>
       </c>
       <c r="B43" t="n">
-        <v>92819</v>
+        <v>91526</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491306</v>
+        <v>491049</v>
       </c>
       <c r="R43" t="n">
-        <v>6710197</v>
+        <v>6709915</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,45 +5280,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129044319</v>
+        <v>129041044</v>
       </c>
       <c r="B44" t="n">
-        <v>91526</v>
+        <v>92819</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491049</v>
+        <v>491306</v>
       </c>
       <c r="R44" t="n">
-        <v>6709915</v>
+        <v>6710197</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5858,54 +5858,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129038812</v>
+        <v>129044332</v>
       </c>
       <c r="B49" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490918</v>
+        <v>491049</v>
       </c>
       <c r="R49" t="n">
-        <v>6709933</v>
+        <v>6709914</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5937,7 +5928,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5947,7 +5938,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5974,7 +5965,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129044332</v>
+        <v>129045046</v>
       </c>
       <c r="B50" t="n">
         <v>98659</v>
@@ -6009,10 +6000,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491049</v>
+        <v>491153</v>
       </c>
       <c r="R50" t="n">
-        <v>6709914</v>
+        <v>6710121</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6044,7 +6035,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6054,7 +6045,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6081,7 +6072,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129045046</v>
+        <v>129039883</v>
       </c>
       <c r="B51" t="n">
         <v>98659</v>
@@ -6116,10 +6107,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>491153</v>
+        <v>491128</v>
       </c>
       <c r="R51" t="n">
-        <v>6710121</v>
+        <v>6710150</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6151,7 +6142,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6161,7 +6152,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6188,45 +6179,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129039883</v>
+        <v>129038812</v>
       </c>
       <c r="B52" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>491128</v>
+        <v>490918</v>
       </c>
       <c r="R52" t="n">
-        <v>6710150</v>
+        <v>6709933</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6621,32 +6621,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129039941</v>
+        <v>129038411</v>
       </c>
       <c r="B56" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>491158</v>
+        <v>490873</v>
       </c>
       <c r="R56" t="n">
-        <v>6710160</v>
+        <v>6709909</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6728,32 +6728,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129040007</v>
+        <v>129044061</v>
       </c>
       <c r="B57" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>491180</v>
+        <v>491110</v>
       </c>
       <c r="R57" t="n">
-        <v>6710139</v>
+        <v>6709915</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,32 +6835,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129037776</v>
+        <v>129045420</v>
       </c>
       <c r="B58" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490952</v>
+        <v>491009</v>
       </c>
       <c r="R58" t="n">
-        <v>6709889</v>
+        <v>6709991</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,7 +6942,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129038411</v>
+        <v>129038173</v>
       </c>
       <c r="B59" t="n">
         <v>98659</v>
@@ -6970,17 +6970,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490873</v>
+        <v>490877</v>
       </c>
       <c r="R59" t="n">
-        <v>6709909</v>
+        <v>6709889</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7012,7 +7026,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7022,7 +7036,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7049,7 +7063,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129044061</v>
+        <v>129043992</v>
       </c>
       <c r="B60" t="n">
         <v>98659</v>
@@ -7084,10 +7098,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>491110</v>
+        <v>491095</v>
       </c>
       <c r="R60" t="n">
-        <v>6709915</v>
+        <v>6709906</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7119,7 +7133,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7129,7 +7143,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7156,32 +7170,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045420</v>
+        <v>129037776</v>
       </c>
       <c r="B61" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7191,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>491009</v>
+        <v>490952</v>
       </c>
       <c r="R61" t="n">
-        <v>6709991</v>
+        <v>6709889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7226,7 +7240,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7236,7 +7250,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7263,59 +7277,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129038173</v>
+        <v>129040007</v>
       </c>
       <c r="B62" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490877</v>
+        <v>491180</v>
       </c>
       <c r="R62" t="n">
-        <v>6709889</v>
+        <v>6710139</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,32 +7384,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129043992</v>
+        <v>129039941</v>
       </c>
       <c r="B63" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491095</v>
+        <v>491158</v>
       </c>
       <c r="R63" t="n">
-        <v>6709906</v>
+        <v>6710160</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7491,50 +7491,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129039716</v>
+        <v>129037762</v>
       </c>
       <c r="B64" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>491118</v>
+        <v>490949</v>
       </c>
       <c r="R64" t="n">
-        <v>6710111</v>
+        <v>6709885</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7566,7 +7561,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7576,12 +7571,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7608,7 +7598,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129044189</v>
+        <v>129039716</v>
       </c>
       <c r="B65" t="n">
         <v>98659</v>
@@ -7637,16 +7627,21 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>491025</v>
+        <v>491118</v>
       </c>
       <c r="R65" t="n">
-        <v>6709886</v>
+        <v>6710111</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7678,7 +7673,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7688,7 +7683,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7715,7 +7715,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129043659</v>
+        <v>129044189</v>
       </c>
       <c r="B66" t="n">
         <v>98659</v>
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491126</v>
+        <v>491025</v>
       </c>
       <c r="R66" t="n">
-        <v>6709977</v>
+        <v>6709886</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7822,7 +7822,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129045555</v>
+        <v>129043659</v>
       </c>
       <c r="B67" t="n">
         <v>98659</v>
@@ -7857,10 +7857,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490955</v>
+        <v>491126</v>
       </c>
       <c r="R67" t="n">
-        <v>6709969</v>
+        <v>6709977</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7929,7 +7929,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129039681</v>
+        <v>129045555</v>
       </c>
       <c r="B68" t="n">
         <v>98659</v>
@@ -7958,21 +7958,16 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>491120</v>
+        <v>490955</v>
       </c>
       <c r="R68" t="n">
-        <v>6710111</v>
+        <v>6709969</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8004,7 +7999,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8014,7 +8009,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8041,7 +8036,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129038944</v>
+        <v>129039681</v>
       </c>
       <c r="B69" t="n">
         <v>98659</v>
@@ -8070,16 +8065,21 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490941</v>
+        <v>491120</v>
       </c>
       <c r="R69" t="n">
-        <v>6709965</v>
+        <v>6710111</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8148,32 +8148,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129037762</v>
+        <v>129038944</v>
       </c>
       <c r="B70" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490949</v>
+        <v>490941</v>
       </c>
       <c r="R70" t="n">
-        <v>6709885</v>
+        <v>6709965</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8367,50 +8367,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129038053</v>
+        <v>129042724</v>
       </c>
       <c r="B72" t="n">
-        <v>57723</v>
+        <v>92855</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490886</v>
+        <v>491257</v>
       </c>
       <c r="R72" t="n">
-        <v>6709872</v>
+        <v>6710085</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8442,7 +8437,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8452,12 +8447,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>08:46</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8484,7 +8474,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129038223</v>
+        <v>129038053</v>
       </c>
       <c r="B73" t="n">
         <v>57723</v>
@@ -8515,7 +8505,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8524,10 +8514,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490878</v>
+        <v>490886</v>
       </c>
       <c r="R73" t="n">
-        <v>6709889</v>
+        <v>6709872</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8559,7 +8549,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8569,7 +8559,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8596,45 +8591,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129042724</v>
+        <v>129038223</v>
       </c>
       <c r="B74" t="n">
-        <v>92855</v>
+        <v>57723</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>491257</v>
+        <v>490878</v>
       </c>
       <c r="R74" t="n">
-        <v>6710085</v>
+        <v>6709889</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8703,32 +8703,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129040356</v>
+        <v>129040051</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>491211</v>
+        <v>491183</v>
       </c>
       <c r="R75" t="n">
-        <v>6710165</v>
+        <v>6710141</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8810,7 +8810,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129043183</v>
+        <v>129040356</v>
       </c>
       <c r="B76" t="n">
         <v>79035</v>
@@ -8845,10 +8845,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>491200</v>
+        <v>491211</v>
       </c>
       <c r="R76" t="n">
-        <v>6709983</v>
+        <v>6710165</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8890,12 +8890,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8922,32 +8917,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129040051</v>
+        <v>129043183</v>
       </c>
       <c r="B77" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8957,10 +8952,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>491183</v>
+        <v>491200</v>
       </c>
       <c r="R77" t="n">
-        <v>6710141</v>
+        <v>6709983</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8992,7 +8987,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9002,7 +8997,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9136,7 +9136,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129043352</v>
+        <v>129039515</v>
       </c>
       <c r="B79" t="n">
         <v>98659</v>
@@ -9165,16 +9165,21 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>491188</v>
+        <v>491104</v>
       </c>
       <c r="R79" t="n">
-        <v>6709988</v>
+        <v>6710105</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9206,7 +9211,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9216,7 +9221,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9243,7 +9248,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129039515</v>
+        <v>129043352</v>
       </c>
       <c r="B80" t="n">
         <v>98659</v>
@@ -9272,21 +9277,16 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>491104</v>
+        <v>491188</v>
       </c>
       <c r="R80" t="n">
-        <v>6710105</v>
+        <v>6709988</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9355,45 +9355,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129044818</v>
+        <v>129038137</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>491116</v>
+        <v>490876</v>
       </c>
       <c r="R81" t="n">
-        <v>6710020</v>
+        <v>6709883</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9425,7 +9430,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9435,12 +9440,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9467,50 +9467,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129042971</v>
+        <v>129039994</v>
       </c>
       <c r="B82" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>491193</v>
+        <v>491173</v>
       </c>
       <c r="R82" t="n">
-        <v>6710074</v>
+        <v>6710152</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9542,7 +9537,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9552,12 +9547,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9584,10 +9574,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129039011</v>
+        <v>129044818</v>
       </c>
       <c r="B83" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9595,39 +9585,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490936</v>
+        <v>491116</v>
       </c>
       <c r="R83" t="n">
-        <v>6709979</v>
+        <v>6710020</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9659,7 +9644,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9669,12 +9654,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9701,50 +9686,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129038137</v>
+        <v>129042971</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>57723</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490876</v>
+        <v>491193</v>
       </c>
       <c r="R84" t="n">
-        <v>6709883</v>
+        <v>6710074</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9776,7 +9761,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9786,7 +9771,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9813,45 +9803,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129039994</v>
+        <v>129039011</v>
       </c>
       <c r="B85" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>491173</v>
+        <v>490936</v>
       </c>
       <c r="R85" t="n">
-        <v>6710152</v>
+        <v>6709979</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9883,7 +9878,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9893,7 +9888,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9920,32 +9920,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129045737</v>
+        <v>129039427</v>
       </c>
       <c r="B86" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>491006</v>
+        <v>491089</v>
       </c>
       <c r="R86" t="n">
-        <v>6709889</v>
+        <v>6710079</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10027,45 +10027,59 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129040273</v>
+        <v>129039369</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491210</v>
+        <v>491082</v>
       </c>
       <c r="R87" t="n">
-        <v>6710152</v>
+        <v>6710072</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10097,7 +10111,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10107,12 +10121,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10139,45 +10148,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129042243</v>
+        <v>129040090</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491324</v>
+        <v>491189</v>
       </c>
       <c r="R88" t="n">
-        <v>6710108</v>
+        <v>6710146</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10209,7 +10218,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10219,12 +10228,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10251,32 +10255,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129043457</v>
+        <v>129045737</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10286,10 +10290,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491159</v>
+        <v>491006</v>
       </c>
       <c r="R89" t="n">
-        <v>6709989</v>
+        <v>6709889</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10321,7 +10325,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10331,12 +10335,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10479,32 +10478,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129039427</v>
+        <v>129040273</v>
       </c>
       <c r="B91" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10514,10 +10513,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491089</v>
+        <v>491210</v>
       </c>
       <c r="R91" t="n">
-        <v>6710079</v>
+        <v>6710152</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10549,7 +10548,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10559,7 +10558,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10586,59 +10590,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129039369</v>
+        <v>129042243</v>
       </c>
       <c r="B92" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491082</v>
+        <v>491324</v>
       </c>
       <c r="R92" t="n">
-        <v>6710072</v>
+        <v>6710108</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10670,7 +10660,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10680,7 +10670,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10707,32 +10702,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129040090</v>
+        <v>129043457</v>
       </c>
       <c r="B93" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10742,10 +10737,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491189</v>
+        <v>491159</v>
       </c>
       <c r="R93" t="n">
-        <v>6710146</v>
+        <v>6709989</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10777,7 +10772,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10787,7 +10782,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129041444</v>
+        <v>129041984</v>
       </c>
       <c r="B94" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10825,39 +10825,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491362</v>
+        <v>491353</v>
       </c>
       <c r="R94" t="n">
-        <v>6710150</v>
+        <v>6710077</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10889,7 +10884,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10899,12 +10894,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10931,10 +10921,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129041984</v>
+        <v>129041444</v>
       </c>
       <c r="B95" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10942,34 +10932,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491353</v>
+        <v>491362</v>
       </c>
       <c r="R95" t="n">
-        <v>6710077</v>
+        <v>6710150</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11001,7 +10996,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11011,7 +11006,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11588,32 +11588,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129040149</v>
+        <v>129044617</v>
       </c>
       <c r="B101" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11623,10 +11623,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491192</v>
+        <v>491091</v>
       </c>
       <c r="R101" t="n">
-        <v>6710147</v>
+        <v>6709950</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11695,50 +11695,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129038846</v>
+        <v>129043760</v>
       </c>
       <c r="B102" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490903</v>
+        <v>491096</v>
       </c>
       <c r="R102" t="n">
-        <v>6709932</v>
+        <v>6709954</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11770,7 +11765,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11780,12 +11775,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11812,10 +11802,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129045506</v>
+        <v>129040149</v>
       </c>
       <c r="B103" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11823,42 +11813,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490975</v>
+        <v>491192</v>
       </c>
       <c r="R103" t="n">
-        <v>6709983</v>
+        <v>6710147</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11890,7 +11872,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11900,12 +11882,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Bohål i gran, på ca 2m.</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11932,45 +11909,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129044617</v>
+        <v>129038846</v>
       </c>
       <c r="B104" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491091</v>
+        <v>490903</v>
       </c>
       <c r="R104" t="n">
-        <v>6709950</v>
+        <v>6709932</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12002,7 +11984,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12012,7 +11994,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12039,45 +12026,53 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129043760</v>
+        <v>129045506</v>
       </c>
       <c r="B105" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491096</v>
+        <v>490975</v>
       </c>
       <c r="R105" t="n">
-        <v>6709954</v>
+        <v>6709983</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12109,7 +12104,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12119,7 +12114,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Bohål i gran, på ca 2m.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12146,54 +12146,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129039218</v>
+        <v>129039623</v>
       </c>
       <c r="B106" t="n">
-        <v>92819</v>
+        <v>91526</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491054</v>
+        <v>491117</v>
       </c>
       <c r="R106" t="n">
-        <v>6710041</v>
+        <v>6710091</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12225,7 +12216,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12235,7 +12226,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12262,32 +12253,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129044243</v>
+        <v>129039646</v>
       </c>
       <c r="B107" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12297,10 +12288,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491026</v>
+        <v>491117</v>
       </c>
       <c r="R107" t="n">
-        <v>6709889</v>
+        <v>6710091</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12332,7 +12323,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12342,7 +12333,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12369,45 +12365,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129039646</v>
+        <v>129039218</v>
       </c>
       <c r="B108" t="n">
-        <v>91811</v>
+        <v>92819</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491117</v>
+        <v>491054</v>
       </c>
       <c r="R108" t="n">
-        <v>6710091</v>
+        <v>6710041</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12439,7 +12444,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12449,12 +12454,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12588,32 +12588,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129039623</v>
+        <v>129044243</v>
       </c>
       <c r="B110" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491117</v>
+        <v>491026</v>
       </c>
       <c r="R110" t="n">
-        <v>6710091</v>
+        <v>6709889</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129039783</v>
+        <v>129039226</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>92819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491113</v>
+        <v>491060</v>
       </c>
       <c r="R2" t="n">
-        <v>6710132</v>
+        <v>6710037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129041992</v>
+        <v>129042946</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491353</v>
+        <v>491232</v>
       </c>
       <c r="R3" t="n">
-        <v>6710077</v>
+        <v>6710086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,50 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129038956</v>
+        <v>129045855</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490939</v>
+        <v>491030</v>
       </c>
       <c r="R4" t="n">
-        <v>6709966</v>
+        <v>6709895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129039226</v>
+        <v>129041481</v>
       </c>
       <c r="B5" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491060</v>
+        <v>491361</v>
       </c>
       <c r="R5" t="n">
-        <v>6710037</v>
+        <v>6710143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129042946</v>
+        <v>129039783</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491232</v>
+        <v>491113</v>
       </c>
       <c r="R6" t="n">
-        <v>6710086</v>
+        <v>6710132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På 2 stående.</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,45 +1215,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129045855</v>
+        <v>129041992</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491030</v>
+        <v>491353</v>
       </c>
       <c r="R7" t="n">
-        <v>6709895</v>
+        <v>6710077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,45 +1322,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129041481</v>
+        <v>129038956</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491361</v>
+        <v>490939</v>
       </c>
       <c r="R8" t="n">
-        <v>6710143</v>
+        <v>6709966</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1407,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2422,32 +2422,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129043063</v>
+        <v>129039950</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491227</v>
+        <v>491157</v>
       </c>
       <c r="R18" t="n">
-        <v>6710010</v>
+        <v>6710161</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,12 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På stenblock.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,32 +2529,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129039950</v>
+        <v>129043063</v>
       </c>
       <c r="B19" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491157</v>
+        <v>491227</v>
       </c>
       <c r="R19" t="n">
-        <v>6710161</v>
+        <v>6710010</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,7 +2599,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,7 +2609,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På stenblock.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,32 +2641,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129040685</v>
+        <v>129037863</v>
       </c>
       <c r="B20" t="n">
-        <v>92819</v>
+        <v>91981</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491251</v>
+        <v>490942</v>
       </c>
       <c r="R20" t="n">
-        <v>6710146</v>
+        <v>6709873</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,45 +2748,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129041584</v>
+        <v>129040685</v>
       </c>
       <c r="B21" t="n">
-        <v>91546</v>
+        <v>92819</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491362</v>
+        <v>491251</v>
       </c>
       <c r="R21" t="n">
-        <v>6710143</v>
+        <v>6710146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,45 +2855,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129037863</v>
+        <v>129041584</v>
       </c>
       <c r="B22" t="n">
-        <v>91981</v>
+        <v>91546</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490942</v>
+        <v>491362</v>
       </c>
       <c r="R22" t="n">
-        <v>6709873</v>
+        <v>6710143</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4732,10 +4732,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129045013</v>
+        <v>129038104</v>
       </c>
       <c r="B39" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,34 +4743,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491157</v>
+        <v>490880</v>
       </c>
       <c r="R39" t="n">
-        <v>6710121</v>
+        <v>6709882</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4802,7 +4810,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4812,7 +4820,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,10 +4852,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129040042</v>
+        <v>129045013</v>
       </c>
       <c r="B40" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4850,21 +4863,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4874,10 +4887,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491181</v>
+        <v>491157</v>
       </c>
       <c r="R40" t="n">
-        <v>6710144</v>
+        <v>6710121</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4909,7 +4922,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4919,7 +4932,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4946,10 +4959,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129038104</v>
+        <v>129040042</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4957,42 +4970,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490880</v>
+        <v>491181</v>
       </c>
       <c r="R41" t="n">
-        <v>6709882</v>
+        <v>6710144</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5024,7 +5029,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5034,12 +5039,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6621,32 +6621,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129038411</v>
+        <v>129037776</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490873</v>
+        <v>490952</v>
       </c>
       <c r="R56" t="n">
-        <v>6709909</v>
+        <v>6709889</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6728,32 +6728,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129044061</v>
+        <v>129040007</v>
       </c>
       <c r="B57" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>491110</v>
+        <v>491180</v>
       </c>
       <c r="R57" t="n">
-        <v>6709915</v>
+        <v>6710139</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,32 +6835,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129045420</v>
+        <v>129039941</v>
       </c>
       <c r="B58" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491009</v>
+        <v>491158</v>
       </c>
       <c r="R58" t="n">
-        <v>6709991</v>
+        <v>6710160</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,7 +6942,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129038173</v>
+        <v>129038411</v>
       </c>
       <c r="B59" t="n">
         <v>98659</v>
@@ -6970,31 +6970,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490877</v>
+        <v>490873</v>
       </c>
       <c r="R59" t="n">
-        <v>6709889</v>
+        <v>6709909</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7026,7 +7012,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7036,7 +7022,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7063,7 +7049,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129043992</v>
+        <v>129044061</v>
       </c>
       <c r="B60" t="n">
         <v>98659</v>
@@ -7098,10 +7084,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>491095</v>
+        <v>491110</v>
       </c>
       <c r="R60" t="n">
-        <v>6709906</v>
+        <v>6709915</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7133,7 +7119,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7143,7 +7129,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,32 +7156,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129037776</v>
+        <v>129045420</v>
       </c>
       <c r="B61" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7205,10 +7191,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490952</v>
+        <v>491009</v>
       </c>
       <c r="R61" t="n">
-        <v>6709889</v>
+        <v>6709991</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7240,7 +7226,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7250,7 +7236,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7277,45 +7263,59 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129040007</v>
+        <v>129038173</v>
       </c>
       <c r="B62" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>491180</v>
+        <v>490877</v>
       </c>
       <c r="R62" t="n">
-        <v>6710139</v>
+        <v>6709889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,32 +7384,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129039941</v>
+        <v>129043992</v>
       </c>
       <c r="B63" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491158</v>
+        <v>491095</v>
       </c>
       <c r="R63" t="n">
-        <v>6710160</v>
+        <v>6709906</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8474,10 +8474,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129038053</v>
+        <v>129040356</v>
       </c>
       <c r="B73" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8485,39 +8485,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490886</v>
+        <v>491211</v>
       </c>
       <c r="R73" t="n">
-        <v>6709872</v>
+        <v>6710165</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8549,7 +8544,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8559,12 +8554,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:46</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8591,10 +8581,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129038223</v>
+        <v>129043183</v>
       </c>
       <c r="B74" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8602,39 +8592,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490878</v>
+        <v>491200</v>
       </c>
       <c r="R74" t="n">
-        <v>6709889</v>
+        <v>6709983</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8666,7 +8651,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8676,7 +8661,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8703,45 +8693,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129040051</v>
+        <v>129038053</v>
       </c>
       <c r="B75" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>491183</v>
+        <v>490886</v>
       </c>
       <c r="R75" t="n">
-        <v>6710141</v>
+        <v>6709872</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8773,7 +8768,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8783,7 +8778,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8810,10 +8810,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129040356</v>
+        <v>129038223</v>
       </c>
       <c r="B76" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8821,34 +8821,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>491211</v>
+        <v>490878</v>
       </c>
       <c r="R76" t="n">
-        <v>6710165</v>
+        <v>6709889</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8880,7 +8885,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8890,7 +8895,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8917,32 +8922,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129043183</v>
+        <v>129040051</v>
       </c>
       <c r="B77" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8952,10 +8957,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>491200</v>
+        <v>491183</v>
       </c>
       <c r="R77" t="n">
-        <v>6709983</v>
+        <v>6710141</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8987,7 +8992,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8997,12 +9002,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -11588,32 +11588,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129044617</v>
+        <v>129040149</v>
       </c>
       <c r="B101" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11623,10 +11623,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491091</v>
+        <v>491192</v>
       </c>
       <c r="R101" t="n">
-        <v>6709950</v>
+        <v>6710147</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11695,45 +11695,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129043760</v>
+        <v>129038846</v>
       </c>
       <c r="B102" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491096</v>
+        <v>490903</v>
       </c>
       <c r="R102" t="n">
-        <v>6709954</v>
+        <v>6709932</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11765,7 +11770,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11775,7 +11780,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11802,10 +11812,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129040149</v>
+        <v>129045506</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11813,34 +11823,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491192</v>
+        <v>490975</v>
       </c>
       <c r="R103" t="n">
-        <v>6710147</v>
+        <v>6709983</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11872,7 +11890,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11882,7 +11900,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Bohål i gran, på ca 2m.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11909,50 +11932,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129038846</v>
+        <v>129044617</v>
       </c>
       <c r="B104" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490903</v>
+        <v>491091</v>
       </c>
       <c r="R104" t="n">
-        <v>6709932</v>
+        <v>6709950</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11984,7 +12002,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11994,12 +12012,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12026,53 +12039,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129045506</v>
+        <v>129043760</v>
       </c>
       <c r="B105" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490975</v>
+        <v>491096</v>
       </c>
       <c r="R105" t="n">
-        <v>6709983</v>
+        <v>6709954</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12104,7 +12109,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12114,12 +12119,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Bohål i gran, på ca 2m.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129042946</v>
+        <v>129038956</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491232</v>
+        <v>490939</v>
       </c>
       <c r="R3" t="n">
-        <v>6710086</v>
+        <v>6709966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På 2 stående.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1322,50 +1327,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129038956</v>
+        <v>129042946</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490939</v>
+        <v>491232</v>
       </c>
       <c r="R8" t="n">
-        <v>6709966</v>
+        <v>6710086</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,50 +1439,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129041053</v>
+        <v>129043673</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491309</v>
+        <v>491125</v>
       </c>
       <c r="R9" t="n">
-        <v>6710192</v>
+        <v>6709976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,12 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,32 +1551,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129039748</v>
+        <v>129043484</v>
       </c>
       <c r="B10" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491113</v>
+        <v>491159</v>
       </c>
       <c r="R10" t="n">
-        <v>6710132</v>
+        <v>6709989</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,32 +1658,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129040305</v>
+        <v>129040595</v>
       </c>
       <c r="B11" t="n">
-        <v>75155</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,7 +1693,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491221</v>
+        <v>491251</v>
       </c>
       <c r="R11" t="n">
         <v>6710146</v>
@@ -1733,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,50 +1765,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129043673</v>
+        <v>129045778</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491125</v>
+        <v>491010</v>
       </c>
       <c r="R12" t="n">
-        <v>6709976</v>
+        <v>6709893</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129043484</v>
+        <v>129041291</v>
       </c>
       <c r="B13" t="n">
         <v>98659</v>
@@ -1913,14 +1903,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491159</v>
+        <v>491359</v>
       </c>
       <c r="R13" t="n">
-        <v>6709989</v>
+        <v>6710158</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,45 +1979,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129040595</v>
+        <v>129041053</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491251</v>
+        <v>491309</v>
       </c>
       <c r="R14" t="n">
-        <v>6710146</v>
+        <v>6710192</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2064,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129045778</v>
+        <v>129039748</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491010</v>
+        <v>491113</v>
       </c>
       <c r="R15" t="n">
-        <v>6709893</v>
+        <v>6710132</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,45 +2203,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129041291</v>
+        <v>129040305</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>75155</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491359</v>
+        <v>491221</v>
       </c>
       <c r="R16" t="n">
-        <v>6710158</v>
+        <v>6710146</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,32 +2422,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129039950</v>
+        <v>129043063</v>
       </c>
       <c r="B18" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491157</v>
+        <v>491227</v>
       </c>
       <c r="R18" t="n">
-        <v>6710161</v>
+        <v>6710010</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,7 +2502,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På stenblock.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,32 +2534,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129043063</v>
+        <v>129039950</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2564,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491227</v>
+        <v>491157</v>
       </c>
       <c r="R19" t="n">
-        <v>6710010</v>
+        <v>6710161</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2609,12 +2614,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På stenblock.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,45 +2641,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129037863</v>
+        <v>129040720</v>
       </c>
       <c r="B20" t="n">
-        <v>91981</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490942</v>
+        <v>491296</v>
       </c>
       <c r="R20" t="n">
-        <v>6709873</v>
+        <v>6710129</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2721,7 +2726,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,32 +2753,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129040685</v>
+        <v>129044129</v>
       </c>
       <c r="B21" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2783,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491251</v>
+        <v>491049</v>
       </c>
       <c r="R21" t="n">
-        <v>6710146</v>
+        <v>6709893</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2833,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,45 +2860,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129041584</v>
+        <v>129037863</v>
       </c>
       <c r="B22" t="n">
-        <v>91546</v>
+        <v>91981</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491362</v>
+        <v>490942</v>
       </c>
       <c r="R22" t="n">
-        <v>6710143</v>
+        <v>6709873</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129040720</v>
+        <v>129040685</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>92819</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,39 +2978,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491296</v>
+        <v>491251</v>
       </c>
       <c r="R23" t="n">
-        <v>6710129</v>
+        <v>6710146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,45 +3074,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129044129</v>
+        <v>129041584</v>
       </c>
       <c r="B24" t="n">
-        <v>98659</v>
+        <v>91546</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491049</v>
+        <v>491362</v>
       </c>
       <c r="R24" t="n">
-        <v>6709893</v>
+        <v>6710143</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129044587</v>
+        <v>129044722</v>
       </c>
       <c r="B31" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491075</v>
+        <v>491088</v>
       </c>
       <c r="R31" t="n">
-        <v>6709943</v>
+        <v>6709977</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3922,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,45 +3954,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129040534</v>
+        <v>129040867</v>
       </c>
       <c r="B32" t="n">
-        <v>91526</v>
+        <v>105722</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491261</v>
+        <v>491332</v>
       </c>
       <c r="R32" t="n">
-        <v>6710156</v>
+        <v>6710175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,7 +4024,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4029,7 +4034,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4056,45 +4061,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129044722</v>
+        <v>129039814</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491088</v>
+        <v>491102</v>
       </c>
       <c r="R33" t="n">
-        <v>6709977</v>
+        <v>6710142</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,7 +4136,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4136,12 +4146,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4168,50 +4173,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129038111</v>
+        <v>129039825</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490874</v>
+        <v>491126</v>
       </c>
       <c r="R34" t="n">
-        <v>6709885</v>
+        <v>6710148</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4253,12 +4253,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4285,45 +4280,59 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129040867</v>
+        <v>129041725</v>
       </c>
       <c r="B35" t="n">
-        <v>105722</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491332</v>
+        <v>491375</v>
       </c>
       <c r="R35" t="n">
-        <v>6710175</v>
+        <v>6710101</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4355,7 +4364,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4365,7 +4374,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,50 +4401,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129039814</v>
+        <v>129044587</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491102</v>
+        <v>491075</v>
       </c>
       <c r="R36" t="n">
-        <v>6710142</v>
+        <v>6709943</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4467,7 +4471,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4477,7 +4481,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4504,32 +4508,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129039825</v>
+        <v>129040534</v>
       </c>
       <c r="B37" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4539,10 +4543,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491126</v>
+        <v>491261</v>
       </c>
       <c r="R37" t="n">
-        <v>6710148</v>
+        <v>6710156</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4574,7 +4578,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4584,7 +4588,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4611,59 +4615,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129041725</v>
+        <v>129038111</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491375</v>
+        <v>490874</v>
       </c>
       <c r="R38" t="n">
-        <v>6710101</v>
+        <v>6709885</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,7 +4690,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4705,7 +4700,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4732,10 +4732,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129038104</v>
+        <v>129045013</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,42 +4743,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490880</v>
+        <v>491157</v>
       </c>
       <c r="R39" t="n">
-        <v>6709882</v>
+        <v>6710121</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4810,7 +4802,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4820,12 +4812,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4852,10 +4839,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129045013</v>
+        <v>129040042</v>
       </c>
       <c r="B40" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4863,21 +4850,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4887,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491157</v>
+        <v>491181</v>
       </c>
       <c r="R40" t="n">
-        <v>6710121</v>
+        <v>6710144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4922,7 +4909,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4932,7 +4919,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4959,10 +4946,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129040042</v>
+        <v>129038104</v>
       </c>
       <c r="B41" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,34 +4957,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491181</v>
+        <v>490880</v>
       </c>
       <c r="R41" t="n">
-        <v>6710144</v>
+        <v>6709882</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5029,7 +5024,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5039,7 +5034,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5173,10 +5173,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129044319</v>
+        <v>129045330</v>
       </c>
       <c r="B43" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5184,34 +5184,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491049</v>
+        <v>491085</v>
       </c>
       <c r="R43" t="n">
-        <v>6709915</v>
+        <v>6710033</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5243,7 +5248,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5253,7 +5258,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,45 +5290,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129041044</v>
+        <v>129044319</v>
       </c>
       <c r="B44" t="n">
-        <v>92819</v>
+        <v>91526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491306</v>
+        <v>491049</v>
       </c>
       <c r="R44" t="n">
-        <v>6710197</v>
+        <v>6709915</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5350,7 +5360,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5360,7 +5370,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,50 +5397,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129045330</v>
+        <v>129041044</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491085</v>
+        <v>491306</v>
       </c>
       <c r="R45" t="n">
-        <v>6710033</v>
+        <v>6710197</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5462,7 +5467,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5472,12 +5477,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5504,45 +5504,59 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129037802</v>
+        <v>129039795</v>
       </c>
       <c r="B46" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490941</v>
+        <v>491106</v>
       </c>
       <c r="R46" t="n">
-        <v>6709886</v>
+        <v>6710124</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5574,7 +5588,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5584,7 +5598,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5611,7 +5625,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129039795</v>
+        <v>129042338</v>
       </c>
       <c r="B47" t="n">
         <v>98659</v>
@@ -5646,24 +5660,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491106</v>
+        <v>491335</v>
       </c>
       <c r="R47" t="n">
-        <v>6710124</v>
+        <v>6710120</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5695,7 +5709,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5705,7 +5719,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5732,59 +5751,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129042338</v>
+        <v>129037802</v>
       </c>
       <c r="B48" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491335</v>
+        <v>490941</v>
       </c>
       <c r="R48" t="n">
-        <v>6710120</v>
+        <v>6709886</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5816,7 +5821,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5826,12 +5831,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5858,45 +5858,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129044332</v>
+        <v>129038812</v>
       </c>
       <c r="B49" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491049</v>
+        <v>490918</v>
       </c>
       <c r="R49" t="n">
-        <v>6709914</v>
+        <v>6709933</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5928,7 +5937,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5938,7 +5947,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5965,7 +5974,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129045046</v>
+        <v>129044332</v>
       </c>
       <c r="B50" t="n">
         <v>98659</v>
@@ -6000,10 +6009,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491153</v>
+        <v>491049</v>
       </c>
       <c r="R50" t="n">
-        <v>6710121</v>
+        <v>6709914</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6035,7 +6044,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6045,7 +6054,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6072,7 +6081,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129039883</v>
+        <v>129045046</v>
       </c>
       <c r="B51" t="n">
         <v>98659</v>
@@ -6107,10 +6116,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>491128</v>
+        <v>491153</v>
       </c>
       <c r="R51" t="n">
-        <v>6710150</v>
+        <v>6710121</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6142,7 +6151,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6152,7 +6161,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6179,54 +6188,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129038812</v>
+        <v>129039883</v>
       </c>
       <c r="B52" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490918</v>
+        <v>491128</v>
       </c>
       <c r="R52" t="n">
-        <v>6709933</v>
+        <v>6710150</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6295,50 +6295,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129038692</v>
+        <v>129044552</v>
       </c>
       <c r="B53" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490892</v>
+        <v>491075</v>
       </c>
       <c r="R53" t="n">
-        <v>6709919</v>
+        <v>6709942</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6370,7 +6365,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6380,7 +6375,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6407,7 +6402,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129044552</v>
+        <v>129040369</v>
       </c>
       <c r="B54" t="n">
         <v>98659</v>
@@ -6442,10 +6437,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>491075</v>
+        <v>491194</v>
       </c>
       <c r="R54" t="n">
-        <v>6709942</v>
+        <v>6710167</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6477,7 +6472,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6487,7 +6482,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6514,45 +6509,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129040369</v>
+        <v>129038692</v>
       </c>
       <c r="B55" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>491194</v>
+        <v>490892</v>
       </c>
       <c r="R55" t="n">
-        <v>6710167</v>
+        <v>6709919</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6621,32 +6621,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129037776</v>
+        <v>129038411</v>
       </c>
       <c r="B56" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490952</v>
+        <v>490873</v>
       </c>
       <c r="R56" t="n">
-        <v>6709889</v>
+        <v>6709909</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6728,32 +6728,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129040007</v>
+        <v>129044061</v>
       </c>
       <c r="B57" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>491180</v>
+        <v>491110</v>
       </c>
       <c r="R57" t="n">
-        <v>6710139</v>
+        <v>6709915</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,32 +6835,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129039941</v>
+        <v>129045420</v>
       </c>
       <c r="B58" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491158</v>
+        <v>491009</v>
       </c>
       <c r="R58" t="n">
-        <v>6710160</v>
+        <v>6709991</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,7 +6942,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129038411</v>
+        <v>129038173</v>
       </c>
       <c r="B59" t="n">
         <v>98659</v>
@@ -6970,17 +6970,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490873</v>
+        <v>490877</v>
       </c>
       <c r="R59" t="n">
-        <v>6709909</v>
+        <v>6709889</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7012,7 +7026,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7022,7 +7036,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7049,7 +7063,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129044061</v>
+        <v>129043992</v>
       </c>
       <c r="B60" t="n">
         <v>98659</v>
@@ -7084,10 +7098,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>491110</v>
+        <v>491095</v>
       </c>
       <c r="R60" t="n">
-        <v>6709915</v>
+        <v>6709906</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7119,7 +7133,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7129,7 +7143,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7156,32 +7170,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045420</v>
+        <v>129037776</v>
       </c>
       <c r="B61" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7191,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>491009</v>
+        <v>490952</v>
       </c>
       <c r="R61" t="n">
-        <v>6709991</v>
+        <v>6709889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7226,7 +7240,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7236,7 +7250,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7263,59 +7277,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129038173</v>
+        <v>129040007</v>
       </c>
       <c r="B62" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490877</v>
+        <v>491180</v>
       </c>
       <c r="R62" t="n">
-        <v>6709889</v>
+        <v>6710139</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,32 +7384,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129043992</v>
+        <v>129039941</v>
       </c>
       <c r="B63" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491095</v>
+        <v>491158</v>
       </c>
       <c r="R63" t="n">
-        <v>6709906</v>
+        <v>6710160</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7491,10 +7491,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129037762</v>
+        <v>129042106</v>
       </c>
       <c r="B64" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7502,21 +7502,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490949</v>
+        <v>491327</v>
       </c>
       <c r="R64" t="n">
-        <v>6709885</v>
+        <v>6710067</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7571,7 +7571,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7598,50 +7603,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129039716</v>
+        <v>129037762</v>
       </c>
       <c r="B65" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>491118</v>
+        <v>490949</v>
       </c>
       <c r="R65" t="n">
-        <v>6710111</v>
+        <v>6709885</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7683,12 +7683,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7715,7 +7710,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129044189</v>
+        <v>129039716</v>
       </c>
       <c r="B66" t="n">
         <v>98659</v>
@@ -7744,16 +7739,21 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491025</v>
+        <v>491118</v>
       </c>
       <c r="R66" t="n">
-        <v>6709886</v>
+        <v>6710111</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7795,7 +7795,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7822,7 +7827,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129043659</v>
+        <v>129044189</v>
       </c>
       <c r="B67" t="n">
         <v>98659</v>
@@ -7857,10 +7862,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>491126</v>
+        <v>491025</v>
       </c>
       <c r="R67" t="n">
-        <v>6709977</v>
+        <v>6709886</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7892,7 +7897,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7902,7 +7907,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7929,7 +7934,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129045555</v>
+        <v>129043659</v>
       </c>
       <c r="B68" t="n">
         <v>98659</v>
@@ -7964,10 +7969,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490955</v>
+        <v>491126</v>
       </c>
       <c r="R68" t="n">
-        <v>6709969</v>
+        <v>6709977</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7999,7 +8004,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8009,7 +8014,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8036,7 +8041,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129039681</v>
+        <v>129045555</v>
       </c>
       <c r="B69" t="n">
         <v>98659</v>
@@ -8065,21 +8070,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>491120</v>
+        <v>490955</v>
       </c>
       <c r="R69" t="n">
-        <v>6710111</v>
+        <v>6709969</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8148,7 +8148,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129038944</v>
+        <v>129039681</v>
       </c>
       <c r="B70" t="n">
         <v>98659</v>
@@ -8177,16 +8177,21 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490941</v>
+        <v>491120</v>
       </c>
       <c r="R70" t="n">
-        <v>6709965</v>
+        <v>6710111</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8218,7 +8223,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8228,7 +8233,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8255,32 +8260,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129042106</v>
+        <v>129038944</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8290,10 +8295,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>491327</v>
+        <v>490941</v>
       </c>
       <c r="R71" t="n">
-        <v>6710067</v>
+        <v>6709965</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8325,7 +8330,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8335,12 +8340,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8367,45 +8367,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129042724</v>
+        <v>129038053</v>
       </c>
       <c r="B72" t="n">
-        <v>92855</v>
+        <v>57723</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>491257</v>
+        <v>490886</v>
       </c>
       <c r="R72" t="n">
-        <v>6710085</v>
+        <v>6709872</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,7 +8442,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8447,7 +8452,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8474,10 +8484,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129040356</v>
+        <v>129038223</v>
       </c>
       <c r="B73" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8485,34 +8495,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>491211</v>
+        <v>490878</v>
       </c>
       <c r="R73" t="n">
-        <v>6710165</v>
+        <v>6709889</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8544,7 +8559,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8554,7 +8569,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8581,32 +8596,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129043183</v>
+        <v>129040051</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8616,10 +8631,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>491200</v>
+        <v>491183</v>
       </c>
       <c r="R74" t="n">
-        <v>6709983</v>
+        <v>6710141</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8651,7 +8666,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8661,12 +8676,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8693,50 +8703,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129038053</v>
+        <v>129042724</v>
       </c>
       <c r="B75" t="n">
-        <v>57723</v>
+        <v>92855</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490886</v>
+        <v>491257</v>
       </c>
       <c r="R75" t="n">
-        <v>6709872</v>
+        <v>6710085</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8768,7 +8773,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8778,12 +8783,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:46</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8810,10 +8810,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129038223</v>
+        <v>129040356</v>
       </c>
       <c r="B76" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8821,39 +8821,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490878</v>
+        <v>491211</v>
       </c>
       <c r="R76" t="n">
-        <v>6709889</v>
+        <v>6710165</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8885,7 +8880,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8895,7 +8890,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8922,32 +8917,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129040051</v>
+        <v>129043183</v>
       </c>
       <c r="B77" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8957,10 +8952,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>491183</v>
+        <v>491200</v>
       </c>
       <c r="R77" t="n">
-        <v>6710141</v>
+        <v>6709983</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8992,7 +8987,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9002,7 +8997,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9355,50 +9355,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129038137</v>
+        <v>129039011</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>57723</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490876</v>
+        <v>490936</v>
       </c>
       <c r="R81" t="n">
-        <v>6709883</v>
+        <v>6709979</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9440,7 +9440,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9467,45 +9472,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129039994</v>
+        <v>129042971</v>
       </c>
       <c r="B82" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>491173</v>
+        <v>491193</v>
       </c>
       <c r="R82" t="n">
-        <v>6710152</v>
+        <v>6710074</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9537,7 +9547,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9547,7 +9557,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9686,50 +9701,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129042971</v>
+        <v>129038137</v>
       </c>
       <c r="B84" t="n">
-        <v>57723</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>491193</v>
+        <v>490876</v>
       </c>
       <c r="R84" t="n">
-        <v>6710074</v>
+        <v>6709883</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9761,7 +9776,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9771,12 +9786,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9803,50 +9813,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129039011</v>
+        <v>129039994</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490936</v>
+        <v>491173</v>
       </c>
       <c r="R85" t="n">
-        <v>6709979</v>
+        <v>6710152</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9878,7 +9883,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9888,12 +9893,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9920,45 +9920,54 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129039427</v>
+        <v>129043286</v>
       </c>
       <c r="B86" t="n">
-        <v>98659</v>
+        <v>91546</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>491089</v>
+        <v>491185</v>
       </c>
       <c r="R86" t="n">
-        <v>6710079</v>
+        <v>6710038</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9990,7 +9999,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10000,7 +10009,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10027,59 +10036,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129039369</v>
+        <v>129040273</v>
       </c>
       <c r="B87" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491082</v>
+        <v>491210</v>
       </c>
       <c r="R87" t="n">
-        <v>6710072</v>
+        <v>6710152</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10111,7 +10106,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10121,7 +10116,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10148,45 +10148,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129040090</v>
+        <v>129042243</v>
       </c>
       <c r="B88" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491189</v>
+        <v>491324</v>
       </c>
       <c r="R88" t="n">
-        <v>6710146</v>
+        <v>6710108</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10228,7 +10228,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10255,32 +10260,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129045737</v>
+        <v>129043457</v>
       </c>
       <c r="B89" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10290,10 +10295,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491006</v>
+        <v>491159</v>
       </c>
       <c r="R89" t="n">
-        <v>6709889</v>
+        <v>6709989</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10325,7 +10330,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10335,7 +10340,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10362,54 +10372,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129043286</v>
+        <v>129045737</v>
       </c>
       <c r="B90" t="n">
-        <v>91546</v>
+        <v>92819</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491185</v>
+        <v>491006</v>
       </c>
       <c r="R90" t="n">
-        <v>6710038</v>
+        <v>6709889</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10441,7 +10442,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10451,7 +10452,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10478,32 +10479,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129040273</v>
+        <v>129039427</v>
       </c>
       <c r="B91" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10513,10 +10514,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491210</v>
+        <v>491089</v>
       </c>
       <c r="R91" t="n">
-        <v>6710152</v>
+        <v>6710079</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10548,7 +10549,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10558,12 +10559,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10590,45 +10586,59 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129042243</v>
+        <v>129039369</v>
       </c>
       <c r="B92" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491324</v>
+        <v>491082</v>
       </c>
       <c r="R92" t="n">
-        <v>6710108</v>
+        <v>6710072</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10660,7 +10670,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10670,12 +10680,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10702,32 +10707,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129043457</v>
+        <v>129040090</v>
       </c>
       <c r="B93" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10737,10 +10742,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491159</v>
+        <v>491189</v>
       </c>
       <c r="R93" t="n">
-        <v>6709989</v>
+        <v>6710146</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10772,7 +10777,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10782,12 +10787,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10814,45 +10814,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129041984</v>
+        <v>129043344</v>
       </c>
       <c r="B94" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491353</v>
+        <v>491176</v>
       </c>
       <c r="R94" t="n">
-        <v>6710077</v>
+        <v>6710019</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10921,50 +10921,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129041444</v>
+        <v>129044713</v>
       </c>
       <c r="B95" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491362</v>
+        <v>491086</v>
       </c>
       <c r="R95" t="n">
-        <v>6710150</v>
+        <v>6709974</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10996,7 +10991,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11006,12 +11001,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11038,7 +11028,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129043344</v>
+        <v>129044360</v>
       </c>
       <c r="B96" t="n">
         <v>98659</v>
@@ -11073,10 +11063,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491176</v>
+        <v>491050</v>
       </c>
       <c r="R96" t="n">
-        <v>6710019</v>
+        <v>6709915</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11108,7 +11098,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11118,7 +11108,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11145,7 +11135,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129044713</v>
+        <v>129041232</v>
       </c>
       <c r="B97" t="n">
         <v>98659</v>
@@ -11174,16 +11164,21 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491086</v>
+        <v>491336</v>
       </c>
       <c r="R97" t="n">
-        <v>6709974</v>
+        <v>6710188</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11215,7 +11210,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11225,7 +11220,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11252,7 +11247,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129044360</v>
+        <v>129045097</v>
       </c>
       <c r="B98" t="n">
         <v>98659</v>
@@ -11281,16 +11276,21 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491050</v>
+        <v>491132</v>
       </c>
       <c r="R98" t="n">
-        <v>6709915</v>
+        <v>6710123</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11332,7 +11332,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11359,38 +11364,38 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129041232</v>
+        <v>129041444</v>
       </c>
       <c r="B99" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11399,10 +11404,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491336</v>
+        <v>491362</v>
       </c>
       <c r="R99" t="n">
-        <v>6710188</v>
+        <v>6710150</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11434,7 +11439,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11444,7 +11449,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11471,50 +11481,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129045097</v>
+        <v>129041984</v>
       </c>
       <c r="B100" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491132</v>
+        <v>491353</v>
       </c>
       <c r="R100" t="n">
-        <v>6710123</v>
+        <v>6710077</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11546,7 +11551,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11556,12 +11561,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD100" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129039226</v>
+        <v>129039783</v>
       </c>
       <c r="B2" t="n">
-        <v>92819</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491060</v>
+        <v>491113</v>
       </c>
       <c r="R2" t="n">
-        <v>6710037</v>
+        <v>6710132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129038956</v>
+        <v>129041992</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>91533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490939</v>
+        <v>491353</v>
       </c>
       <c r="R3" t="n">
-        <v>6709966</v>
+        <v>6710077</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129045855</v>
+        <v>129039226</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491030</v>
+        <v>491060</v>
       </c>
       <c r="R4" t="n">
-        <v>6709895</v>
+        <v>6710037</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129041481</v>
+        <v>129038956</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491361</v>
+        <v>490939</v>
       </c>
       <c r="R5" t="n">
-        <v>6710143</v>
+        <v>6709966</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,32 +1113,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129039783</v>
+        <v>129045855</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491113</v>
+        <v>491030</v>
       </c>
       <c r="R6" t="n">
-        <v>6710132</v>
+        <v>6709895</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129041992</v>
+        <v>129041481</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491353</v>
+        <v>491361</v>
       </c>
       <c r="R7" t="n">
-        <v>6710077</v>
+        <v>6710143</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,50 +1439,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129043673</v>
+        <v>129041053</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491125</v>
+        <v>491309</v>
       </c>
       <c r="R9" t="n">
-        <v>6709976</v>
+        <v>6710192</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1524,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,45 +1556,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129043484</v>
+        <v>129043673</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491159</v>
+        <v>491125</v>
       </c>
       <c r="R10" t="n">
-        <v>6709989</v>
+        <v>6709976</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129040595</v>
+        <v>129039748</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491251</v>
+        <v>491113</v>
       </c>
       <c r="R11" t="n">
-        <v>6710146</v>
+        <v>6710132</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,32 +1775,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129045778</v>
+        <v>129040305</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>75157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491010</v>
+        <v>491221</v>
       </c>
       <c r="R12" t="n">
-        <v>6709893</v>
+        <v>6710146</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129041291</v>
+        <v>129043484</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,14 +1913,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491359</v>
+        <v>491159</v>
       </c>
       <c r="R13" t="n">
-        <v>6710158</v>
+        <v>6709988</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,50 +1989,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129041053</v>
+        <v>129040595</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491309</v>
+        <v>491251</v>
       </c>
       <c r="R14" t="n">
-        <v>6710192</v>
+        <v>6710146</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2064,12 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129039748</v>
+        <v>129045778</v>
       </c>
       <c r="B15" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491113</v>
+        <v>491010</v>
       </c>
       <c r="R15" t="n">
-        <v>6710132</v>
+        <v>6709893</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,45 +2203,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129040305</v>
+        <v>129041291</v>
       </c>
       <c r="B16" t="n">
-        <v>75155</v>
+        <v>98669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491221</v>
+        <v>491359</v>
       </c>
       <c r="R16" t="n">
-        <v>6710146</v>
+        <v>6710158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129039360</v>
+        <v>129039950</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>91818</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491080</v>
+        <v>491157</v>
       </c>
       <c r="R17" t="n">
-        <v>6710071</v>
+        <v>6710161</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,12 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,32 +2417,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129043063</v>
+        <v>129039360</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491227</v>
+        <v>491080</v>
       </c>
       <c r="R18" t="n">
-        <v>6710010</v>
+        <v>6710071</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,12 +2497,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På stenblock.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,32 +2529,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129039950</v>
+        <v>129043063</v>
       </c>
       <c r="B19" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491157</v>
+        <v>491227</v>
       </c>
       <c r="R19" t="n">
-        <v>6710161</v>
+        <v>6710010</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,7 +2599,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,7 +2609,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På stenblock.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,50 +2641,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129040720</v>
+        <v>129037863</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>91988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491296</v>
+        <v>490942</v>
       </c>
       <c r="R20" t="n">
-        <v>6710129</v>
+        <v>6709873</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2716,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,7 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,32 +2748,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129044129</v>
+        <v>129040685</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2788,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491049</v>
+        <v>491251</v>
       </c>
       <c r="R21" t="n">
-        <v>6709893</v>
+        <v>6710146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2833,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2860,45 +2855,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129037863</v>
+        <v>129040720</v>
       </c>
       <c r="B22" t="n">
-        <v>91981</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490942</v>
+        <v>491296</v>
       </c>
       <c r="R22" t="n">
-        <v>6709873</v>
+        <v>6710129</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,32 +2967,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129040685</v>
+        <v>129044129</v>
       </c>
       <c r="B23" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491251</v>
+        <v>491049</v>
       </c>
       <c r="R23" t="n">
-        <v>6710146</v>
+        <v>6709893</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,7 +3077,7 @@
         <v>129041584</v>
       </c>
       <c r="B24" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,45 +3181,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129045583</v>
+        <v>129040515</v>
       </c>
       <c r="B25" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490946</v>
+        <v>491251</v>
       </c>
       <c r="R25" t="n">
-        <v>6709935</v>
+        <v>6710165</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,7 +3256,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3266,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,32 +3298,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129043562</v>
+        <v>129045240</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3323,10 +3333,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491129</v>
+        <v>491133</v>
       </c>
       <c r="R26" t="n">
-        <v>6709987</v>
+        <v>6710118</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3358,7 +3368,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3368,7 +3378,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,45 +3405,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129041242</v>
+        <v>129042527</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491341</v>
+        <v>491296</v>
       </c>
       <c r="R27" t="n">
-        <v>6710206</v>
+        <v>6710104</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3465,7 +3484,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3475,7 +3494,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,32 +3521,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129045240</v>
+        <v>129045583</v>
       </c>
       <c r="B28" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3537,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491133</v>
+        <v>490946</v>
       </c>
       <c r="R28" t="n">
-        <v>6710118</v>
+        <v>6709935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3572,7 +3591,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3582,7 +3601,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3609,54 +3628,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129042527</v>
+        <v>129043562</v>
       </c>
       <c r="B29" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491296</v>
+        <v>491129</v>
       </c>
       <c r="R29" t="n">
-        <v>6710104</v>
+        <v>6709987</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3688,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3698,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3725,50 +3735,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129040515</v>
+        <v>129041242</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491251</v>
+        <v>491341</v>
       </c>
       <c r="R30" t="n">
-        <v>6710165</v>
+        <v>6710206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3800,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3810,12 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129044722</v>
+        <v>129044587</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>91818</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491088</v>
+        <v>491075</v>
       </c>
       <c r="R31" t="n">
-        <v>6709977</v>
+        <v>6709943</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,12 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3954,45 +3949,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129040867</v>
+        <v>129040534</v>
       </c>
       <c r="B32" t="n">
-        <v>105722</v>
+        <v>91533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491332</v>
+        <v>491261</v>
       </c>
       <c r="R32" t="n">
-        <v>6710175</v>
+        <v>6710156</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4034,7 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4061,50 +4056,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129039814</v>
+        <v>129044722</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491102</v>
+        <v>491088</v>
       </c>
       <c r="R33" t="n">
-        <v>6710142</v>
+        <v>6709977</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4136,7 +4126,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4146,7 +4136,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4173,45 +4168,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129039825</v>
+        <v>129038111</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491126</v>
+        <v>490874</v>
       </c>
       <c r="R34" t="n">
-        <v>6710148</v>
+        <v>6709885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4253,7 +4253,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4280,59 +4285,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129041725</v>
+        <v>129040867</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>105732</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491375</v>
+        <v>491332</v>
       </c>
       <c r="R35" t="n">
-        <v>6710101</v>
+        <v>6710175</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4364,7 +4355,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4374,7 +4365,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4401,45 +4392,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129044587</v>
+        <v>129039814</v>
       </c>
       <c r="B36" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491075</v>
+        <v>491102</v>
       </c>
       <c r="R36" t="n">
-        <v>6709943</v>
+        <v>6710142</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4471,7 +4467,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4481,7 +4477,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4508,32 +4504,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129040534</v>
+        <v>129039825</v>
       </c>
       <c r="B37" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4543,10 +4539,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491261</v>
+        <v>491126</v>
       </c>
       <c r="R37" t="n">
-        <v>6710156</v>
+        <v>6710148</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,7 +4574,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4588,7 +4584,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4615,50 +4611,59 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129038111</v>
+        <v>129041725</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490874</v>
+        <v>491375</v>
       </c>
       <c r="R38" t="n">
-        <v>6709885</v>
+        <v>6710101</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4690,7 +4695,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4700,12 +4705,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4732,10 +4732,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129045013</v>
+        <v>129040042</v>
       </c>
       <c r="B39" t="n">
-        <v>91526</v>
+        <v>91818</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,21 +4743,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491157</v>
+        <v>491181</v>
       </c>
       <c r="R39" t="n">
-        <v>6710121</v>
+        <v>6710144</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,32 +4839,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129040042</v>
+        <v>129044467</v>
       </c>
       <c r="B40" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491181</v>
+        <v>491036</v>
       </c>
       <c r="R40" t="n">
-        <v>6710144</v>
+        <v>6709945</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4946,10 +4946,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129038104</v>
+        <v>129045013</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>91533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4957,42 +4957,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490880</v>
+        <v>491157</v>
       </c>
       <c r="R41" t="n">
-        <v>6709882</v>
+        <v>6710121</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5024,7 +5016,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5034,12 +5026,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5066,45 +5053,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129044467</v>
+        <v>129038104</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491036</v>
+        <v>490880</v>
       </c>
       <c r="R42" t="n">
-        <v>6709945</v>
+        <v>6709882</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5136,7 +5131,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5146,7 +5141,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5173,10 +5173,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129045330</v>
+        <v>129044319</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>91533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5184,39 +5184,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491085</v>
+        <v>491049</v>
       </c>
       <c r="R43" t="n">
-        <v>6710033</v>
+        <v>6709915</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5248,7 +5243,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5258,12 +5253,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5290,45 +5280,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129044319</v>
+        <v>129041044</v>
       </c>
       <c r="B44" t="n">
-        <v>91526</v>
+        <v>92826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491049</v>
+        <v>491306</v>
       </c>
       <c r="R44" t="n">
-        <v>6709915</v>
+        <v>6710197</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5360,7 +5350,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5370,7 +5360,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,45 +5387,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129041044</v>
+        <v>129045330</v>
       </c>
       <c r="B45" t="n">
-        <v>92819</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491306</v>
+        <v>491085</v>
       </c>
       <c r="R45" t="n">
-        <v>6710197</v>
+        <v>6710033</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5467,7 +5462,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5477,7 +5472,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5504,59 +5504,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129039795</v>
+        <v>129037802</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491106</v>
+        <v>490941</v>
       </c>
       <c r="R46" t="n">
-        <v>6710124</v>
+        <v>6709886</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5588,7 +5574,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5598,7 +5584,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5625,10 +5611,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129042338</v>
+        <v>129039795</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5660,24 +5646,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491335</v>
+        <v>491106</v>
       </c>
       <c r="R47" t="n">
-        <v>6710120</v>
+        <v>6710124</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5709,7 +5695,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5719,12 +5705,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5751,45 +5732,59 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129037802</v>
+        <v>129042338</v>
       </c>
       <c r="B48" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490941</v>
+        <v>491335</v>
       </c>
       <c r="R48" t="n">
-        <v>6709886</v>
+        <v>6710120</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5821,7 +5816,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5831,7 +5826,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5858,54 +5858,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129038812</v>
+        <v>129044332</v>
       </c>
       <c r="B49" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490918</v>
+        <v>491049</v>
       </c>
       <c r="R49" t="n">
-        <v>6709933</v>
+        <v>6709914</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5937,7 +5928,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5947,7 +5938,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5974,10 +5965,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129044332</v>
+        <v>129045046</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6009,10 +6000,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491049</v>
+        <v>491153</v>
       </c>
       <c r="R50" t="n">
-        <v>6709914</v>
+        <v>6710121</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6044,7 +6035,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6054,7 +6045,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6081,10 +6072,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129045046</v>
+        <v>129039883</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,10 +6107,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>491153</v>
+        <v>491128</v>
       </c>
       <c r="R51" t="n">
-        <v>6710121</v>
+        <v>6710150</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6151,7 +6142,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6161,7 +6152,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6188,45 +6179,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129039883</v>
+        <v>129038812</v>
       </c>
       <c r="B52" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>491128</v>
+        <v>490918</v>
       </c>
       <c r="R52" t="n">
-        <v>6710150</v>
+        <v>6709933</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6295,45 +6295,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129044552</v>
+        <v>129038692</v>
       </c>
       <c r="B53" t="n">
-        <v>98659</v>
+        <v>57885</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>491075</v>
+        <v>490892</v>
       </c>
       <c r="R53" t="n">
-        <v>6709942</v>
+        <v>6709919</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6365,7 +6370,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6375,7 +6380,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6402,10 +6407,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129040369</v>
+        <v>129044552</v>
       </c>
       <c r="B54" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6437,10 +6442,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>491194</v>
+        <v>491075</v>
       </c>
       <c r="R54" t="n">
-        <v>6710167</v>
+        <v>6709942</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6472,7 +6477,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6482,7 +6487,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6509,50 +6514,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129038692</v>
+        <v>129040369</v>
       </c>
       <c r="B55" t="n">
-        <v>57883</v>
+        <v>98669</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490892</v>
+        <v>491194</v>
       </c>
       <c r="R55" t="n">
-        <v>6709919</v>
+        <v>6710167</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6624,7 +6624,7 @@
         <v>129038411</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>129044061</v>
       </c>
       <c r="B57" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>129045420</v>
       </c>
       <c r="B58" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>129038173</v>
       </c>
       <c r="B59" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>129043992</v>
       </c>
       <c r="B60" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>129037776</v>
       </c>
       <c r="B61" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7277,10 +7277,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129040007</v>
+        <v>129039941</v>
       </c>
       <c r="B62" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>491180</v>
+        <v>491158</v>
       </c>
       <c r="R62" t="n">
-        <v>6710139</v>
+        <v>6710160</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,10 +7384,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129039941</v>
+        <v>129040007</v>
       </c>
       <c r="B63" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491158</v>
+        <v>491180</v>
       </c>
       <c r="R63" t="n">
-        <v>6710160</v>
+        <v>6710139</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7494,7 +7494,7 @@
         <v>129042106</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7603,45 +7603,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129037762</v>
+        <v>129039716</v>
       </c>
       <c r="B65" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490949</v>
+        <v>491118</v>
       </c>
       <c r="R65" t="n">
-        <v>6709885</v>
+        <v>6710111</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7673,7 +7678,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7683,7 +7688,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7710,10 +7720,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129039716</v>
+        <v>129044189</v>
       </c>
       <c r="B66" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7739,21 +7749,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491118</v>
+        <v>491025</v>
       </c>
       <c r="R66" t="n">
-        <v>6710111</v>
+        <v>6709886</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7785,7 +7790,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7795,12 +7800,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7827,10 +7827,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129044189</v>
+        <v>129043659</v>
       </c>
       <c r="B67" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>491025</v>
+        <v>491126</v>
       </c>
       <c r="R67" t="n">
-        <v>6709886</v>
+        <v>6709977</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7934,10 +7934,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129043659</v>
+        <v>129045555</v>
       </c>
       <c r="B68" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>491126</v>
+        <v>490955</v>
       </c>
       <c r="R68" t="n">
-        <v>6709977</v>
+        <v>6709969</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8041,10 +8041,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129045555</v>
+        <v>129039681</v>
       </c>
       <c r="B69" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8070,16 +8070,21 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490955</v>
+        <v>491120</v>
       </c>
       <c r="R69" t="n">
-        <v>6709969</v>
+        <v>6710111</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8111,7 +8116,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8121,7 +8126,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8148,10 +8153,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129039681</v>
+        <v>129038944</v>
       </c>
       <c r="B70" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8177,21 +8182,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>491120</v>
+        <v>490941</v>
       </c>
       <c r="R70" t="n">
-        <v>6710111</v>
+        <v>6709965</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8260,32 +8260,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129038944</v>
+        <v>129037762</v>
       </c>
       <c r="B71" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8295,10 +8295,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490941</v>
+        <v>490949</v>
       </c>
       <c r="R71" t="n">
-        <v>6709965</v>
+        <v>6709885</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8367,50 +8367,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129038053</v>
+        <v>129042724</v>
       </c>
       <c r="B72" t="n">
-        <v>57723</v>
+        <v>92862</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490886</v>
+        <v>491257</v>
       </c>
       <c r="R72" t="n">
-        <v>6709872</v>
+        <v>6710085</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8442,7 +8437,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8452,12 +8447,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>08:46</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8484,10 +8474,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129038223</v>
+        <v>129040356</v>
       </c>
       <c r="B73" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8495,39 +8485,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490878</v>
+        <v>491211</v>
       </c>
       <c r="R73" t="n">
-        <v>6709889</v>
+        <v>6710165</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8559,7 +8544,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8569,7 +8554,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8596,32 +8581,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129040051</v>
+        <v>129043183</v>
       </c>
       <c r="B74" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8631,10 +8616,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>491183</v>
+        <v>491200</v>
       </c>
       <c r="R74" t="n">
-        <v>6710141</v>
+        <v>6709983</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8666,7 +8651,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8676,7 +8661,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8703,45 +8693,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129042724</v>
+        <v>129038053</v>
       </c>
       <c r="B75" t="n">
-        <v>92855</v>
+        <v>57725</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>491257</v>
+        <v>490886</v>
       </c>
       <c r="R75" t="n">
-        <v>6710085</v>
+        <v>6709872</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8773,7 +8768,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8783,7 +8778,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8810,10 +8810,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129040356</v>
+        <v>129038223</v>
       </c>
       <c r="B76" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8821,34 +8821,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>491211</v>
+        <v>490878</v>
       </c>
       <c r="R76" t="n">
-        <v>6710165</v>
+        <v>6709889</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8880,7 +8885,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8890,7 +8895,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8917,32 +8922,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129043183</v>
+        <v>129040051</v>
       </c>
       <c r="B77" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8952,10 +8957,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>491200</v>
+        <v>491183</v>
       </c>
       <c r="R77" t="n">
-        <v>6709983</v>
+        <v>6710141</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8987,7 +8992,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8997,12 +9002,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9029,10 +9029,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129040173</v>
+        <v>129039515</v>
       </c>
       <c r="B78" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9058,16 +9058,21 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>491201</v>
+        <v>491104</v>
       </c>
       <c r="R78" t="n">
-        <v>6710139</v>
+        <v>6710105</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9099,7 +9104,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9109,7 +9114,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9136,10 +9141,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129039515</v>
+        <v>129043352</v>
       </c>
       <c r="B79" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9165,21 +9170,16 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>491104</v>
+        <v>491188</v>
       </c>
       <c r="R79" t="n">
-        <v>6710105</v>
+        <v>6709988</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9248,10 +9248,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129043352</v>
+        <v>129040173</v>
       </c>
       <c r="B80" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9283,10 +9283,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>491188</v>
+        <v>491201</v>
       </c>
       <c r="R80" t="n">
-        <v>6709988</v>
+        <v>6710139</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9355,10 +9355,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129039011</v>
+        <v>129044818</v>
       </c>
       <c r="B81" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9366,39 +9366,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490936</v>
+        <v>491116</v>
       </c>
       <c r="R81" t="n">
-        <v>6709979</v>
+        <v>6710020</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9430,7 +9425,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9440,12 +9435,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9475,7 +9470,7 @@
         <v>129042971</v>
       </c>
       <c r="B82" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9589,10 +9584,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129044818</v>
+        <v>129039011</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9600,34 +9595,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>491116</v>
+        <v>490936</v>
       </c>
       <c r="R83" t="n">
-        <v>6710020</v>
+        <v>6709979</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9816,7 +9816,7 @@
         <v>129039994</v>
       </c>
       <c r="B85" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9920,54 +9920,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129043286</v>
+        <v>129045737</v>
       </c>
       <c r="B86" t="n">
-        <v>91546</v>
+        <v>92826</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>491185</v>
+        <v>491006</v>
       </c>
       <c r="R86" t="n">
-        <v>6710038</v>
+        <v>6709889</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9999,7 +9990,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10009,7 +10000,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10036,10 +10027,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129040273</v>
+        <v>129043286</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>91553</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10047,34 +10038,43 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491210</v>
+        <v>491185</v>
       </c>
       <c r="R87" t="n">
-        <v>6710152</v>
+        <v>6710038</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10116,12 +10116,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10148,10 +10143,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129042243</v>
+        <v>129040273</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10179,14 +10174,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491324</v>
+        <v>491210</v>
       </c>
       <c r="R88" t="n">
-        <v>6710108</v>
+        <v>6710152</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10218,7 +10213,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10228,12 +10223,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10260,10 +10255,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129043457</v>
+        <v>129042243</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10291,14 +10286,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491159</v>
+        <v>491324</v>
       </c>
       <c r="R89" t="n">
-        <v>6709989</v>
+        <v>6710108</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10330,7 +10325,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10340,7 +10335,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10372,32 +10367,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129045737</v>
+        <v>129043457</v>
       </c>
       <c r="B90" t="n">
-        <v>92819</v>
+        <v>79039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10407,10 +10402,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491006</v>
+        <v>491159</v>
       </c>
       <c r="R90" t="n">
-        <v>6709889</v>
+        <v>6709989</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10442,7 +10437,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10452,7 +10447,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10482,7 +10482,7 @@
         <v>129039427</v>
       </c>
       <c r="B91" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>129039369</v>
       </c>
       <c r="B92" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>129040090</v>
       </c>
       <c r="B93" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10814,10 +10814,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129043344</v>
+        <v>129041232</v>
       </c>
       <c r="B94" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10843,16 +10843,21 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491176</v>
+        <v>491336</v>
       </c>
       <c r="R94" t="n">
-        <v>6710019</v>
+        <v>6710188</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10884,7 +10889,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10894,7 +10899,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10921,10 +10926,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129044713</v>
+        <v>129045097</v>
       </c>
       <c r="B95" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10950,16 +10955,21 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491086</v>
+        <v>491132</v>
       </c>
       <c r="R95" t="n">
-        <v>6709974</v>
+        <v>6710123</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10991,7 +11001,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11001,7 +11011,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11028,45 +11043,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129044360</v>
+        <v>129041984</v>
       </c>
       <c r="B96" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491050</v>
+        <v>491353</v>
       </c>
       <c r="R96" t="n">
-        <v>6709915</v>
+        <v>6710077</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11098,7 +11113,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11108,7 +11123,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11135,38 +11150,38 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129041232</v>
+        <v>129041444</v>
       </c>
       <c r="B97" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11175,10 +11190,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491336</v>
+        <v>491362</v>
       </c>
       <c r="R97" t="n">
-        <v>6710188</v>
+        <v>6710150</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11210,7 +11225,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11220,7 +11235,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11247,10 +11267,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129045097</v>
+        <v>129043344</v>
       </c>
       <c r="B98" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11276,21 +11296,16 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491132</v>
+        <v>491176</v>
       </c>
       <c r="R98" t="n">
-        <v>6710123</v>
+        <v>6710019</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11322,7 +11337,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11332,12 +11347,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11364,50 +11374,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129041444</v>
+        <v>129044713</v>
       </c>
       <c r="B99" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491362</v>
+        <v>491086</v>
       </c>
       <c r="R99" t="n">
-        <v>6710150</v>
+        <v>6709974</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11439,7 +11444,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11449,12 +11454,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11481,45 +11481,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129041984</v>
+        <v>129044360</v>
       </c>
       <c r="B100" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491353</v>
+        <v>491050</v>
       </c>
       <c r="R100" t="n">
-        <v>6710077</v>
+        <v>6709915</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11591,7 +11591,7 @@
         <v>129040149</v>
       </c>
       <c r="B101" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11695,10 +11695,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129038846</v>
+        <v>129045506</v>
       </c>
       <c r="B102" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11724,21 +11724,24 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490903</v>
+        <v>490975</v>
       </c>
       <c r="R102" t="n">
-        <v>6709932</v>
+        <v>6709983</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11770,7 +11773,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11780,12 +11783,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Bohål i gran, på ca 2m.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11812,10 +11815,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129045506</v>
+        <v>129038846</v>
       </c>
       <c r="B103" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11841,24 +11844,21 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490975</v>
+        <v>490903</v>
       </c>
       <c r="R103" t="n">
-        <v>6709983</v>
+        <v>6709932</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Bohål i gran, på ca 2m.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11935,7 +11935,7 @@
         <v>129044617</v>
       </c>
       <c r="B104" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>129043760</v>
       </c>
       <c r="B105" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12146,32 +12146,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129039623</v>
+        <v>129042566</v>
       </c>
       <c r="B106" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12181,10 +12181,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491117</v>
+        <v>491288</v>
       </c>
       <c r="R106" t="n">
-        <v>6710091</v>
+        <v>6710104</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12253,32 +12253,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129039646</v>
+        <v>129044243</v>
       </c>
       <c r="B107" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491117</v>
+        <v>491026</v>
       </c>
       <c r="R107" t="n">
-        <v>6710091</v>
+        <v>6709889</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12333,12 +12333,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12365,54 +12360,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129039218</v>
+        <v>129039646</v>
       </c>
       <c r="B108" t="n">
-        <v>92819</v>
+        <v>91818</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491054</v>
+        <v>491117</v>
       </c>
       <c r="R108" t="n">
-        <v>6710041</v>
+        <v>6710091</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12444,7 +12430,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12454,7 +12440,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12481,45 +12472,54 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129042566</v>
+        <v>129039218</v>
       </c>
       <c r="B109" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491288</v>
+        <v>491054</v>
       </c>
       <c r="R109" t="n">
-        <v>6710104</v>
+        <v>6710041</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12588,32 +12588,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129044243</v>
+        <v>129039623</v>
       </c>
       <c r="B110" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491026</v>
+        <v>491117</v>
       </c>
       <c r="R110" t="n">
-        <v>6709889</v>
+        <v>6710091</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -1439,50 +1439,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129041053</v>
+        <v>129040305</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>75157</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491309</v>
+        <v>491221</v>
       </c>
       <c r="R9" t="n">
-        <v>6710192</v>
+        <v>6710146</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,12 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,50 +1546,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129043673</v>
+        <v>129041053</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491125</v>
+        <v>491309</v>
       </c>
       <c r="R10" t="n">
-        <v>6709976</v>
+        <v>6710192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1631,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129039748</v>
+        <v>129043673</v>
       </c>
       <c r="B11" t="n">
-        <v>92826</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,34 +1674,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491113</v>
+        <v>491125</v>
       </c>
       <c r="R11" t="n">
-        <v>6710132</v>
+        <v>6709976</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,32 +1775,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129040305</v>
+        <v>129043484</v>
       </c>
       <c r="B12" t="n">
-        <v>75157</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491221</v>
+        <v>491159</v>
       </c>
       <c r="R12" t="n">
-        <v>6710146</v>
+        <v>6709988</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,7 +1882,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129043484</v>
+        <v>129040595</v>
       </c>
       <c r="B13" t="n">
         <v>98669</v>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491159</v>
+        <v>491251</v>
       </c>
       <c r="R13" t="n">
-        <v>6709988</v>
+        <v>6710146</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129040595</v>
+        <v>129045778</v>
       </c>
       <c r="B14" t="n">
         <v>98669</v>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491251</v>
+        <v>491010</v>
       </c>
       <c r="R14" t="n">
-        <v>6710146</v>
+        <v>6709893</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,7 +2096,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129045778</v>
+        <v>129041291</v>
       </c>
       <c r="B15" t="n">
         <v>98669</v>
@@ -2127,14 +2127,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491010</v>
+        <v>491359</v>
       </c>
       <c r="R15" t="n">
-        <v>6709893</v>
+        <v>6710158</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,45 +2203,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129041291</v>
+        <v>129039748</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>92826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491359</v>
+        <v>491113</v>
       </c>
       <c r="R16" t="n">
-        <v>6710158</v>
+        <v>6710132</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129040515</v>
+        <v>129045240</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>91818</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,39 +3192,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491251</v>
+        <v>491133</v>
       </c>
       <c r="R25" t="n">
-        <v>6710165</v>
+        <v>6710118</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3266,12 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,45 +3288,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129045240</v>
+        <v>129042527</v>
       </c>
       <c r="B26" t="n">
-        <v>91818</v>
+        <v>92826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491133</v>
+        <v>491296</v>
       </c>
       <c r="R26" t="n">
-        <v>6710118</v>
+        <v>6710104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3368,7 +3367,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3378,7 +3377,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3405,42 +3404,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129042527</v>
+        <v>129040515</v>
       </c>
       <c r="B27" t="n">
-        <v>92826</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3449,10 +3444,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491296</v>
+        <v>491251</v>
       </c>
       <c r="R27" t="n">
-        <v>6710104</v>
+        <v>6710165</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3484,7 +3479,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3494,7 +3489,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4168,50 +4168,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129038111</v>
+        <v>129040867</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>105732</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490874</v>
+        <v>491332</v>
       </c>
       <c r="R34" t="n">
-        <v>6709885</v>
+        <v>6710175</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4243,7 +4238,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4253,12 +4248,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4285,45 +4275,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129040867</v>
+        <v>129039814</v>
       </c>
       <c r="B35" t="n">
-        <v>105732</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491332</v>
+        <v>491102</v>
       </c>
       <c r="R35" t="n">
-        <v>6710175</v>
+        <v>6710142</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4355,7 +4350,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4365,7 +4360,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,7 +4387,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129039814</v>
+        <v>129039825</v>
       </c>
       <c r="B36" t="n">
         <v>98669</v>
@@ -4421,21 +4416,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491102</v>
+        <v>491126</v>
       </c>
       <c r="R36" t="n">
-        <v>6710142</v>
+        <v>6710148</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4467,7 +4457,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4477,7 +4467,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4504,7 +4494,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129039825</v>
+        <v>129041725</v>
       </c>
       <c r="B37" t="n">
         <v>98669</v>
@@ -4532,17 +4522,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491126</v>
+        <v>491375</v>
       </c>
       <c r="R37" t="n">
-        <v>6710148</v>
+        <v>6710101</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4574,7 +4578,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4584,7 +4588,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4611,59 +4615,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129041725</v>
+        <v>129038111</v>
       </c>
       <c r="B38" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491375</v>
+        <v>490874</v>
       </c>
       <c r="R38" t="n">
-        <v>6710101</v>
+        <v>6709885</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,7 +4690,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4705,7 +4700,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6621,32 +6621,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129038411</v>
+        <v>129037776</v>
       </c>
       <c r="B56" t="n">
-        <v>98669</v>
+        <v>91818</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490873</v>
+        <v>490952</v>
       </c>
       <c r="R56" t="n">
-        <v>6709909</v>
+        <v>6709889</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6728,32 +6728,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129044061</v>
+        <v>129039941</v>
       </c>
       <c r="B57" t="n">
-        <v>98669</v>
+        <v>91533</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>491110</v>
+        <v>491158</v>
       </c>
       <c r="R57" t="n">
-        <v>6709915</v>
+        <v>6710160</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,32 +6835,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129045420</v>
+        <v>129040007</v>
       </c>
       <c r="B58" t="n">
-        <v>98669</v>
+        <v>91533</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491009</v>
+        <v>491180</v>
       </c>
       <c r="R58" t="n">
-        <v>6709991</v>
+        <v>6710139</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,7 +6942,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129038173</v>
+        <v>129038411</v>
       </c>
       <c r="B59" t="n">
         <v>98669</v>
@@ -6970,31 +6970,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490877</v>
+        <v>490873</v>
       </c>
       <c r="R59" t="n">
-        <v>6709889</v>
+        <v>6709909</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7026,7 +7012,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7036,7 +7022,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7063,7 +7049,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129043992</v>
+        <v>129044061</v>
       </c>
       <c r="B60" t="n">
         <v>98669</v>
@@ -7098,10 +7084,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>491095</v>
+        <v>491110</v>
       </c>
       <c r="R60" t="n">
-        <v>6709906</v>
+        <v>6709915</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7133,7 +7119,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7143,7 +7129,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,32 +7156,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129037776</v>
+        <v>129045420</v>
       </c>
       <c r="B61" t="n">
-        <v>91818</v>
+        <v>98669</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7205,10 +7191,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>490952</v>
+        <v>491009</v>
       </c>
       <c r="R61" t="n">
-        <v>6709889</v>
+        <v>6709991</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7240,7 +7226,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7250,7 +7236,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7277,45 +7263,59 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129039941</v>
+        <v>129038173</v>
       </c>
       <c r="B62" t="n">
-        <v>91533</v>
+        <v>98669</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>491158</v>
+        <v>490877</v>
       </c>
       <c r="R62" t="n">
-        <v>6710160</v>
+        <v>6709889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,32 +7384,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129040007</v>
+        <v>129043992</v>
       </c>
       <c r="B63" t="n">
-        <v>91533</v>
+        <v>98669</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491180</v>
+        <v>491095</v>
       </c>
       <c r="R63" t="n">
-        <v>6710139</v>
+        <v>6709906</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9029,7 +9029,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129039515</v>
+        <v>129040173</v>
       </c>
       <c r="B78" t="n">
         <v>98669</v>
@@ -9058,21 +9058,16 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>491104</v>
+        <v>491201</v>
       </c>
       <c r="R78" t="n">
-        <v>6710105</v>
+        <v>6710139</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9104,7 +9099,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9114,7 +9109,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9141,7 +9136,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129043352</v>
+        <v>129039515</v>
       </c>
       <c r="B79" t="n">
         <v>98669</v>
@@ -9170,16 +9165,21 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>491188</v>
+        <v>491104</v>
       </c>
       <c r="R79" t="n">
-        <v>6709988</v>
+        <v>6710105</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9248,7 +9248,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129040173</v>
+        <v>129043352</v>
       </c>
       <c r="B80" t="n">
         <v>98669</v>
@@ -9283,10 +9283,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>491201</v>
+        <v>491188</v>
       </c>
       <c r="R80" t="n">
-        <v>6710139</v>
+        <v>6709988</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9467,50 +9467,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129042971</v>
+        <v>129039994</v>
       </c>
       <c r="B82" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>491193</v>
+        <v>491173</v>
       </c>
       <c r="R82" t="n">
-        <v>6710074</v>
+        <v>6710152</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9542,7 +9537,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9552,12 +9547,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9584,7 +9574,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129039011</v>
+        <v>129042971</v>
       </c>
       <c r="B83" t="n">
         <v>57725</v>
@@ -9624,10 +9614,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490936</v>
+        <v>491193</v>
       </c>
       <c r="R83" t="n">
-        <v>6709979</v>
+        <v>6710074</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9659,7 +9649,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9669,7 +9659,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9701,50 +9691,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129038137</v>
+        <v>129039011</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>57725</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490876</v>
+        <v>490936</v>
       </c>
       <c r="R84" t="n">
-        <v>6709883</v>
+        <v>6709979</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9776,7 +9766,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9786,7 +9776,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9813,45 +9808,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129039994</v>
+        <v>129038137</v>
       </c>
       <c r="B85" t="n">
-        <v>98669</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>491173</v>
+        <v>490876</v>
       </c>
       <c r="R85" t="n">
-        <v>6710152</v>
+        <v>6709883</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129039783</v>
+        <v>129039226</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>92833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491113</v>
+        <v>491060</v>
       </c>
       <c r="R2" t="n">
-        <v>6710132</v>
+        <v>6710037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129041992</v>
+        <v>129039783</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491353</v>
+        <v>491113</v>
       </c>
       <c r="R3" t="n">
-        <v>6710077</v>
+        <v>6710132</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129039226</v>
+        <v>129041992</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491060</v>
+        <v>491353</v>
       </c>
       <c r="R4" t="n">
-        <v>6710037</v>
+        <v>6710077</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1116,7 +1116,7 @@
         <v>129045855</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129041481</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1775,32 +1775,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129043484</v>
+        <v>129039748</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>92833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491159</v>
+        <v>491113</v>
       </c>
       <c r="R12" t="n">
-        <v>6709988</v>
+        <v>6710132</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129040595</v>
+        <v>129043484</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491251</v>
+        <v>491159</v>
       </c>
       <c r="R13" t="n">
-        <v>6710146</v>
+        <v>6709989</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129045778</v>
+        <v>129040595</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491010</v>
+        <v>491251</v>
       </c>
       <c r="R14" t="n">
-        <v>6709893</v>
+        <v>6710146</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129041291</v>
+        <v>129045778</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,14 +2127,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491359</v>
+        <v>491010</v>
       </c>
       <c r="R15" t="n">
-        <v>6710158</v>
+        <v>6709893</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,45 +2203,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129039748</v>
+        <v>129041291</v>
       </c>
       <c r="B16" t="n">
-        <v>92826</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491113</v>
+        <v>491359</v>
       </c>
       <c r="R16" t="n">
-        <v>6710132</v>
+        <v>6710158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,32 +2310,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129039950</v>
+        <v>129043063</v>
       </c>
       <c r="B17" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491157</v>
+        <v>491227</v>
       </c>
       <c r="R17" t="n">
-        <v>6710161</v>
+        <v>6710010</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På stenblock.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,32 +2534,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129043063</v>
+        <v>129039950</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>91825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2564,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491227</v>
+        <v>491157</v>
       </c>
       <c r="R19" t="n">
-        <v>6710010</v>
+        <v>6710161</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2609,12 +2614,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På stenblock.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,45 +2641,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129037863</v>
+        <v>129041584</v>
       </c>
       <c r="B20" t="n">
-        <v>91988</v>
+        <v>91560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490942</v>
+        <v>491362</v>
       </c>
       <c r="R20" t="n">
-        <v>6709873</v>
+        <v>6710143</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2751,7 +2751,7 @@
         <v>129040685</v>
       </c>
       <c r="B21" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,50 +2855,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129040720</v>
+        <v>129037863</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>91995</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491296</v>
+        <v>490942</v>
       </c>
       <c r="R22" t="n">
-        <v>6710129</v>
+        <v>6709873</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,45 +2962,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129044129</v>
+        <v>129040720</v>
       </c>
       <c r="B23" t="n">
-        <v>98669</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491049</v>
+        <v>491296</v>
       </c>
       <c r="R23" t="n">
-        <v>6709893</v>
+        <v>6710129</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,45 +3074,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129041584</v>
+        <v>129044129</v>
       </c>
       <c r="B24" t="n">
-        <v>91553</v>
+        <v>98676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491362</v>
+        <v>491049</v>
       </c>
       <c r="R24" t="n">
-        <v>6710143</v>
+        <v>6709893</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3184,7 +3184,7 @@
         <v>129045240</v>
       </c>
       <c r="B25" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3288,42 +3288,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129042527</v>
+        <v>129040515</v>
       </c>
       <c r="B26" t="n">
-        <v>92826</v>
+        <v>57725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3332,10 +3328,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491296</v>
+        <v>491251</v>
       </c>
       <c r="R26" t="n">
-        <v>6710104</v>
+        <v>6710165</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3363,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3377,7 +3373,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3404,38 +3405,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129040515</v>
+        <v>129042527</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>92833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3444,10 +3449,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491251</v>
+        <v>491296</v>
       </c>
       <c r="R27" t="n">
-        <v>6710165</v>
+        <v>6710104</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3479,7 +3484,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3489,12 +3494,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,7 +3524,7 @@
         <v>129045583</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>129043562</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>129041242</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>129044587</v>
       </c>
       <c r="B31" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>129040534</v>
       </c>
       <c r="B32" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,45 +4056,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129044722</v>
+        <v>129040867</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>105739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491088</v>
+        <v>491332</v>
       </c>
       <c r="R33" t="n">
-        <v>6709977</v>
+        <v>6710175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4136,12 +4136,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4168,45 +4163,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129040867</v>
+        <v>129039814</v>
       </c>
       <c r="B34" t="n">
-        <v>105732</v>
+        <v>98676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491332</v>
+        <v>491102</v>
       </c>
       <c r="R34" t="n">
-        <v>6710175</v>
+        <v>6710142</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4275,10 +4275,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129039814</v>
+        <v>129039825</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4304,21 +4304,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491102</v>
+        <v>491126</v>
       </c>
       <c r="R35" t="n">
-        <v>6710142</v>
+        <v>6710148</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4350,7 +4345,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4360,7 +4355,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4387,10 +4382,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129039825</v>
+        <v>129041725</v>
       </c>
       <c r="B36" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4415,17 +4410,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491126</v>
+        <v>491375</v>
       </c>
       <c r="R36" t="n">
-        <v>6710148</v>
+        <v>6710101</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4457,7 +4466,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4467,7 +4476,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4494,59 +4503,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129041725</v>
+        <v>129044722</v>
       </c>
       <c r="B37" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491375</v>
+        <v>491088</v>
       </c>
       <c r="R37" t="n">
-        <v>6710101</v>
+        <v>6709977</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,7 +4573,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4588,7 +4583,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4732,10 +4732,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129040042</v>
+        <v>129045013</v>
       </c>
       <c r="B39" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,21 +4743,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491181</v>
+        <v>491157</v>
       </c>
       <c r="R39" t="n">
-        <v>6710144</v>
+        <v>6710121</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,32 +4839,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129044467</v>
+        <v>129040042</v>
       </c>
       <c r="B40" t="n">
-        <v>98669</v>
+        <v>91825</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491036</v>
+        <v>491181</v>
       </c>
       <c r="R40" t="n">
-        <v>6709945</v>
+        <v>6710144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4946,10 +4946,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129045013</v>
+        <v>129038104</v>
       </c>
       <c r="B41" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4957,34 +4957,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491157</v>
+        <v>490880</v>
       </c>
       <c r="R41" t="n">
-        <v>6710121</v>
+        <v>6709882</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5016,7 +5024,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5026,7 +5034,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5053,53 +5066,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129038104</v>
+        <v>129044467</v>
       </c>
       <c r="B42" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490880</v>
+        <v>491036</v>
       </c>
       <c r="R42" t="n">
-        <v>6709882</v>
+        <v>6709945</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5131,7 +5136,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5141,12 +5146,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5173,45 +5173,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129044319</v>
+        <v>129041044</v>
       </c>
       <c r="B43" t="n">
-        <v>91533</v>
+        <v>92833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491049</v>
+        <v>491306</v>
       </c>
       <c r="R43" t="n">
-        <v>6709915</v>
+        <v>6710197</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,45 +5280,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129041044</v>
+        <v>129044319</v>
       </c>
       <c r="B44" t="n">
-        <v>92826</v>
+        <v>91540</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491306</v>
+        <v>491049</v>
       </c>
       <c r="R44" t="n">
-        <v>6710197</v>
+        <v>6709915</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5507,7 +5507,7 @@
         <v>129037802</v>
       </c>
       <c r="B46" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>129039795</v>
       </c>
       <c r="B47" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>129042338</v>
       </c>
       <c r="B48" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5858,45 +5858,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129044332</v>
+        <v>129038812</v>
       </c>
       <c r="B49" t="n">
-        <v>98669</v>
+        <v>92833</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491049</v>
+        <v>490918</v>
       </c>
       <c r="R49" t="n">
-        <v>6709914</v>
+        <v>6709933</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5928,7 +5937,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5938,7 +5947,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5965,10 +5974,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129045046</v>
+        <v>129044332</v>
       </c>
       <c r="B50" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6000,10 +6009,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491153</v>
+        <v>491049</v>
       </c>
       <c r="R50" t="n">
-        <v>6710121</v>
+        <v>6709914</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6035,7 +6044,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6045,7 +6054,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6072,10 +6081,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129039883</v>
+        <v>129045046</v>
       </c>
       <c r="B51" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6107,10 +6116,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>491128</v>
+        <v>491153</v>
       </c>
       <c r="R51" t="n">
-        <v>6710150</v>
+        <v>6710121</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6142,7 +6151,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6152,7 +6161,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6179,54 +6188,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129038812</v>
+        <v>129039883</v>
       </c>
       <c r="B52" t="n">
-        <v>92826</v>
+        <v>98676</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490918</v>
+        <v>491128</v>
       </c>
       <c r="R52" t="n">
-        <v>6709933</v>
+        <v>6710150</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6295,50 +6295,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129038692</v>
+        <v>129040369</v>
       </c>
       <c r="B53" t="n">
-        <v>57885</v>
+        <v>98676</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490892</v>
+        <v>491194</v>
       </c>
       <c r="R53" t="n">
-        <v>6709919</v>
+        <v>6710167</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6370,7 +6365,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6380,7 +6375,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6407,45 +6402,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129044552</v>
+        <v>129038692</v>
       </c>
       <c r="B54" t="n">
-        <v>98669</v>
+        <v>57885</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>491075</v>
+        <v>490892</v>
       </c>
       <c r="R54" t="n">
-        <v>6709942</v>
+        <v>6709919</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6514,10 +6514,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129040369</v>
+        <v>129044552</v>
       </c>
       <c r="B55" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>491194</v>
+        <v>491075</v>
       </c>
       <c r="R55" t="n">
-        <v>6710167</v>
+        <v>6709942</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6624,7 +6624,7 @@
         <v>129037776</v>
       </c>
       <c r="B56" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6728,32 +6728,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129039941</v>
+        <v>129038411</v>
       </c>
       <c r="B57" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>491158</v>
+        <v>490873</v>
       </c>
       <c r="R57" t="n">
-        <v>6710160</v>
+        <v>6709909</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,32 +6835,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129040007</v>
+        <v>129044061</v>
       </c>
       <c r="B58" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491180</v>
+        <v>491110</v>
       </c>
       <c r="R58" t="n">
-        <v>6710139</v>
+        <v>6709915</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,10 +6942,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129038411</v>
+        <v>129045420</v>
       </c>
       <c r="B59" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490873</v>
+        <v>491009</v>
       </c>
       <c r="R59" t="n">
-        <v>6709909</v>
+        <v>6709991</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7049,10 +7049,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129044061</v>
+        <v>129038173</v>
       </c>
       <c r="B60" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7077,17 +7077,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>491110</v>
+        <v>490877</v>
       </c>
       <c r="R60" t="n">
-        <v>6709915</v>
+        <v>6709889</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7119,7 +7133,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7129,7 +7143,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7156,10 +7170,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045420</v>
+        <v>129043992</v>
       </c>
       <c r="B61" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7191,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>491009</v>
+        <v>491095</v>
       </c>
       <c r="R61" t="n">
-        <v>6709991</v>
+        <v>6709906</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7226,7 +7240,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7236,7 +7250,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7263,59 +7277,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129038173</v>
+        <v>129040007</v>
       </c>
       <c r="B62" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490877</v>
+        <v>491180</v>
       </c>
       <c r="R62" t="n">
-        <v>6709889</v>
+        <v>6710139</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,32 +7384,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129043992</v>
+        <v>129039941</v>
       </c>
       <c r="B63" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491095</v>
+        <v>491158</v>
       </c>
       <c r="R63" t="n">
-        <v>6709906</v>
+        <v>6710160</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7603,50 +7603,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129039716</v>
+        <v>129037762</v>
       </c>
       <c r="B65" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>491118</v>
+        <v>490949</v>
       </c>
       <c r="R65" t="n">
-        <v>6710111</v>
+        <v>6709885</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7678,7 +7673,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7688,12 +7683,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7720,10 +7710,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129044189</v>
+        <v>129039716</v>
       </c>
       <c r="B66" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7749,16 +7739,21 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491025</v>
+        <v>491118</v>
       </c>
       <c r="R66" t="n">
-        <v>6709886</v>
+        <v>6710111</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7790,7 +7785,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7800,7 +7795,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7827,10 +7827,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129043659</v>
+        <v>129044189</v>
       </c>
       <c r="B67" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>491126</v>
+        <v>491025</v>
       </c>
       <c r="R67" t="n">
-        <v>6709977</v>
+        <v>6709886</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7934,10 +7934,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129045555</v>
+        <v>129043659</v>
       </c>
       <c r="B68" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490955</v>
+        <v>491126</v>
       </c>
       <c r="R68" t="n">
-        <v>6709969</v>
+        <v>6709977</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8041,10 +8041,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129039681</v>
+        <v>129045555</v>
       </c>
       <c r="B69" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8070,21 +8070,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>491120</v>
+        <v>490955</v>
       </c>
       <c r="R69" t="n">
-        <v>6710111</v>
+        <v>6709969</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8116,7 +8111,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8126,7 +8121,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8153,10 +8148,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129038944</v>
+        <v>129039681</v>
       </c>
       <c r="B70" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8182,16 +8177,21 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490941</v>
+        <v>491120</v>
       </c>
       <c r="R70" t="n">
-        <v>6709965</v>
+        <v>6710111</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8260,32 +8260,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129037762</v>
+        <v>129038944</v>
       </c>
       <c r="B71" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8295,10 +8295,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490949</v>
+        <v>490941</v>
       </c>
       <c r="R71" t="n">
-        <v>6709885</v>
+        <v>6709965</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8367,32 +8367,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129042724</v>
+        <v>129040356</v>
       </c>
       <c r="B72" t="n">
-        <v>92862</v>
+        <v>79039</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>491257</v>
+        <v>491211</v>
       </c>
       <c r="R72" t="n">
-        <v>6710085</v>
+        <v>6710165</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8474,7 +8474,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129040356</v>
+        <v>129043183</v>
       </c>
       <c r="B73" t="n">
         <v>79039</v>
@@ -8509,10 +8509,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>491211</v>
+        <v>491200</v>
       </c>
       <c r="R73" t="n">
-        <v>6710165</v>
+        <v>6709983</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8554,7 +8554,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8581,32 +8586,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129043183</v>
+        <v>129042724</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>92869</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8616,10 +8621,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>491200</v>
+        <v>491257</v>
       </c>
       <c r="R74" t="n">
-        <v>6709983</v>
+        <v>6710085</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8651,7 +8656,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8661,12 +8666,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8925,7 +8925,7 @@
         <v>129040051</v>
       </c>
       <c r="B77" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>129040173</v>
       </c>
       <c r="B78" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>129039515</v>
       </c>
       <c r="B79" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>129043352</v>
       </c>
       <c r="B80" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9467,45 +9467,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129039994</v>
+        <v>129042971</v>
       </c>
       <c r="B82" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>491173</v>
+        <v>491193</v>
       </c>
       <c r="R82" t="n">
-        <v>6710152</v>
+        <v>6710074</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9537,7 +9542,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9547,7 +9552,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9574,7 +9584,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129042971</v>
+        <v>129039011</v>
       </c>
       <c r="B83" t="n">
         <v>57725</v>
@@ -9614,10 +9624,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>491193</v>
+        <v>490936</v>
       </c>
       <c r="R83" t="n">
-        <v>6710074</v>
+        <v>6709979</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9649,7 +9659,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9659,7 +9669,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9691,50 +9701,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129039011</v>
+        <v>129038137</v>
       </c>
       <c r="B84" t="n">
-        <v>57725</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490936</v>
+        <v>490876</v>
       </c>
       <c r="R84" t="n">
-        <v>6709979</v>
+        <v>6709883</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9766,7 +9776,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9776,12 +9786,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9808,50 +9813,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129038137</v>
+        <v>129039994</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>98676</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490876</v>
+        <v>491173</v>
       </c>
       <c r="R85" t="n">
-        <v>6709883</v>
+        <v>6710152</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9923,7 +9923,7 @@
         <v>129045737</v>
       </c>
       <c r="B86" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>129043286</v>
       </c>
       <c r="B87" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10143,32 +10143,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129040273</v>
+        <v>129039427</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10178,10 +10178,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491210</v>
+        <v>491089</v>
       </c>
       <c r="R88" t="n">
-        <v>6710152</v>
+        <v>6710079</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10223,12 +10223,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10255,7 +10250,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129042243</v>
+        <v>129040273</v>
       </c>
       <c r="B89" t="n">
         <v>79039</v>
@@ -10286,14 +10281,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491324</v>
+        <v>491210</v>
       </c>
       <c r="R89" t="n">
-        <v>6710108</v>
+        <v>6710152</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10325,7 +10320,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10335,12 +10330,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10367,7 +10362,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129043457</v>
+        <v>129042243</v>
       </c>
       <c r="B90" t="n">
         <v>79039</v>
@@ -10398,14 +10393,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491159</v>
+        <v>491324</v>
       </c>
       <c r="R90" t="n">
-        <v>6709989</v>
+        <v>6710108</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10437,7 +10432,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10447,7 +10442,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10479,32 +10474,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129039427</v>
+        <v>129043457</v>
       </c>
       <c r="B91" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10514,10 +10509,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491089</v>
+        <v>491159</v>
       </c>
       <c r="R91" t="n">
-        <v>6710079</v>
+        <v>6709989</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10549,7 +10544,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10559,7 +10554,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10589,7 +10589,7 @@
         <v>129039369</v>
       </c>
       <c r="B92" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>129040090</v>
       </c>
       <c r="B93" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10814,50 +10814,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129041232</v>
+        <v>129041984</v>
       </c>
       <c r="B94" t="n">
-        <v>98669</v>
+        <v>91825</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491336</v>
+        <v>491353</v>
       </c>
       <c r="R94" t="n">
-        <v>6710188</v>
+        <v>6710077</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10889,7 +10884,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10899,7 +10894,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10926,50 +10921,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129045097</v>
+        <v>129041444</v>
       </c>
       <c r="B95" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491132</v>
+        <v>491362</v>
       </c>
       <c r="R95" t="n">
-        <v>6710123</v>
+        <v>6710150</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11001,7 +10996,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11011,12 +11006,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11043,45 +11038,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129041984</v>
+        <v>129043344</v>
       </c>
       <c r="B96" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491353</v>
+        <v>491176</v>
       </c>
       <c r="R96" t="n">
-        <v>6710077</v>
+        <v>6710019</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11113,7 +11108,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11123,7 +11118,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11150,50 +11145,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129041444</v>
+        <v>129044713</v>
       </c>
       <c r="B97" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491362</v>
+        <v>491086</v>
       </c>
       <c r="R97" t="n">
-        <v>6710150</v>
+        <v>6709974</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11225,7 +11215,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11235,12 +11225,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11267,10 +11252,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129043344</v>
+        <v>129044360</v>
       </c>
       <c r="B98" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11302,10 +11287,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491176</v>
+        <v>491050</v>
       </c>
       <c r="R98" t="n">
-        <v>6710019</v>
+        <v>6709915</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11337,7 +11322,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11347,7 +11332,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11374,10 +11359,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129044713</v>
+        <v>129041232</v>
       </c>
       <c r="B99" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11403,16 +11388,21 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491086</v>
+        <v>491336</v>
       </c>
       <c r="R99" t="n">
-        <v>6709974</v>
+        <v>6710188</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11444,7 +11434,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11454,7 +11444,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11481,10 +11471,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129044360</v>
+        <v>129045097</v>
       </c>
       <c r="B100" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11510,16 +11500,21 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491050</v>
+        <v>491132</v>
       </c>
       <c r="R100" t="n">
-        <v>6709915</v>
+        <v>6710123</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11551,7 +11546,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11561,7 +11556,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11695,7 +11695,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129045506</v>
+        <v>129038846</v>
       </c>
       <c r="B102" t="n">
         <v>57725</v>
@@ -11724,24 +11724,21 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490975</v>
+        <v>490903</v>
       </c>
       <c r="R102" t="n">
-        <v>6709983</v>
+        <v>6709932</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11773,7 +11770,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11783,12 +11780,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Bohål i gran, på ca 2m.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11815,7 +11812,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129038846</v>
+        <v>129045506</v>
       </c>
       <c r="B103" t="n">
         <v>57725</v>
@@ -11844,21 +11841,24 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490903</v>
+        <v>490975</v>
       </c>
       <c r="R103" t="n">
-        <v>6709932</v>
+        <v>6709983</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Bohål i gran, på ca 2m.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11935,7 +11935,7 @@
         <v>129044617</v>
       </c>
       <c r="B104" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>129043760</v>
       </c>
       <c r="B105" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12146,32 +12146,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129042566</v>
+        <v>129039623</v>
       </c>
       <c r="B106" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12181,10 +12181,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491288</v>
+        <v>491117</v>
       </c>
       <c r="R106" t="n">
-        <v>6710104</v>
+        <v>6710091</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12253,32 +12253,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129044243</v>
+        <v>129039646</v>
       </c>
       <c r="B107" t="n">
-        <v>98669</v>
+        <v>91825</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491026</v>
+        <v>491117</v>
       </c>
       <c r="R107" t="n">
-        <v>6709889</v>
+        <v>6710091</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12333,7 +12333,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12360,45 +12365,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129039646</v>
+        <v>129039218</v>
       </c>
       <c r="B108" t="n">
-        <v>91818</v>
+        <v>92833</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491117</v>
+        <v>491054</v>
       </c>
       <c r="R108" t="n">
-        <v>6710091</v>
+        <v>6710041</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12430,7 +12444,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12440,12 +12454,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12472,54 +12481,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129039218</v>
+        <v>129042566</v>
       </c>
       <c r="B109" t="n">
-        <v>92826</v>
+        <v>98676</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491054</v>
+        <v>491288</v>
       </c>
       <c r="R109" t="n">
-        <v>6710041</v>
+        <v>6710104</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12588,32 +12588,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129039623</v>
+        <v>129044243</v>
       </c>
       <c r="B110" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491117</v>
+        <v>491026</v>
       </c>
       <c r="R110" t="n">
-        <v>6710091</v>
+        <v>6709889</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129039226</v>
       </c>
       <c r="B2" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129039783</v>
+        <v>129042946</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491113</v>
+        <v>491232</v>
       </c>
       <c r="R3" t="n">
-        <v>6710132</v>
+        <v>6710086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129041992</v>
+        <v>129045855</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491353</v>
+        <v>491030</v>
       </c>
       <c r="R4" t="n">
-        <v>6710077</v>
+        <v>6709895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,50 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129038956</v>
+        <v>129041481</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490939</v>
+        <v>491361</v>
       </c>
       <c r="R5" t="n">
-        <v>6709966</v>
+        <v>6710143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129045855</v>
+        <v>129039783</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491030</v>
+        <v>491113</v>
       </c>
       <c r="R6" t="n">
-        <v>6709895</v>
+        <v>6710132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,32 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129041481</v>
+        <v>129041992</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491361</v>
+        <v>491353</v>
       </c>
       <c r="R7" t="n">
-        <v>6710143</v>
+        <v>6710077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,45 +1322,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129042946</v>
+        <v>129038956</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491232</v>
+        <v>490939</v>
       </c>
       <c r="R8" t="n">
-        <v>6710086</v>
+        <v>6709966</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På 2 stående.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129040305</v>
+        <v>129043673</v>
       </c>
       <c r="B9" t="n">
-        <v>75157</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,34 +1450,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491221</v>
+        <v>491125</v>
       </c>
       <c r="R9" t="n">
-        <v>6710146</v>
+        <v>6709976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1554,7 @@
         <v>129041053</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,50 +1668,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129043673</v>
+        <v>129043484</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491125</v>
+        <v>491159</v>
       </c>
       <c r="R11" t="n">
-        <v>6709976</v>
+        <v>6709989</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,32 +1775,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129039748</v>
+        <v>129040595</v>
       </c>
       <c r="B12" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491113</v>
+        <v>491251</v>
       </c>
       <c r="R12" t="n">
-        <v>6710132</v>
+        <v>6710146</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129043484</v>
+        <v>129045778</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491159</v>
+        <v>491010</v>
       </c>
       <c r="R13" t="n">
-        <v>6709989</v>
+        <v>6709893</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129040595</v>
+        <v>129041291</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,14 +2020,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491251</v>
+        <v>491359</v>
       </c>
       <c r="R14" t="n">
-        <v>6710146</v>
+        <v>6710158</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129045778</v>
+        <v>129040305</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>75159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491010</v>
+        <v>491221</v>
       </c>
       <c r="R15" t="n">
-        <v>6709893</v>
+        <v>6710146</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,45 +2203,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129041291</v>
+        <v>129039748</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491359</v>
+        <v>491113</v>
       </c>
       <c r="R16" t="n">
-        <v>6710158</v>
+        <v>6710132</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,32 +2310,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129043063</v>
+        <v>129039360</v>
       </c>
       <c r="B17" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491227</v>
+        <v>491080</v>
       </c>
       <c r="R17" t="n">
-        <v>6710010</v>
+        <v>6710071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På stenblock.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129039360</v>
+        <v>129039950</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>91827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,21 +2433,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491080</v>
+        <v>491157</v>
       </c>
       <c r="R18" t="n">
-        <v>6710071</v>
+        <v>6710161</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,12 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,32 +2529,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129039950</v>
+        <v>129043063</v>
       </c>
       <c r="B19" t="n">
-        <v>91825</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491157</v>
+        <v>491227</v>
       </c>
       <c r="R19" t="n">
-        <v>6710161</v>
+        <v>6710010</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,7 +2599,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2614,7 +2609,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På stenblock.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,7 +2644,7 @@
         <v>129041584</v>
       </c>
       <c r="B20" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,32 +2748,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129040685</v>
+        <v>129037863</v>
       </c>
       <c r="B21" t="n">
-        <v>92833</v>
+        <v>91997</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491251</v>
+        <v>490942</v>
       </c>
       <c r="R21" t="n">
-        <v>6710146</v>
+        <v>6709873</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129037863</v>
+        <v>129040685</v>
       </c>
       <c r="B22" t="n">
-        <v>91995</v>
+        <v>92835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490942</v>
+        <v>491251</v>
       </c>
       <c r="R22" t="n">
-        <v>6709873</v>
+        <v>6710146</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3077,7 +3077,7 @@
         <v>129044129</v>
       </c>
       <c r="B24" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,45 +3181,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129045240</v>
+        <v>129042527</v>
       </c>
       <c r="B25" t="n">
-        <v>91825</v>
+        <v>92835</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491133</v>
+        <v>491296</v>
       </c>
       <c r="R25" t="n">
-        <v>6710118</v>
+        <v>6710104</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,7 +3260,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3270,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3291,7 +3300,7 @@
         <v>129040515</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3405,54 +3414,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129042527</v>
+        <v>129045583</v>
       </c>
       <c r="B27" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491296</v>
+        <v>490946</v>
       </c>
       <c r="R27" t="n">
-        <v>6710104</v>
+        <v>6709935</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,10 +3521,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129045583</v>
+        <v>129043562</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490946</v>
+        <v>491129</v>
       </c>
       <c r="R28" t="n">
-        <v>6709935</v>
+        <v>6709987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3628,10 +3628,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129043562</v>
+        <v>129041242</v>
       </c>
       <c r="B29" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,14 +3659,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491129</v>
+        <v>491341</v>
       </c>
       <c r="R29" t="n">
-        <v>6709987</v>
+        <v>6710206</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,45 +3735,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129041242</v>
+        <v>129045240</v>
       </c>
       <c r="B30" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491341</v>
+        <v>491133</v>
       </c>
       <c r="R30" t="n">
-        <v>6710206</v>
+        <v>6710118</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129044587</v>
+        <v>129044722</v>
       </c>
       <c r="B31" t="n">
-        <v>91825</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491075</v>
+        <v>491088</v>
       </c>
       <c r="R31" t="n">
-        <v>6709943</v>
+        <v>6709977</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3922,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,45 +3954,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129040534</v>
+        <v>129040867</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>105741</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491261</v>
+        <v>491332</v>
       </c>
       <c r="R32" t="n">
-        <v>6710156</v>
+        <v>6710175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,7 +4024,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4029,7 +4034,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4056,45 +4061,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129040867</v>
+        <v>129044587</v>
       </c>
       <c r="B33" t="n">
-        <v>105739</v>
+        <v>91827</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491332</v>
+        <v>491075</v>
       </c>
       <c r="R33" t="n">
-        <v>6710175</v>
+        <v>6709943</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,7 +4131,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4136,7 +4141,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4163,50 +4168,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129039814</v>
+        <v>129040534</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491102</v>
+        <v>491261</v>
       </c>
       <c r="R34" t="n">
-        <v>6710142</v>
+        <v>6710156</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4275,45 +4275,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129039825</v>
+        <v>129038111</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491126</v>
+        <v>490874</v>
       </c>
       <c r="R35" t="n">
-        <v>6710148</v>
+        <v>6709885</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4345,7 +4350,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4355,7 +4360,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4382,10 +4392,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129041725</v>
+        <v>129039814</v>
       </c>
       <c r="B36" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4410,31 +4420,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491375</v>
+        <v>491102</v>
       </c>
       <c r="R36" t="n">
-        <v>6710101</v>
+        <v>6710142</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4466,7 +4467,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4476,7 +4477,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4503,32 +4504,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129044722</v>
+        <v>129039825</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4538,10 +4539,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491088</v>
+        <v>491126</v>
       </c>
       <c r="R37" t="n">
-        <v>6709977</v>
+        <v>6710148</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4573,7 +4574,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4583,12 +4584,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4615,50 +4611,59 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129038111</v>
+        <v>129041725</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490874</v>
+        <v>491375</v>
       </c>
       <c r="R38" t="n">
-        <v>6709885</v>
+        <v>6710101</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4690,7 +4695,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4700,12 +4705,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4735,7 +4735,7 @@
         <v>129045013</v>
       </c>
       <c r="B39" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>129040042</v>
       </c>
       <c r="B40" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>129038104</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>129044467</v>
       </c>
       <c r="B42" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5173,45 +5173,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129041044</v>
+        <v>129044319</v>
       </c>
       <c r="B43" t="n">
-        <v>92833</v>
+        <v>91542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491306</v>
+        <v>491049</v>
       </c>
       <c r="R43" t="n">
-        <v>6710197</v>
+        <v>6709915</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5280,10 +5280,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129044319</v>
+        <v>129045330</v>
       </c>
       <c r="B44" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5291,34 +5291,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491049</v>
+        <v>491085</v>
       </c>
       <c r="R44" t="n">
-        <v>6709915</v>
+        <v>6710033</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5350,7 +5355,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5360,7 +5365,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,50 +5397,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129045330</v>
+        <v>129041044</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>92835</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491085</v>
+        <v>491306</v>
       </c>
       <c r="R45" t="n">
-        <v>6710033</v>
+        <v>6710197</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5462,7 +5467,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5472,12 +5477,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5507,7 +5507,7 @@
         <v>129037802</v>
       </c>
       <c r="B46" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>129039795</v>
       </c>
       <c r="B47" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         <v>129042338</v>
       </c>
       <c r="B48" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>129038812</v>
       </c>
       <c r="B49" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>129044332</v>
       </c>
       <c r="B50" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>129045046</v>
       </c>
       <c r="B51" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>129039883</v>
       </c>
       <c r="B52" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6295,45 +6295,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129040369</v>
+        <v>129038692</v>
       </c>
       <c r="B53" t="n">
-        <v>98676</v>
+        <v>57887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>491194</v>
+        <v>490892</v>
       </c>
       <c r="R53" t="n">
-        <v>6710167</v>
+        <v>6709919</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6365,7 +6370,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6375,7 +6380,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6402,50 +6407,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129038692</v>
+        <v>129044552</v>
       </c>
       <c r="B54" t="n">
-        <v>57885</v>
+        <v>98678</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490892</v>
+        <v>491075</v>
       </c>
       <c r="R54" t="n">
-        <v>6709919</v>
+        <v>6709942</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6514,10 +6514,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129044552</v>
+        <v>129040369</v>
       </c>
       <c r="B55" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>491075</v>
+        <v>491194</v>
       </c>
       <c r="R55" t="n">
-        <v>6709942</v>
+        <v>6710167</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6624,7 +6624,7 @@
         <v>129037776</v>
       </c>
       <c r="B56" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6728,32 +6728,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129038411</v>
+        <v>129040007</v>
       </c>
       <c r="B57" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490873</v>
+        <v>491180</v>
       </c>
       <c r="R57" t="n">
-        <v>6709909</v>
+        <v>6710139</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,32 +6835,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129044061</v>
+        <v>129039941</v>
       </c>
       <c r="B58" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491110</v>
+        <v>491158</v>
       </c>
       <c r="R58" t="n">
-        <v>6709915</v>
+        <v>6710160</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,10 +6942,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129045420</v>
+        <v>129038411</v>
       </c>
       <c r="B59" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>491009</v>
+        <v>490873</v>
       </c>
       <c r="R59" t="n">
-        <v>6709991</v>
+        <v>6709909</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7049,10 +7049,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129038173</v>
+        <v>129044061</v>
       </c>
       <c r="B60" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7077,31 +7077,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490877</v>
+        <v>491110</v>
       </c>
       <c r="R60" t="n">
-        <v>6709889</v>
+        <v>6709915</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7133,7 +7119,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7143,7 +7129,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,10 +7156,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129043992</v>
+        <v>129045420</v>
       </c>
       <c r="B61" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7205,10 +7191,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>491095</v>
+        <v>491009</v>
       </c>
       <c r="R61" t="n">
-        <v>6709906</v>
+        <v>6709991</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7240,7 +7226,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7250,7 +7236,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7277,45 +7263,59 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129040007</v>
+        <v>129038173</v>
       </c>
       <c r="B62" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>491180</v>
+        <v>490877</v>
       </c>
       <c r="R62" t="n">
-        <v>6710139</v>
+        <v>6709889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,32 +7384,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129039941</v>
+        <v>129043992</v>
       </c>
       <c r="B63" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491158</v>
+        <v>491095</v>
       </c>
       <c r="R63" t="n">
-        <v>6710160</v>
+        <v>6709906</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7491,10 +7491,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129042106</v>
+        <v>129037762</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7502,21 +7502,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>491327</v>
+        <v>490949</v>
       </c>
       <c r="R64" t="n">
-        <v>6710067</v>
+        <v>6709885</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7571,12 +7571,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7603,45 +7598,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129037762</v>
+        <v>129039716</v>
       </c>
       <c r="B65" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490949</v>
+        <v>491118</v>
       </c>
       <c r="R65" t="n">
-        <v>6709885</v>
+        <v>6710111</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7683,7 +7683,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7710,10 +7715,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129039716</v>
+        <v>129044189</v>
       </c>
       <c r="B66" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7739,21 +7744,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491118</v>
+        <v>491025</v>
       </c>
       <c r="R66" t="n">
-        <v>6710111</v>
+        <v>6709886</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7795,12 +7795,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7827,10 +7822,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129044189</v>
+        <v>129043659</v>
       </c>
       <c r="B67" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7862,10 +7857,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>491025</v>
+        <v>491126</v>
       </c>
       <c r="R67" t="n">
-        <v>6709886</v>
+        <v>6709977</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7897,7 +7892,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7907,7 +7902,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7934,10 +7929,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129043659</v>
+        <v>129045555</v>
       </c>
       <c r="B68" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7969,10 +7964,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>491126</v>
+        <v>490955</v>
       </c>
       <c r="R68" t="n">
-        <v>6709977</v>
+        <v>6709969</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8004,7 +7999,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8014,7 +8009,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8041,10 +8036,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129045555</v>
+        <v>129039681</v>
       </c>
       <c r="B69" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8070,16 +8065,21 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490955</v>
+        <v>491120</v>
       </c>
       <c r="R69" t="n">
-        <v>6709969</v>
+        <v>6710111</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8148,10 +8148,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129039681</v>
+        <v>129038944</v>
       </c>
       <c r="B70" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8177,21 +8177,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>491120</v>
+        <v>490941</v>
       </c>
       <c r="R70" t="n">
-        <v>6710111</v>
+        <v>6709965</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8223,7 +8218,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8233,7 +8228,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8260,32 +8255,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129038944</v>
+        <v>129042106</v>
       </c>
       <c r="B71" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8295,10 +8290,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490941</v>
+        <v>491327</v>
       </c>
       <c r="R71" t="n">
-        <v>6709965</v>
+        <v>6710067</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8330,7 +8325,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8340,7 +8335,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8370,7 +8370,7 @@
         <v>129040356</v>
       </c>
       <c r="B72" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>129043183</v>
       </c>
       <c r="B73" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>129042724</v>
       </c>
       <c r="B74" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>129038053</v>
       </c>
       <c r="B75" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>129038223</v>
       </c>
       <c r="B76" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>129040051</v>
       </c>
       <c r="B77" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>129040173</v>
       </c>
       <c r="B78" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>129039515</v>
       </c>
       <c r="B79" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>129043352</v>
       </c>
       <c r="B80" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>129044818</v>
       </c>
       <c r="B81" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>129042971</v>
       </c>
       <c r="B82" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>129039011</v>
       </c>
       <c r="B83" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>129039994</v>
       </c>
       <c r="B85" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9920,45 +9920,54 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129045737</v>
+        <v>129043286</v>
       </c>
       <c r="B86" t="n">
-        <v>92833</v>
+        <v>91562</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>491006</v>
+        <v>491185</v>
       </c>
       <c r="R86" t="n">
-        <v>6709889</v>
+        <v>6710038</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9990,7 +9999,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10000,7 +10009,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10027,10 +10036,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129043286</v>
+        <v>129040273</v>
       </c>
       <c r="B87" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10038,43 +10047,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491185</v>
+        <v>491210</v>
       </c>
       <c r="R87" t="n">
-        <v>6710038</v>
+        <v>6710152</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10116,7 +10116,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10143,45 +10148,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129039427</v>
+        <v>129042243</v>
       </c>
       <c r="B88" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491089</v>
+        <v>491324</v>
       </c>
       <c r="R88" t="n">
-        <v>6710079</v>
+        <v>6710108</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10213,7 +10218,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10223,7 +10228,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10250,10 +10260,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129040273</v>
+        <v>129043457</v>
       </c>
       <c r="B89" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10285,10 +10295,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491210</v>
+        <v>491159</v>
       </c>
       <c r="R89" t="n">
-        <v>6710152</v>
+        <v>6709989</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10320,7 +10330,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10330,12 +10340,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10362,45 +10372,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129042243</v>
+        <v>129045737</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>92835</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491324</v>
+        <v>491006</v>
       </c>
       <c r="R90" t="n">
-        <v>6710108</v>
+        <v>6709889</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10432,7 +10442,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10442,12 +10452,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10474,32 +10479,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129043457</v>
+        <v>129039427</v>
       </c>
       <c r="B91" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10509,10 +10514,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491159</v>
+        <v>491089</v>
       </c>
       <c r="R91" t="n">
-        <v>6709989</v>
+        <v>6710079</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10544,7 +10549,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10554,12 +10559,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10589,7 +10589,7 @@
         <v>129039369</v>
       </c>
       <c r="B92" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>129040090</v>
       </c>
       <c r="B93" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>129041984</v>
       </c>
       <c r="B94" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>129041444</v>
       </c>
       <c r="B95" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11038,10 +11038,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129043344</v>
+        <v>129044360</v>
       </c>
       <c r="B96" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11073,10 +11073,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491176</v>
+        <v>491050</v>
       </c>
       <c r="R96" t="n">
-        <v>6710019</v>
+        <v>6709915</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11145,10 +11145,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129044713</v>
+        <v>129041232</v>
       </c>
       <c r="B97" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11174,16 +11174,21 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491086</v>
+        <v>491336</v>
       </c>
       <c r="R97" t="n">
-        <v>6709974</v>
+        <v>6710188</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11215,7 +11220,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11225,7 +11230,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11252,10 +11257,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129044360</v>
+        <v>129045097</v>
       </c>
       <c r="B98" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11281,16 +11286,21 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491050</v>
+        <v>491132</v>
       </c>
       <c r="R98" t="n">
-        <v>6709915</v>
+        <v>6710123</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11322,7 +11332,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11332,7 +11342,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11359,10 +11374,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129041232</v>
+        <v>129043344</v>
       </c>
       <c r="B99" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11388,21 +11403,16 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491336</v>
+        <v>491176</v>
       </c>
       <c r="R99" t="n">
-        <v>6710188</v>
+        <v>6710019</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11434,7 +11444,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11444,7 +11454,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11471,10 +11481,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129045097</v>
+        <v>129044713</v>
       </c>
       <c r="B100" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11500,21 +11510,16 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491132</v>
+        <v>491086</v>
       </c>
       <c r="R100" t="n">
-        <v>6710123</v>
+        <v>6709974</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11546,7 +11551,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11556,12 +11561,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11591,7 +11591,7 @@
         <v>129040149</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>129038846</v>
       </c>
       <c r="B102" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>129045506</v>
       </c>
       <c r="B103" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>129044617</v>
       </c>
       <c r="B104" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>129043760</v>
       </c>
       <c r="B105" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12146,10 +12146,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129039623</v>
+        <v>129039646</v>
       </c>
       <c r="B106" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12157,21 +12157,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12226,7 +12226,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12253,45 +12258,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129039646</v>
+        <v>129039218</v>
       </c>
       <c r="B107" t="n">
-        <v>91825</v>
+        <v>92835</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491117</v>
+        <v>491054</v>
       </c>
       <c r="R107" t="n">
-        <v>6710091</v>
+        <v>6710041</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12323,7 +12337,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12333,12 +12347,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12365,54 +12374,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129039218</v>
+        <v>129042566</v>
       </c>
       <c r="B108" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491054</v>
+        <v>491288</v>
       </c>
       <c r="R108" t="n">
-        <v>6710041</v>
+        <v>6710104</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12444,7 +12444,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12481,10 +12481,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129042566</v>
+        <v>129044243</v>
       </c>
       <c r="B109" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491288</v>
+        <v>491026</v>
       </c>
       <c r="R109" t="n">
-        <v>6710104</v>
+        <v>6709889</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12588,32 +12588,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129044243</v>
+        <v>129039623</v>
       </c>
       <c r="B110" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491026</v>
+        <v>491117</v>
       </c>
       <c r="R110" t="n">
-        <v>6709889</v>
+        <v>6710091</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129039226</v>
+        <v>129045855</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491060</v>
+        <v>491030</v>
       </c>
       <c r="R2" t="n">
-        <v>6710037</v>
+        <v>6709895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129042946</v>
+        <v>129041481</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491232</v>
+        <v>491361</v>
       </c>
       <c r="R3" t="n">
-        <v>6710086</v>
+        <v>6710143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På 2 stående.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129045855</v>
+        <v>129039783</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491030</v>
+        <v>491113</v>
       </c>
       <c r="R4" t="n">
-        <v>6709895</v>
+        <v>6710132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129041481</v>
+        <v>129041992</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491361</v>
+        <v>491353</v>
       </c>
       <c r="R5" t="n">
-        <v>6710143</v>
+        <v>6710077</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129039783</v>
+        <v>129039226</v>
       </c>
       <c r="B6" t="n">
-        <v>91542</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491113</v>
+        <v>491060</v>
       </c>
       <c r="R6" t="n">
-        <v>6710132</v>
+        <v>6710037</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129041992</v>
+        <v>129038956</v>
       </c>
       <c r="B7" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491353</v>
+        <v>490939</v>
       </c>
       <c r="R7" t="n">
-        <v>6710077</v>
+        <v>6709966</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,50 +1327,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129038956</v>
+        <v>129042946</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490939</v>
+        <v>491232</v>
       </c>
       <c r="R8" t="n">
-        <v>6709966</v>
+        <v>6710086</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129043673</v>
+        <v>129039748</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,39 +1450,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491125</v>
+        <v>491113</v>
       </c>
       <c r="R9" t="n">
-        <v>6709976</v>
+        <v>6710132</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,50 +1546,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129041053</v>
+        <v>129040305</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>75159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491309</v>
+        <v>491221</v>
       </c>
       <c r="R10" t="n">
-        <v>6710192</v>
+        <v>6710146</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,12 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,45 +1653,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129043484</v>
+        <v>129041053</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491159</v>
+        <v>491309</v>
       </c>
       <c r="R11" t="n">
-        <v>6709989</v>
+        <v>6710192</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1748,7 +1738,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,45 +1770,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129040595</v>
+        <v>129043673</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491251</v>
+        <v>491125</v>
       </c>
       <c r="R12" t="n">
-        <v>6710146</v>
+        <v>6709976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,7 +1882,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129045778</v>
+        <v>129043484</v>
       </c>
       <c r="B13" t="n">
         <v>98678</v>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491010</v>
+        <v>491159</v>
       </c>
       <c r="R13" t="n">
-        <v>6709893</v>
+        <v>6709989</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129041291</v>
+        <v>129040595</v>
       </c>
       <c r="B14" t="n">
         <v>98678</v>
@@ -2020,14 +2020,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491359</v>
+        <v>491251</v>
       </c>
       <c r="R14" t="n">
-        <v>6710158</v>
+        <v>6710146</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129040305</v>
+        <v>129045778</v>
       </c>
       <c r="B15" t="n">
-        <v>75159</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491221</v>
+        <v>491010</v>
       </c>
       <c r="R15" t="n">
-        <v>6710146</v>
+        <v>6709893</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,45 +2203,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129039748</v>
+        <v>129041291</v>
       </c>
       <c r="B16" t="n">
-        <v>92835</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491113</v>
+        <v>491359</v>
       </c>
       <c r="R16" t="n">
-        <v>6710132</v>
+        <v>6710158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129039360</v>
+        <v>129039950</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491080</v>
+        <v>491157</v>
       </c>
       <c r="R17" t="n">
-        <v>6710071</v>
+        <v>6710161</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,12 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129039950</v>
+        <v>129039360</v>
       </c>
       <c r="B18" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,21 +2428,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491157</v>
+        <v>491080</v>
       </c>
       <c r="R18" t="n">
-        <v>6710161</v>
+        <v>6710071</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,7 +2497,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,45 +2641,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129041584</v>
+        <v>129037863</v>
       </c>
       <c r="B20" t="n">
-        <v>91562</v>
+        <v>91997</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491362</v>
+        <v>490942</v>
       </c>
       <c r="R20" t="n">
-        <v>6710143</v>
+        <v>6709873</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,45 +2748,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129037863</v>
+        <v>129040720</v>
       </c>
       <c r="B21" t="n">
-        <v>91997</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490942</v>
+        <v>491296</v>
       </c>
       <c r="R21" t="n">
-        <v>6709873</v>
+        <v>6710129</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2833,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,32 +2860,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129040685</v>
+        <v>129044129</v>
       </c>
       <c r="B22" t="n">
-        <v>92835</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491251</v>
+        <v>491049</v>
       </c>
       <c r="R22" t="n">
-        <v>6710146</v>
+        <v>6709893</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129040720</v>
+        <v>129040685</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>92835</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,39 +2978,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491296</v>
+        <v>491251</v>
       </c>
       <c r="R23" t="n">
-        <v>6710129</v>
+        <v>6710146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,45 +3074,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129044129</v>
+        <v>129041584</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>91562</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491049</v>
+        <v>491362</v>
       </c>
       <c r="R24" t="n">
-        <v>6709893</v>
+        <v>6710143</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,54 +3181,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129042527</v>
+        <v>129045240</v>
       </c>
       <c r="B25" t="n">
-        <v>92835</v>
+        <v>91827</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491296</v>
+        <v>491133</v>
       </c>
       <c r="R25" t="n">
-        <v>6710104</v>
+        <v>6710118</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3260,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3270,7 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3297,38 +3288,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129040515</v>
+        <v>129042527</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3337,10 +3332,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491251</v>
+        <v>491296</v>
       </c>
       <c r="R26" t="n">
-        <v>6710165</v>
+        <v>6710104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,7 +3367,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3382,12 +3377,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,45 +3404,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129045583</v>
+        <v>129040515</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490946</v>
+        <v>491251</v>
       </c>
       <c r="R27" t="n">
-        <v>6709935</v>
+        <v>6710165</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3484,7 +3479,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3494,7 +3489,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,7 +3521,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129043562</v>
+        <v>129045583</v>
       </c>
       <c r="B28" t="n">
         <v>98678</v>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491129</v>
+        <v>490946</v>
       </c>
       <c r="R28" t="n">
-        <v>6709987</v>
+        <v>6709935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3628,7 +3628,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129041242</v>
+        <v>129043562</v>
       </c>
       <c r="B29" t="n">
         <v>98678</v>
@@ -3659,14 +3659,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491341</v>
+        <v>491129</v>
       </c>
       <c r="R29" t="n">
-        <v>6710206</v>
+        <v>6709987</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,45 +3735,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129045240</v>
+        <v>129041242</v>
       </c>
       <c r="B30" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491133</v>
+        <v>491341</v>
       </c>
       <c r="R30" t="n">
-        <v>6710118</v>
+        <v>6710206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129044722</v>
+        <v>129040534</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491088</v>
+        <v>491261</v>
       </c>
       <c r="R31" t="n">
-        <v>6709977</v>
+        <v>6710156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,12 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3954,45 +3949,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129040867</v>
+        <v>129044587</v>
       </c>
       <c r="B32" t="n">
-        <v>105741</v>
+        <v>91827</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491332</v>
+        <v>491075</v>
       </c>
       <c r="R32" t="n">
-        <v>6710175</v>
+        <v>6709943</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4034,7 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4061,10 +4056,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129044587</v>
+        <v>129044722</v>
       </c>
       <c r="B33" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4072,21 +4067,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4096,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491075</v>
+        <v>491088</v>
       </c>
       <c r="R33" t="n">
-        <v>6709943</v>
+        <v>6709977</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4126,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4141,7 +4136,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4168,10 +4168,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129040534</v>
+        <v>129038111</v>
       </c>
       <c r="B34" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4179,34 +4179,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491261</v>
+        <v>490874</v>
       </c>
       <c r="R34" t="n">
-        <v>6710156</v>
+        <v>6709885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,7 +4243,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4248,7 +4253,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4275,50 +4285,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129038111</v>
+        <v>129040867</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>105741</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490874</v>
+        <v>491332</v>
       </c>
       <c r="R35" t="n">
-        <v>6709885</v>
+        <v>6710175</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4350,7 +4355,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4360,12 +4365,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4732,10 +4732,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129045013</v>
+        <v>129038104</v>
       </c>
       <c r="B39" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,34 +4743,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491157</v>
+        <v>490880</v>
       </c>
       <c r="R39" t="n">
-        <v>6710121</v>
+        <v>6709882</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4802,7 +4810,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4812,7 +4820,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4946,53 +4959,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129038104</v>
+        <v>129044467</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490880</v>
+        <v>491036</v>
       </c>
       <c r="R41" t="n">
-        <v>6709882</v>
+        <v>6709945</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5024,7 +5029,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5034,12 +5039,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5066,32 +5066,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129044467</v>
+        <v>129045013</v>
       </c>
       <c r="B42" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491036</v>
+        <v>491157</v>
       </c>
       <c r="R42" t="n">
-        <v>6709945</v>
+        <v>6710121</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5280,50 +5280,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129045330</v>
+        <v>129041044</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491085</v>
+        <v>491306</v>
       </c>
       <c r="R44" t="n">
-        <v>6710033</v>
+        <v>6710197</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5355,7 +5350,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5365,12 +5360,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,45 +5387,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129041044</v>
+        <v>129045330</v>
       </c>
       <c r="B45" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491306</v>
+        <v>491085</v>
       </c>
       <c r="R45" t="n">
-        <v>6710197</v>
+        <v>6710033</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5467,7 +5462,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5477,7 +5472,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6621,32 +6621,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129037776</v>
+        <v>129038411</v>
       </c>
       <c r="B56" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490952</v>
+        <v>490873</v>
       </c>
       <c r="R56" t="n">
-        <v>6709889</v>
+        <v>6709909</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6728,32 +6728,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129040007</v>
+        <v>129044061</v>
       </c>
       <c r="B57" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>491180</v>
+        <v>491110</v>
       </c>
       <c r="R57" t="n">
-        <v>6710139</v>
+        <v>6709915</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,32 +6835,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129039941</v>
+        <v>129045420</v>
       </c>
       <c r="B58" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491158</v>
+        <v>491009</v>
       </c>
       <c r="R58" t="n">
-        <v>6710160</v>
+        <v>6709991</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,7 +6942,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129038411</v>
+        <v>129038173</v>
       </c>
       <c r="B59" t="n">
         <v>98678</v>
@@ -6970,17 +6970,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490873</v>
+        <v>490877</v>
       </c>
       <c r="R59" t="n">
-        <v>6709909</v>
+        <v>6709889</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7012,7 +7026,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7022,7 +7036,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7049,7 +7063,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129044061</v>
+        <v>129043992</v>
       </c>
       <c r="B60" t="n">
         <v>98678</v>
@@ -7084,10 +7098,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>491110</v>
+        <v>491095</v>
       </c>
       <c r="R60" t="n">
-        <v>6709915</v>
+        <v>6709906</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7119,7 +7133,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7129,7 +7143,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7156,32 +7170,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129045420</v>
+        <v>129039941</v>
       </c>
       <c r="B61" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7191,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>491009</v>
+        <v>491158</v>
       </c>
       <c r="R61" t="n">
-        <v>6709991</v>
+        <v>6710160</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7226,7 +7240,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7236,7 +7250,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7263,59 +7277,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129038173</v>
+        <v>129040007</v>
       </c>
       <c r="B62" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490877</v>
+        <v>491180</v>
       </c>
       <c r="R62" t="n">
-        <v>6709889</v>
+        <v>6710139</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,32 +7384,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129043992</v>
+        <v>129037776</v>
       </c>
       <c r="B63" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491095</v>
+        <v>490952</v>
       </c>
       <c r="R63" t="n">
-        <v>6709906</v>
+        <v>6709889</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7491,10 +7491,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129037762</v>
+        <v>129042106</v>
       </c>
       <c r="B64" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7502,21 +7502,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490949</v>
+        <v>491327</v>
       </c>
       <c r="R64" t="n">
-        <v>6709885</v>
+        <v>6710067</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7571,7 +7571,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7598,50 +7603,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129039716</v>
+        <v>129037762</v>
       </c>
       <c r="B65" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>491118</v>
+        <v>490949</v>
       </c>
       <c r="R65" t="n">
-        <v>6710111</v>
+        <v>6709885</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7683,12 +7683,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7715,7 +7710,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129044189</v>
+        <v>129039716</v>
       </c>
       <c r="B66" t="n">
         <v>98678</v>
@@ -7744,16 +7739,21 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491025</v>
+        <v>491118</v>
       </c>
       <c r="R66" t="n">
-        <v>6709886</v>
+        <v>6710111</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7795,7 +7795,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7822,7 +7827,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129043659</v>
+        <v>129044189</v>
       </c>
       <c r="B67" t="n">
         <v>98678</v>
@@ -7857,10 +7862,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>491126</v>
+        <v>491025</v>
       </c>
       <c r="R67" t="n">
-        <v>6709977</v>
+        <v>6709886</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7892,7 +7897,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7902,7 +7907,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7929,7 +7934,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129045555</v>
+        <v>129043659</v>
       </c>
       <c r="B68" t="n">
         <v>98678</v>
@@ -7964,10 +7969,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490955</v>
+        <v>491126</v>
       </c>
       <c r="R68" t="n">
-        <v>6709969</v>
+        <v>6709977</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7999,7 +8004,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8009,7 +8014,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8036,7 +8041,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129039681</v>
+        <v>129045555</v>
       </c>
       <c r="B69" t="n">
         <v>98678</v>
@@ -8065,21 +8070,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>491120</v>
+        <v>490955</v>
       </c>
       <c r="R69" t="n">
-        <v>6710111</v>
+        <v>6709969</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8148,7 +8148,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129038944</v>
+        <v>129039681</v>
       </c>
       <c r="B70" t="n">
         <v>98678</v>
@@ -8177,16 +8177,21 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490941</v>
+        <v>491120</v>
       </c>
       <c r="R70" t="n">
-        <v>6709965</v>
+        <v>6710111</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8218,7 +8223,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8228,7 +8233,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8255,32 +8260,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129042106</v>
+        <v>129038944</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8290,10 +8295,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>491327</v>
+        <v>490941</v>
       </c>
       <c r="R71" t="n">
-        <v>6710067</v>
+        <v>6709965</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8325,7 +8330,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8335,12 +8340,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8367,10 +8367,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129040356</v>
+        <v>129038053</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8378,34 +8378,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>491211</v>
+        <v>490886</v>
       </c>
       <c r="R72" t="n">
-        <v>6710165</v>
+        <v>6709872</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,7 +8442,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8447,7 +8452,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8474,10 +8484,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129043183</v>
+        <v>129038223</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8485,34 +8495,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>491200</v>
+        <v>490878</v>
       </c>
       <c r="R73" t="n">
-        <v>6709983</v>
+        <v>6709889</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8544,7 +8559,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8554,12 +8569,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8586,32 +8596,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129042724</v>
+        <v>129040356</v>
       </c>
       <c r="B74" t="n">
-        <v>92871</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8621,10 +8631,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>491257</v>
+        <v>491211</v>
       </c>
       <c r="R74" t="n">
-        <v>6710085</v>
+        <v>6710165</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8656,7 +8666,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8666,7 +8676,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8693,10 +8703,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129038053</v>
+        <v>129043183</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8704,39 +8714,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490886</v>
+        <v>491200</v>
       </c>
       <c r="R75" t="n">
-        <v>6709872</v>
+        <v>6709983</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8768,7 +8773,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8778,12 +8783,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8810,50 +8815,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129038223</v>
+        <v>129042724</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>92871</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490878</v>
+        <v>491257</v>
       </c>
       <c r="R76" t="n">
-        <v>6709889</v>
+        <v>6710085</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9029,7 +9029,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129040173</v>
+        <v>129043352</v>
       </c>
       <c r="B78" t="n">
         <v>98678</v>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>491201</v>
+        <v>491188</v>
       </c>
       <c r="R78" t="n">
-        <v>6710139</v>
+        <v>6709988</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9136,7 +9136,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129039515</v>
+        <v>129040173</v>
       </c>
       <c r="B79" t="n">
         <v>98678</v>
@@ -9165,21 +9165,16 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>491104</v>
+        <v>491201</v>
       </c>
       <c r="R79" t="n">
-        <v>6710105</v>
+        <v>6710139</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9211,7 +9206,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9221,7 +9216,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9248,7 +9243,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129043352</v>
+        <v>129039515</v>
       </c>
       <c r="B80" t="n">
         <v>98678</v>
@@ -9277,16 +9272,21 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>491188</v>
+        <v>491104</v>
       </c>
       <c r="R80" t="n">
-        <v>6709988</v>
+        <v>6710105</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9355,10 +9355,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129044818</v>
+        <v>129042971</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9366,34 +9366,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>491116</v>
+        <v>491193</v>
       </c>
       <c r="R81" t="n">
-        <v>6710020</v>
+        <v>6710074</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9425,7 +9430,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9435,12 +9440,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9467,7 +9472,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129042971</v>
+        <v>129039011</v>
       </c>
       <c r="B82" t="n">
         <v>57727</v>
@@ -9507,10 +9512,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>491193</v>
+        <v>490936</v>
       </c>
       <c r="R82" t="n">
-        <v>6710074</v>
+        <v>6709979</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9542,7 +9547,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9552,7 +9557,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9584,10 +9589,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129039011</v>
+        <v>129044818</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9595,39 +9600,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490936</v>
+        <v>491116</v>
       </c>
       <c r="R83" t="n">
-        <v>6709979</v>
+        <v>6710020</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9701,50 +9701,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129038137</v>
+        <v>129039994</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>98678</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490876</v>
+        <v>491173</v>
       </c>
       <c r="R84" t="n">
-        <v>6709883</v>
+        <v>6710152</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9776,7 +9771,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9786,7 +9781,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9813,45 +9808,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129039994</v>
+        <v>129038137</v>
       </c>
       <c r="B85" t="n">
-        <v>98678</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>491173</v>
+        <v>490876</v>
       </c>
       <c r="R85" t="n">
-        <v>6710152</v>
+        <v>6709883</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9920,10 +9920,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129043286</v>
+        <v>129040273</v>
       </c>
       <c r="B86" t="n">
-        <v>91562</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9931,43 +9931,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>491185</v>
+        <v>491210</v>
       </c>
       <c r="R86" t="n">
-        <v>6710038</v>
+        <v>6710152</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9999,7 +9990,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10009,7 +10000,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10036,7 +10032,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129040273</v>
+        <v>129042243</v>
       </c>
       <c r="B87" t="n">
         <v>79041</v>
@@ -10067,14 +10063,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491210</v>
+        <v>491324</v>
       </c>
       <c r="R87" t="n">
-        <v>6710152</v>
+        <v>6710108</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10106,7 +10102,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10116,12 +10112,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10148,7 +10144,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129042243</v>
+        <v>129043457</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -10179,14 +10175,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491324</v>
+        <v>491159</v>
       </c>
       <c r="R88" t="n">
-        <v>6710108</v>
+        <v>6709989</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10218,7 +10214,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10228,7 +10224,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10260,10 +10256,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129043457</v>
+        <v>129043286</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>91562</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10271,34 +10267,43 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491159</v>
+        <v>491185</v>
       </c>
       <c r="R89" t="n">
-        <v>6709989</v>
+        <v>6710038</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10330,7 +10335,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10340,12 +10345,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10814,45 +10814,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129041984</v>
+        <v>129043344</v>
       </c>
       <c r="B94" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491353</v>
+        <v>491176</v>
       </c>
       <c r="R94" t="n">
-        <v>6710077</v>
+        <v>6710019</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10921,50 +10921,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129041444</v>
+        <v>129044713</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491362</v>
+        <v>491086</v>
       </c>
       <c r="R95" t="n">
-        <v>6710150</v>
+        <v>6709974</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10996,7 +10991,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11006,12 +11001,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11374,45 +11364,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129043344</v>
+        <v>129041984</v>
       </c>
       <c r="B99" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491176</v>
+        <v>491353</v>
       </c>
       <c r="R99" t="n">
-        <v>6710019</v>
+        <v>6710077</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11444,7 +11434,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11454,7 +11444,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11481,45 +11471,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129044713</v>
+        <v>129041444</v>
       </c>
       <c r="B100" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491086</v>
+        <v>491362</v>
       </c>
       <c r="R100" t="n">
-        <v>6709974</v>
+        <v>6710150</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11551,7 +11546,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11561,7 +11556,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11588,32 +11588,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129040149</v>
+        <v>129043760</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11623,10 +11623,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491192</v>
+        <v>491096</v>
       </c>
       <c r="R101" t="n">
-        <v>6710147</v>
+        <v>6709954</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12039,32 +12039,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129043760</v>
+        <v>129040149</v>
       </c>
       <c r="B105" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12074,10 +12074,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491096</v>
+        <v>491192</v>
       </c>
       <c r="R105" t="n">
-        <v>6709954</v>
+        <v>6710147</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12146,10 +12146,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129039646</v>
+        <v>129039623</v>
       </c>
       <c r="B106" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12157,21 +12157,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12226,12 +12226,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12258,54 +12253,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129039218</v>
+        <v>129039646</v>
       </c>
       <c r="B107" t="n">
-        <v>92835</v>
+        <v>91827</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491054</v>
+        <v>491117</v>
       </c>
       <c r="R107" t="n">
-        <v>6710041</v>
+        <v>6710091</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12337,7 +12323,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12347,7 +12333,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12374,45 +12365,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129042566</v>
+        <v>129039218</v>
       </c>
       <c r="B108" t="n">
-        <v>98678</v>
+        <v>92835</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491288</v>
+        <v>491054</v>
       </c>
       <c r="R108" t="n">
-        <v>6710104</v>
+        <v>6710041</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12444,7 +12444,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12481,7 +12481,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129044243</v>
+        <v>129042566</v>
       </c>
       <c r="B109" t="n">
         <v>98678</v>
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491026</v>
+        <v>491288</v>
       </c>
       <c r="R109" t="n">
-        <v>6709889</v>
+        <v>6710104</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12588,32 +12588,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129039623</v>
+        <v>129044243</v>
       </c>
       <c r="B110" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491117</v>
+        <v>491026</v>
       </c>
       <c r="R110" t="n">
-        <v>6710091</v>
+        <v>6709889</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129045855</v>
+        <v>129042946</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491030</v>
+        <v>491232</v>
       </c>
       <c r="R2" t="n">
-        <v>6709895</v>
+        <v>6710086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129041481</v>
+        <v>129039226</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491361</v>
+        <v>491060</v>
       </c>
       <c r="R3" t="n">
-        <v>6710143</v>
+        <v>6710037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129039783</v>
+        <v>129038956</v>
       </c>
       <c r="B4" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491113</v>
+        <v>490939</v>
       </c>
       <c r="R4" t="n">
-        <v>6710132</v>
+        <v>6709966</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129041992</v>
+        <v>129039783</v>
       </c>
       <c r="B5" t="n">
         <v>91542</v>
@@ -1027,14 +1042,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491353</v>
+        <v>491113</v>
       </c>
       <c r="R5" t="n">
-        <v>6710077</v>
+        <v>6710132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,45 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129039226</v>
+        <v>129041992</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>91542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491060</v>
+        <v>491353</v>
       </c>
       <c r="R6" t="n">
-        <v>6710037</v>
+        <v>6710077</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,50 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129038956</v>
+        <v>129045855</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490939</v>
+        <v>491030</v>
       </c>
       <c r="R7" t="n">
-        <v>6709966</v>
+        <v>6709895</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,12 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,45 +1332,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129042946</v>
+        <v>129041481</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491232</v>
+        <v>491361</v>
       </c>
       <c r="R8" t="n">
-        <v>6710086</v>
+        <v>6710143</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,12 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På 2 stående.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2641,10 +2641,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129037863</v>
+        <v>129044129</v>
       </c>
       <c r="B20" t="n">
-        <v>91997</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,21 +2652,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490942</v>
+        <v>491049</v>
       </c>
       <c r="R20" t="n">
-        <v>6709873</v>
+        <v>6709893</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,10 +2748,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129040720</v>
+        <v>129040685</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,39 +2759,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491296</v>
+        <v>491251</v>
       </c>
       <c r="R21" t="n">
-        <v>6710129</v>
+        <v>6710146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2833,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2860,10 +2855,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129044129</v>
+        <v>129037863</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>91997</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2871,21 +2866,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2895,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491049</v>
+        <v>490942</v>
       </c>
       <c r="R22" t="n">
-        <v>6709893</v>
+        <v>6709873</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,45 +2962,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129040685</v>
+        <v>129041584</v>
       </c>
       <c r="B23" t="n">
-        <v>92835</v>
+        <v>91562</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491251</v>
+        <v>491362</v>
       </c>
       <c r="R23" t="n">
-        <v>6710146</v>
+        <v>6710143</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,45 +3069,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129041584</v>
+        <v>129040720</v>
       </c>
       <c r="B24" t="n">
-        <v>91562</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491362</v>
+        <v>491296</v>
       </c>
       <c r="R24" t="n">
-        <v>6710143</v>
+        <v>6710129</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3842,45 +3842,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129040534</v>
+        <v>129040867</v>
       </c>
       <c r="B31" t="n">
-        <v>91542</v>
+        <v>105741</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491261</v>
+        <v>491332</v>
       </c>
       <c r="R31" t="n">
-        <v>6710156</v>
+        <v>6710175</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,45 +3949,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129044587</v>
+        <v>129039814</v>
       </c>
       <c r="B32" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491075</v>
+        <v>491102</v>
       </c>
       <c r="R32" t="n">
-        <v>6709943</v>
+        <v>6710142</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,7 +4024,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4029,7 +4034,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4056,32 +4061,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129044722</v>
+        <v>129039825</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4091,10 +4096,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491088</v>
+        <v>491126</v>
       </c>
       <c r="R33" t="n">
-        <v>6709977</v>
+        <v>6710148</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,7 +4131,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4136,12 +4141,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4168,50 +4168,59 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129038111</v>
+        <v>129041725</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490874</v>
+        <v>491375</v>
       </c>
       <c r="R34" t="n">
-        <v>6709885</v>
+        <v>6710101</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4243,7 +4252,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4253,12 +4262,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4285,45 +4289,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129040867</v>
+        <v>129040534</v>
       </c>
       <c r="B35" t="n">
-        <v>105741</v>
+        <v>91542</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491332</v>
+        <v>491261</v>
       </c>
       <c r="R35" t="n">
-        <v>6710175</v>
+        <v>6710156</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4355,7 +4359,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4365,7 +4369,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,50 +4396,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129039814</v>
+        <v>129044587</v>
       </c>
       <c r="B36" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491102</v>
+        <v>491075</v>
       </c>
       <c r="R36" t="n">
-        <v>6710142</v>
+        <v>6709943</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4467,7 +4466,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4477,7 +4476,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4504,32 +4503,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129039825</v>
+        <v>129044722</v>
       </c>
       <c r="B37" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4539,10 +4538,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491126</v>
+        <v>491088</v>
       </c>
       <c r="R37" t="n">
-        <v>6710148</v>
+        <v>6709977</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4574,7 +4573,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4584,7 +4583,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4611,59 +4615,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129041725</v>
+        <v>129038111</v>
       </c>
       <c r="B38" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491375</v>
+        <v>490874</v>
       </c>
       <c r="R38" t="n">
-        <v>6710101</v>
+        <v>6709885</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,7 +4690,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4705,7 +4700,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4732,53 +4732,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129038104</v>
+        <v>129044467</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490880</v>
+        <v>491036</v>
       </c>
       <c r="R39" t="n">
-        <v>6709882</v>
+        <v>6709945</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4810,7 +4802,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4820,12 +4812,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4852,10 +4839,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129040042</v>
+        <v>129038104</v>
       </c>
       <c r="B40" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4863,34 +4850,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491181</v>
+        <v>490880</v>
       </c>
       <c r="R40" t="n">
-        <v>6710144</v>
+        <v>6709882</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4922,7 +4917,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4932,7 +4927,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4959,32 +4959,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129044467</v>
+        <v>129045013</v>
       </c>
       <c r="B41" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491036</v>
+        <v>491157</v>
       </c>
       <c r="R41" t="n">
-        <v>6709945</v>
+        <v>6710121</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5066,10 +5066,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129045013</v>
+        <v>129040042</v>
       </c>
       <c r="B42" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491157</v>
+        <v>491181</v>
       </c>
       <c r="R42" t="n">
-        <v>6710121</v>
+        <v>6710144</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -8367,10 +8367,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129038053</v>
+        <v>129040356</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8378,39 +8378,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490886</v>
+        <v>491211</v>
       </c>
       <c r="R72" t="n">
-        <v>6709872</v>
+        <v>6710165</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8442,7 +8437,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8452,12 +8447,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>08:46</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8484,10 +8474,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129038223</v>
+        <v>129043183</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8495,39 +8485,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490878</v>
+        <v>491200</v>
       </c>
       <c r="R73" t="n">
-        <v>6709889</v>
+        <v>6709983</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8559,7 +8544,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8569,7 +8554,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8596,10 +8586,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129040356</v>
+        <v>129038053</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8607,34 +8597,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>491211</v>
+        <v>490886</v>
       </c>
       <c r="R74" t="n">
-        <v>6710165</v>
+        <v>6709872</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8666,7 +8661,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8676,7 +8671,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8703,10 +8703,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129043183</v>
+        <v>129038223</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8714,34 +8714,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>491200</v>
+        <v>490878</v>
       </c>
       <c r="R75" t="n">
-        <v>6709983</v>
+        <v>6709889</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8773,7 +8778,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8783,12 +8788,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9029,7 +9029,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129043352</v>
+        <v>129040173</v>
       </c>
       <c r="B78" t="n">
         <v>98678</v>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>491188</v>
+        <v>491201</v>
       </c>
       <c r="R78" t="n">
-        <v>6709988</v>
+        <v>6710139</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9136,7 +9136,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129040173</v>
+        <v>129039515</v>
       </c>
       <c r="B79" t="n">
         <v>98678</v>
@@ -9165,16 +9165,21 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>491201</v>
+        <v>491104</v>
       </c>
       <c r="R79" t="n">
-        <v>6710139</v>
+        <v>6710105</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9206,7 +9211,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9216,7 +9221,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9243,7 +9248,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129039515</v>
+        <v>129043352</v>
       </c>
       <c r="B80" t="n">
         <v>98678</v>
@@ -9272,21 +9277,16 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>491104</v>
+        <v>491188</v>
       </c>
       <c r="R80" t="n">
-        <v>6710105</v>
+        <v>6709988</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9355,50 +9355,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129042971</v>
+        <v>129038137</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>491193</v>
+        <v>490876</v>
       </c>
       <c r="R81" t="n">
-        <v>6710074</v>
+        <v>6709883</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9440,12 +9440,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9472,50 +9467,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129039011</v>
+        <v>129039994</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490936</v>
+        <v>491173</v>
       </c>
       <c r="R82" t="n">
-        <v>6709979</v>
+        <v>6710152</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9547,7 +9537,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9557,12 +9547,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9701,45 +9686,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129039994</v>
+        <v>129042971</v>
       </c>
       <c r="B84" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>491173</v>
+        <v>491193</v>
       </c>
       <c r="R84" t="n">
-        <v>6710152</v>
+        <v>6710074</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9771,7 +9761,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9781,7 +9771,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9808,50 +9803,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129038137</v>
+        <v>129039011</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490876</v>
+        <v>490936</v>
       </c>
       <c r="R85" t="n">
-        <v>6709883</v>
+        <v>6709979</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9883,7 +9878,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9893,7 +9888,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9920,45 +9920,59 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129040273</v>
+        <v>129039369</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>491210</v>
+        <v>491082</v>
       </c>
       <c r="R86" t="n">
-        <v>6710152</v>
+        <v>6710072</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9990,7 +10004,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10000,12 +10014,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10032,45 +10041,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129042243</v>
+        <v>129040090</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491324</v>
+        <v>491189</v>
       </c>
       <c r="R87" t="n">
-        <v>6710108</v>
+        <v>6710146</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10102,7 +10111,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10112,12 +10121,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10144,32 +10148,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129043457</v>
+        <v>129039427</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10179,10 +10183,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491159</v>
+        <v>491089</v>
       </c>
       <c r="R88" t="n">
-        <v>6709989</v>
+        <v>6710079</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10214,7 +10218,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10224,12 +10228,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10256,10 +10255,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129043286</v>
+        <v>129040273</v>
       </c>
       <c r="B89" t="n">
-        <v>91562</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10267,43 +10266,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491185</v>
+        <v>491210</v>
       </c>
       <c r="R89" t="n">
-        <v>6710038</v>
+        <v>6710152</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10335,7 +10325,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10345,7 +10335,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10372,45 +10367,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129045737</v>
+        <v>129042243</v>
       </c>
       <c r="B90" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491006</v>
+        <v>491324</v>
       </c>
       <c r="R90" t="n">
-        <v>6709889</v>
+        <v>6710108</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10442,7 +10437,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10452,7 +10447,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10479,32 +10479,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129039427</v>
+        <v>129043457</v>
       </c>
       <c r="B91" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491089</v>
+        <v>491159</v>
       </c>
       <c r="R91" t="n">
-        <v>6710079</v>
+        <v>6709989</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10559,7 +10559,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10586,32 +10591,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129039369</v>
+        <v>129043286</v>
       </c>
       <c r="B92" t="n">
-        <v>98678</v>
+        <v>91562</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10621,12 +10626,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491082</v>
+        <v>491185</v>
       </c>
       <c r="R92" t="n">
-        <v>6710072</v>
+        <v>6710038</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10707,32 +10707,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129040090</v>
+        <v>129045737</v>
       </c>
       <c r="B93" t="n">
-        <v>98678</v>
+        <v>92835</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10742,10 +10742,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491189</v>
+        <v>491006</v>
       </c>
       <c r="R93" t="n">
-        <v>6710146</v>
+        <v>6709889</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12146,32 +12146,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129039623</v>
+        <v>129042566</v>
       </c>
       <c r="B106" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12181,10 +12181,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491117</v>
+        <v>491288</v>
       </c>
       <c r="R106" t="n">
-        <v>6710091</v>
+        <v>6710104</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12253,32 +12253,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129039646</v>
+        <v>129044243</v>
       </c>
       <c r="B107" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491117</v>
+        <v>491026</v>
       </c>
       <c r="R107" t="n">
-        <v>6710091</v>
+        <v>6709889</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12333,12 +12333,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12365,54 +12360,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129039218</v>
+        <v>129039623</v>
       </c>
       <c r="B108" t="n">
-        <v>92835</v>
+        <v>91542</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491054</v>
+        <v>491117</v>
       </c>
       <c r="R108" t="n">
-        <v>6710041</v>
+        <v>6710091</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12444,7 +12430,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12454,7 +12440,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12481,32 +12467,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129042566</v>
+        <v>129039646</v>
       </c>
       <c r="B109" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12516,10 +12502,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491288</v>
+        <v>491117</v>
       </c>
       <c r="R109" t="n">
-        <v>6710104</v>
+        <v>6710091</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12551,7 +12537,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12561,7 +12547,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12588,45 +12579,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129044243</v>
+        <v>129039218</v>
       </c>
       <c r="B110" t="n">
-        <v>98678</v>
+        <v>92835</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491026</v>
+        <v>491054</v>
       </c>
       <c r="R110" t="n">
-        <v>6709889</v>
+        <v>6710041</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129042946</v>
+        <v>129039783</v>
       </c>
       <c r="B2" t="n">
-        <v>8450</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491232</v>
+        <v>491113</v>
       </c>
       <c r="R2" t="n">
-        <v>6710086</v>
+        <v>6710132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På 2 stående.</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129039226</v>
+        <v>129041992</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491060</v>
+        <v>491353</v>
       </c>
       <c r="R3" t="n">
-        <v>6710037</v>
+        <v>6710077</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129038956</v>
+        <v>129039226</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490939</v>
+        <v>491060</v>
       </c>
       <c r="R4" t="n">
-        <v>6709966</v>
+        <v>6710037</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129039783</v>
+        <v>129038956</v>
       </c>
       <c r="B5" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491113</v>
+        <v>490939</v>
       </c>
       <c r="R5" t="n">
-        <v>6710132</v>
+        <v>6709966</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,45 +1113,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129041992</v>
+        <v>129042946</v>
       </c>
       <c r="B6" t="n">
-        <v>91542</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491353</v>
+        <v>491232</v>
       </c>
       <c r="R6" t="n">
-        <v>6710077</v>
+        <v>6710086</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
         <v>129045855</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129041481</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129039748</v>
+        <v>129040305</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>75159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491113</v>
+        <v>491221</v>
       </c>
       <c r="R9" t="n">
-        <v>6710132</v>
+        <v>6710146</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,45 +1546,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129040305</v>
+        <v>129041053</v>
       </c>
       <c r="B10" t="n">
-        <v>75159</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491221</v>
+        <v>491309</v>
       </c>
       <c r="R10" t="n">
-        <v>6710146</v>
+        <v>6710192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1631,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,50 +1663,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129041053</v>
+        <v>129043673</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491309</v>
+        <v>491125</v>
       </c>
       <c r="R11" t="n">
-        <v>6710192</v>
+        <v>6709976</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,12 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,50 +1775,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129043673</v>
+        <v>129043484</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491125</v>
+        <v>491159</v>
       </c>
       <c r="R12" t="n">
-        <v>6709976</v>
+        <v>6709989</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129043484</v>
+        <v>129040595</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491159</v>
+        <v>491251</v>
       </c>
       <c r="R13" t="n">
-        <v>6709989</v>
+        <v>6710146</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129040595</v>
+        <v>129045778</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491251</v>
+        <v>491010</v>
       </c>
       <c r="R14" t="n">
-        <v>6710146</v>
+        <v>6709893</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129045778</v>
+        <v>129041291</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,14 +2127,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491010</v>
+        <v>491359</v>
       </c>
       <c r="R15" t="n">
-        <v>6709893</v>
+        <v>6710158</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,45 +2203,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129041291</v>
+        <v>129039748</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>92821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491359</v>
+        <v>491113</v>
       </c>
       <c r="R16" t="n">
-        <v>6710158</v>
+        <v>6710132</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,7 +2313,7 @@
         <v>129039950</v>
       </c>
       <c r="B17" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>129043063</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129044129</v>
+        <v>129037863</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>91992</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,21 +2652,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491049</v>
+        <v>490942</v>
       </c>
       <c r="R20" t="n">
-        <v>6709893</v>
+        <v>6709873</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,45 +2748,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129040685</v>
+        <v>129041584</v>
       </c>
       <c r="B21" t="n">
-        <v>92835</v>
+        <v>91560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491251</v>
+        <v>491362</v>
       </c>
       <c r="R21" t="n">
-        <v>6710146</v>
+        <v>6710143</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,32 +2855,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129037863</v>
+        <v>129040685</v>
       </c>
       <c r="B22" t="n">
-        <v>91997</v>
+        <v>92821</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490942</v>
+        <v>491251</v>
       </c>
       <c r="R22" t="n">
-        <v>6709873</v>
+        <v>6710146</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,45 +2962,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129041584</v>
+        <v>129040720</v>
       </c>
       <c r="B23" t="n">
-        <v>91562</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491362</v>
+        <v>491296</v>
       </c>
       <c r="R23" t="n">
-        <v>6710143</v>
+        <v>6710129</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,50 +3074,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129040720</v>
+        <v>129044129</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491296</v>
+        <v>491049</v>
       </c>
       <c r="R24" t="n">
-        <v>6710129</v>
+        <v>6709893</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,45 +3181,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129045240</v>
+        <v>129042527</v>
       </c>
       <c r="B25" t="n">
-        <v>91827</v>
+        <v>92821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491133</v>
+        <v>491296</v>
       </c>
       <c r="R25" t="n">
-        <v>6710118</v>
+        <v>6710104</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,7 +3260,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3270,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,42 +3297,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129042527</v>
+        <v>129040515</v>
       </c>
       <c r="B26" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3332,10 +3337,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491296</v>
+        <v>491251</v>
       </c>
       <c r="R26" t="n">
-        <v>6710104</v>
+        <v>6710165</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3372,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3377,7 +3382,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3404,50 +3414,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129040515</v>
+        <v>129045583</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491251</v>
+        <v>490946</v>
       </c>
       <c r="R27" t="n">
-        <v>6710165</v>
+        <v>6709935</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3479,7 +3484,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3489,12 +3494,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,10 +3521,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129045583</v>
+        <v>129043562</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490946</v>
+        <v>491129</v>
       </c>
       <c r="R28" t="n">
-        <v>6709935</v>
+        <v>6709987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3628,10 +3628,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129043562</v>
+        <v>129041242</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,14 +3659,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491129</v>
+        <v>491341</v>
       </c>
       <c r="R29" t="n">
-        <v>6709987</v>
+        <v>6710206</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,45 +3735,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129041242</v>
+        <v>129045240</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491341</v>
+        <v>491133</v>
       </c>
       <c r="R30" t="n">
-        <v>6710206</v>
+        <v>6710118</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,45 +3842,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129040867</v>
+        <v>129040534</v>
       </c>
       <c r="B31" t="n">
-        <v>105741</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491332</v>
+        <v>491261</v>
       </c>
       <c r="R31" t="n">
-        <v>6710175</v>
+        <v>6710156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,50 +3949,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129039814</v>
+        <v>129044587</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491102</v>
+        <v>491075</v>
       </c>
       <c r="R32" t="n">
-        <v>6710142</v>
+        <v>6709943</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4034,7 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4061,32 +4056,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129039825</v>
+        <v>129044722</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4096,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491126</v>
+        <v>491088</v>
       </c>
       <c r="R33" t="n">
-        <v>6710148</v>
+        <v>6709977</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4126,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4141,7 +4136,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4168,59 +4168,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129041725</v>
+        <v>129038111</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491375</v>
+        <v>490874</v>
       </c>
       <c r="R34" t="n">
-        <v>6710101</v>
+        <v>6709885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4252,7 +4243,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4262,7 +4253,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4289,45 +4285,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129040534</v>
+        <v>129040867</v>
       </c>
       <c r="B35" t="n">
-        <v>91542</v>
+        <v>105767</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491261</v>
+        <v>491332</v>
       </c>
       <c r="R35" t="n">
-        <v>6710156</v>
+        <v>6710175</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4359,7 +4355,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4369,7 +4365,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4396,45 +4392,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129044587</v>
+        <v>129039814</v>
       </c>
       <c r="B36" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491075</v>
+        <v>491102</v>
       </c>
       <c r="R36" t="n">
-        <v>6709943</v>
+        <v>6710142</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4466,7 +4467,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4476,7 +4477,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4503,32 +4504,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129044722</v>
+        <v>129039825</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4538,10 +4539,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491088</v>
+        <v>491126</v>
       </c>
       <c r="R37" t="n">
-        <v>6709977</v>
+        <v>6710148</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4573,7 +4574,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4583,12 +4584,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4615,50 +4611,59 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129038111</v>
+        <v>129041725</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490874</v>
+        <v>491375</v>
       </c>
       <c r="R38" t="n">
-        <v>6709885</v>
+        <v>6710101</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4690,7 +4695,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4700,12 +4705,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4732,32 +4732,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129044467</v>
+        <v>129045013</v>
       </c>
       <c r="B39" t="n">
-        <v>98678</v>
+        <v>91540</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491036</v>
+        <v>491157</v>
       </c>
       <c r="R39" t="n">
-        <v>6709945</v>
+        <v>6710121</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,10 +4839,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129038104</v>
+        <v>129040042</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>91837</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4850,42 +4850,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490880</v>
+        <v>491181</v>
       </c>
       <c r="R40" t="n">
-        <v>6709882</v>
+        <v>6710144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4917,7 +4909,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4927,12 +4919,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4959,10 +4946,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129045013</v>
+        <v>129038104</v>
       </c>
       <c r="B41" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,34 +4957,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491157</v>
+        <v>490880</v>
       </c>
       <c r="R41" t="n">
-        <v>6710121</v>
+        <v>6709882</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5029,7 +5024,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5039,7 +5034,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5066,32 +5066,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129040042</v>
+        <v>129044467</v>
       </c>
       <c r="B42" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491181</v>
+        <v>491036</v>
       </c>
       <c r="R42" t="n">
-        <v>6710144</v>
+        <v>6709945</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5176,7 +5176,7 @@
         <v>129044319</v>
       </c>
       <c r="B43" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>129041044</v>
       </c>
       <c r="B44" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,45 +5504,59 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129037802</v>
+        <v>129039795</v>
       </c>
       <c r="B46" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490941</v>
+        <v>491106</v>
       </c>
       <c r="R46" t="n">
-        <v>6709886</v>
+        <v>6710124</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5574,7 +5588,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5584,7 +5598,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5611,10 +5625,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129039795</v>
+        <v>129042338</v>
       </c>
       <c r="B47" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5646,24 +5660,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491106</v>
+        <v>491335</v>
       </c>
       <c r="R47" t="n">
-        <v>6710124</v>
+        <v>6710120</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5695,7 +5709,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5705,7 +5719,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5732,59 +5751,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129042338</v>
+        <v>129037802</v>
       </c>
       <c r="B48" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491335</v>
+        <v>490941</v>
       </c>
       <c r="R48" t="n">
-        <v>6710120</v>
+        <v>6709886</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5816,7 +5821,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5826,12 +5831,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5861,7 +5861,7 @@
         <v>129038812</v>
       </c>
       <c r="B49" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>129044332</v>
       </c>
       <c r="B50" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>129045046</v>
       </c>
       <c r="B51" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>129039883</v>
       </c>
       <c r="B52" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6295,50 +6295,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129038692</v>
+        <v>129044552</v>
       </c>
       <c r="B53" t="n">
-        <v>57887</v>
+        <v>98704</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490892</v>
+        <v>491075</v>
       </c>
       <c r="R53" t="n">
-        <v>6709919</v>
+        <v>6709942</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6370,7 +6365,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6380,7 +6375,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6407,10 +6402,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129044552</v>
+        <v>129040369</v>
       </c>
       <c r="B54" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6442,10 +6437,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>491075</v>
+        <v>491194</v>
       </c>
       <c r="R54" t="n">
-        <v>6709942</v>
+        <v>6710167</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6477,7 +6472,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6487,7 +6482,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6514,45 +6509,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129040369</v>
+        <v>129038692</v>
       </c>
       <c r="B55" t="n">
-        <v>98678</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>491194</v>
+        <v>490892</v>
       </c>
       <c r="R55" t="n">
-        <v>6710167</v>
+        <v>6709919</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6621,32 +6621,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129038411</v>
+        <v>129037776</v>
       </c>
       <c r="B56" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490873</v>
+        <v>490952</v>
       </c>
       <c r="R56" t="n">
-        <v>6709909</v>
+        <v>6709889</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129044061</v>
+        <v>129038411</v>
       </c>
       <c r="B57" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>491110</v>
+        <v>490873</v>
       </c>
       <c r="R57" t="n">
-        <v>6709915</v>
+        <v>6709909</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,10 +6835,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129045420</v>
+        <v>129044061</v>
       </c>
       <c r="B58" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491009</v>
+        <v>491110</v>
       </c>
       <c r="R58" t="n">
-        <v>6709991</v>
+        <v>6709915</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,10 +6942,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129038173</v>
+        <v>129045420</v>
       </c>
       <c r="B59" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,31 +6970,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490877</v>
+        <v>491009</v>
       </c>
       <c r="R59" t="n">
-        <v>6709889</v>
+        <v>6709991</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7026,7 +7012,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7036,7 +7022,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7063,10 +7049,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129043992</v>
+        <v>129038173</v>
       </c>
       <c r="B60" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7091,17 +7077,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>491095</v>
+        <v>490877</v>
       </c>
       <c r="R60" t="n">
-        <v>6709906</v>
+        <v>6709889</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7170,32 +7170,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129039941</v>
+        <v>129043992</v>
       </c>
       <c r="B61" t="n">
-        <v>91542</v>
+        <v>98704</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>491158</v>
+        <v>491095</v>
       </c>
       <c r="R61" t="n">
-        <v>6710160</v>
+        <v>6709906</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7280,7 +7280,7 @@
         <v>129040007</v>
       </c>
       <c r="B62" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7384,10 +7384,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129037776</v>
+        <v>129039941</v>
       </c>
       <c r="B63" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7395,21 +7395,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490952</v>
+        <v>491158</v>
       </c>
       <c r="R63" t="n">
-        <v>6709889</v>
+        <v>6710160</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7491,10 +7491,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129042106</v>
+        <v>129037762</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7502,21 +7502,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>491327</v>
+        <v>490949</v>
       </c>
       <c r="R64" t="n">
-        <v>6710067</v>
+        <v>6709885</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7571,12 +7571,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7603,10 +7598,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129037762</v>
+        <v>129042106</v>
       </c>
       <c r="B65" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7614,21 +7609,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7638,10 +7633,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490949</v>
+        <v>491327</v>
       </c>
       <c r="R65" t="n">
-        <v>6709885</v>
+        <v>6710067</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7673,7 +7668,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7683,7 +7678,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7713,7 +7713,7 @@
         <v>129039716</v>
       </c>
       <c r="B66" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>129044189</v>
       </c>
       <c r="B67" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>129043659</v>
       </c>
       <c r="B68" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>129045555</v>
       </c>
       <c r="B69" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>129039681</v>
       </c>
       <c r="B70" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>129038944</v>
       </c>
       <c r="B71" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8367,32 +8367,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129040356</v>
+        <v>129042724</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>92857</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>491211</v>
+        <v>491257</v>
       </c>
       <c r="R72" t="n">
-        <v>6710165</v>
+        <v>6710085</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8815,32 +8815,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129042724</v>
+        <v>129040051</v>
       </c>
       <c r="B76" t="n">
-        <v>92871</v>
+        <v>98704</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8850,10 +8850,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>491257</v>
+        <v>491183</v>
       </c>
       <c r="R76" t="n">
-        <v>6710085</v>
+        <v>6710141</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8922,32 +8922,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129040051</v>
+        <v>129040356</v>
       </c>
       <c r="B77" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8957,10 +8957,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>491183</v>
+        <v>491211</v>
       </c>
       <c r="R77" t="n">
-        <v>6710141</v>
+        <v>6710165</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9032,7 +9032,7 @@
         <v>129040173</v>
       </c>
       <c r="B78" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>129039515</v>
       </c>
       <c r="B79" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>129043352</v>
       </c>
       <c r="B80" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9355,50 +9355,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129038137</v>
+        <v>129044818</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490876</v>
+        <v>491116</v>
       </c>
       <c r="R81" t="n">
-        <v>6709883</v>
+        <v>6710020</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9430,7 +9425,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9440,7 +9435,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9467,45 +9467,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129039994</v>
+        <v>129042971</v>
       </c>
       <c r="B82" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>491173</v>
+        <v>491193</v>
       </c>
       <c r="R82" t="n">
-        <v>6710152</v>
+        <v>6710074</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9537,7 +9542,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9547,7 +9552,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9574,10 +9584,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129044818</v>
+        <v>129039011</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9585,34 +9595,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>491116</v>
+        <v>490936</v>
       </c>
       <c r="R83" t="n">
-        <v>6710020</v>
+        <v>6709979</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9644,7 +9659,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9654,12 +9669,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9686,50 +9701,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129042971</v>
+        <v>129038137</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>491193</v>
+        <v>490876</v>
       </c>
       <c r="R84" t="n">
-        <v>6710074</v>
+        <v>6709883</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9761,7 +9776,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9771,12 +9786,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9803,50 +9813,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129039011</v>
+        <v>129039994</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>490936</v>
+        <v>491173</v>
       </c>
       <c r="R85" t="n">
-        <v>6709979</v>
+        <v>6710152</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9878,7 +9883,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9888,12 +9893,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9920,59 +9920,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129039369</v>
+        <v>129045737</v>
       </c>
       <c r="B86" t="n">
-        <v>98678</v>
+        <v>92821</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>491082</v>
+        <v>491006</v>
       </c>
       <c r="R86" t="n">
-        <v>6710072</v>
+        <v>6709889</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10004,7 +9990,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10014,7 +10000,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10041,32 +10027,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129040090</v>
+        <v>129043457</v>
       </c>
       <c r="B87" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10076,10 +10062,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491189</v>
+        <v>491159</v>
       </c>
       <c r="R87" t="n">
-        <v>6710146</v>
+        <v>6709989</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10111,7 +10097,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10121,7 +10107,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10151,7 +10142,7 @@
         <v>129039427</v>
       </c>
       <c r="B88" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10255,45 +10246,59 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129040273</v>
+        <v>129039369</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491210</v>
+        <v>491082</v>
       </c>
       <c r="R89" t="n">
-        <v>6710152</v>
+        <v>6710072</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10325,7 +10330,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10335,12 +10340,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10367,45 +10367,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129042243</v>
+        <v>129040090</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491324</v>
+        <v>491189</v>
       </c>
       <c r="R90" t="n">
-        <v>6710108</v>
+        <v>6710146</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10447,12 +10447,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10479,10 +10474,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129043457</v>
+        <v>129043286</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10490,34 +10485,43 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491159</v>
+        <v>491185</v>
       </c>
       <c r="R91" t="n">
-        <v>6709989</v>
+        <v>6710038</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10549,7 +10553,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10559,12 +10563,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10591,10 +10590,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129043286</v>
+        <v>129040273</v>
       </c>
       <c r="B92" t="n">
-        <v>91562</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10602,43 +10601,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491185</v>
+        <v>491210</v>
       </c>
       <c r="R92" t="n">
-        <v>6710038</v>
+        <v>6710152</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10670,7 +10660,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10680,7 +10670,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10707,45 +10702,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129045737</v>
+        <v>129042243</v>
       </c>
       <c r="B93" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491006</v>
+        <v>491324</v>
       </c>
       <c r="R93" t="n">
-        <v>6709889</v>
+        <v>6710108</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10777,7 +10772,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10787,7 +10782,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10814,45 +10814,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129043344</v>
+        <v>129041444</v>
       </c>
       <c r="B94" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491176</v>
+        <v>491362</v>
       </c>
       <c r="R94" t="n">
-        <v>6710019</v>
+        <v>6710150</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10884,7 +10889,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10894,7 +10899,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10921,10 +10931,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129044713</v>
+        <v>129043344</v>
       </c>
       <c r="B95" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10956,10 +10966,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491086</v>
+        <v>491176</v>
       </c>
       <c r="R95" t="n">
-        <v>6709974</v>
+        <v>6710019</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10991,7 +11001,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11001,7 +11011,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11028,10 +11038,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129044360</v>
+        <v>129044713</v>
       </c>
       <c r="B96" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11063,10 +11073,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491050</v>
+        <v>491086</v>
       </c>
       <c r="R96" t="n">
-        <v>6709915</v>
+        <v>6709974</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11098,7 +11108,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11108,7 +11118,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11135,10 +11145,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129041232</v>
+        <v>129044360</v>
       </c>
       <c r="B97" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11164,21 +11174,16 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491336</v>
+        <v>491050</v>
       </c>
       <c r="R97" t="n">
-        <v>6710188</v>
+        <v>6709915</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11210,7 +11215,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11220,7 +11225,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11247,10 +11252,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129045097</v>
+        <v>129041232</v>
       </c>
       <c r="B98" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11283,14 +11288,14 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491132</v>
+        <v>491336</v>
       </c>
       <c r="R98" t="n">
-        <v>6710123</v>
+        <v>6710188</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11322,7 +11327,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11332,12 +11337,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11364,45 +11364,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129041984</v>
+        <v>129045097</v>
       </c>
       <c r="B99" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491353</v>
+        <v>491132</v>
       </c>
       <c r="R99" t="n">
-        <v>6710077</v>
+        <v>6710123</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11434,7 +11439,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11444,7 +11449,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11471,10 +11481,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129041444</v>
+        <v>129041984</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>91837</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11482,39 +11492,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491362</v>
+        <v>491353</v>
       </c>
       <c r="R100" t="n">
-        <v>6710150</v>
+        <v>6710077</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11546,7 +11551,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11556,12 +11561,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11588,10 +11588,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129043760</v>
+        <v>129044617</v>
       </c>
       <c r="B101" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11623,10 +11623,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491096</v>
+        <v>491091</v>
       </c>
       <c r="R101" t="n">
-        <v>6709954</v>
+        <v>6709950</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11695,50 +11695,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129038846</v>
+        <v>129043760</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>490903</v>
+        <v>491096</v>
       </c>
       <c r="R102" t="n">
-        <v>6709932</v>
+        <v>6709954</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11770,7 +11765,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11780,12 +11775,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11812,10 +11802,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129045506</v>
+        <v>129040149</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11823,42 +11813,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490975</v>
+        <v>491192</v>
       </c>
       <c r="R103" t="n">
-        <v>6709983</v>
+        <v>6710147</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11890,7 +11872,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11900,12 +11882,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Bohål i gran, på ca 2m.</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11932,45 +11909,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129044617</v>
+        <v>129038846</v>
       </c>
       <c r="B104" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491091</v>
+        <v>490903</v>
       </c>
       <c r="R104" t="n">
-        <v>6709950</v>
+        <v>6709932</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12002,7 +11984,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12012,7 +11994,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12039,10 +12026,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129040149</v>
+        <v>129045506</v>
       </c>
       <c r="B105" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12050,34 +12037,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491192</v>
+        <v>490975</v>
       </c>
       <c r="R105" t="n">
-        <v>6710147</v>
+        <v>6709983</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12109,7 +12104,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12119,7 +12114,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Bohål i gran, på ca 2m.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12149,7 +12149,7 @@
         <v>129042566</v>
       </c>
       <c r="B106" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>129044243</v>
       </c>
       <c r="B107" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12360,10 +12360,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129039623</v>
+        <v>129039646</v>
       </c>
       <c r="B108" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12371,21 +12371,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12430,7 +12430,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12440,7 +12440,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12467,10 +12472,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129039646</v>
+        <v>129039623</v>
       </c>
       <c r="B109" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12478,21 +12483,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12537,7 +12542,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12547,12 +12552,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12582,7 +12582,7 @@
         <v>129039218</v>
       </c>
       <c r="B110" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129039783</v>
+        <v>129045855</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491113</v>
+        <v>491030</v>
       </c>
       <c r="R2" t="n">
-        <v>6710132</v>
+        <v>6709895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129041992</v>
+        <v>129042946</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491353</v>
+        <v>491232</v>
       </c>
       <c r="R3" t="n">
-        <v>6710077</v>
+        <v>6710086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129039226</v>
+        <v>129041481</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491060</v>
+        <v>491361</v>
       </c>
       <c r="R4" t="n">
-        <v>6710037</v>
+        <v>6710143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,32 +1118,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129042946</v>
+        <v>129039783</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491232</v>
+        <v>491113</v>
       </c>
       <c r="R6" t="n">
-        <v>6710086</v>
+        <v>6710132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,12 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På 2 stående.</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,45 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129045855</v>
+        <v>129041992</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491030</v>
+        <v>491353</v>
       </c>
       <c r="R7" t="n">
-        <v>6709895</v>
+        <v>6710077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,45 +1332,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129041481</v>
+        <v>129039226</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>92822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491361</v>
+        <v>491060</v>
       </c>
       <c r="R8" t="n">
-        <v>6710143</v>
+        <v>6710037</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129043484</v>
+        <v>129040595</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491159</v>
+        <v>491251</v>
       </c>
       <c r="R12" t="n">
-        <v>6709989</v>
+        <v>6710146</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129040595</v>
+        <v>129045778</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491251</v>
+        <v>491010</v>
       </c>
       <c r="R13" t="n">
-        <v>6710146</v>
+        <v>6709893</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129045778</v>
+        <v>129041291</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2020,14 +2020,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491010</v>
+        <v>491359</v>
       </c>
       <c r="R14" t="n">
-        <v>6709893</v>
+        <v>6710158</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,45 +2096,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129041291</v>
+        <v>129039748</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>92822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491359</v>
+        <v>491113</v>
       </c>
       <c r="R15" t="n">
-        <v>6710158</v>
+        <v>6710132</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,32 +2203,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129039748</v>
+        <v>129043484</v>
       </c>
       <c r="B16" t="n">
-        <v>92821</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491113</v>
+        <v>491159</v>
       </c>
       <c r="R16" t="n">
-        <v>6710132</v>
+        <v>6709989</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,7 +2313,7 @@
         <v>129039950</v>
       </c>
       <c r="B17" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>129043063</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>129037863</v>
       </c>
       <c r="B20" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>129041584</v>
       </c>
       <c r="B21" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129040685</v>
       </c>
       <c r="B22" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>129044129</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,54 +3181,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129042527</v>
+        <v>129045583</v>
       </c>
       <c r="B25" t="n">
-        <v>92821</v>
+        <v>98705</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491296</v>
+        <v>490946</v>
       </c>
       <c r="R25" t="n">
-        <v>6710104</v>
+        <v>6709935</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3260,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3270,7 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3297,50 +3288,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129040515</v>
+        <v>129043562</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491251</v>
+        <v>491129</v>
       </c>
       <c r="R26" t="n">
-        <v>6710165</v>
+        <v>6709987</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,7 +3358,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3382,12 +3368,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129045583</v>
+        <v>129041242</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3445,14 +3426,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490946</v>
+        <v>491341</v>
       </c>
       <c r="R27" t="n">
-        <v>6709935</v>
+        <v>6710206</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3484,7 +3465,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3494,7 +3475,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,32 +3502,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129043562</v>
+        <v>129045240</v>
       </c>
       <c r="B28" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3556,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491129</v>
+        <v>491133</v>
       </c>
       <c r="R28" t="n">
-        <v>6709987</v>
+        <v>6710118</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3601,7 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3628,45 +3609,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129041242</v>
+        <v>129042527</v>
       </c>
       <c r="B29" t="n">
-        <v>98704</v>
+        <v>92822</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491341</v>
+        <v>491296</v>
       </c>
       <c r="R29" t="n">
-        <v>6710206</v>
+        <v>6710104</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3688,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3698,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,10 +3725,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129045240</v>
+        <v>129040515</v>
       </c>
       <c r="B30" t="n">
-        <v>91837</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,34 +3736,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491133</v>
+        <v>491251</v>
       </c>
       <c r="R30" t="n">
-        <v>6710118</v>
+        <v>6710165</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3800,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3810,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,45 +3842,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129040534</v>
+        <v>129039814</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491261</v>
+        <v>491102</v>
       </c>
       <c r="R31" t="n">
-        <v>6710156</v>
+        <v>6710142</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3917,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3927,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,32 +3954,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129044587</v>
+        <v>129039825</v>
       </c>
       <c r="B32" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491075</v>
+        <v>491126</v>
       </c>
       <c r="R32" t="n">
-        <v>6709943</v>
+        <v>6710148</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,7 +4024,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4029,7 +4034,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4056,10 +4061,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129044722</v>
+        <v>129038111</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,34 +4072,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491088</v>
+        <v>490874</v>
       </c>
       <c r="R33" t="n">
-        <v>6709977</v>
+        <v>6709885</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,7 +4136,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4136,12 +4146,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4168,10 +4178,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129038111</v>
+        <v>129044587</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4179,39 +4189,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490874</v>
+        <v>491075</v>
       </c>
       <c r="R34" t="n">
-        <v>6709885</v>
+        <v>6709943</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4243,7 +4248,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4253,12 +4258,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4285,45 +4285,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129040867</v>
+        <v>129040534</v>
       </c>
       <c r="B35" t="n">
-        <v>105767</v>
+        <v>91540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491332</v>
+        <v>491261</v>
       </c>
       <c r="R35" t="n">
-        <v>6710175</v>
+        <v>6710156</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,50 +4392,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129039814</v>
+        <v>129044722</v>
       </c>
       <c r="B36" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491102</v>
+        <v>491088</v>
       </c>
       <c r="R36" t="n">
-        <v>6710142</v>
+        <v>6709977</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4467,7 +4462,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4477,7 +4472,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4504,45 +4504,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129039825</v>
+        <v>129040867</v>
       </c>
       <c r="B37" t="n">
-        <v>98704</v>
+        <v>105769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491126</v>
+        <v>491332</v>
       </c>
       <c r="R37" t="n">
-        <v>6710148</v>
+        <v>6710175</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4614,7 +4614,7 @@
         <v>129041725</v>
       </c>
       <c r="B38" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>129040042</v>
       </c>
       <c r="B40" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4946,53 +4946,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129038104</v>
+        <v>129044467</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490880</v>
+        <v>491036</v>
       </c>
       <c r="R41" t="n">
-        <v>6709882</v>
+        <v>6709945</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5024,7 +5016,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5034,12 +5026,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5066,45 +5053,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129044467</v>
+        <v>129038104</v>
       </c>
       <c r="B42" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491036</v>
+        <v>490880</v>
       </c>
       <c r="R42" t="n">
-        <v>6709945</v>
+        <v>6709882</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5136,7 +5131,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5146,7 +5141,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5283,7 +5283,7 @@
         <v>129041044</v>
       </c>
       <c r="B44" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>129039795</v>
       </c>
       <c r="B46" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>129042338</v>
       </c>
       <c r="B47" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>129037802</v>
       </c>
       <c r="B48" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5858,54 +5858,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129038812</v>
+        <v>129045046</v>
       </c>
       <c r="B49" t="n">
-        <v>92821</v>
+        <v>98705</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490918</v>
+        <v>491153</v>
       </c>
       <c r="R49" t="n">
-        <v>6709933</v>
+        <v>6710121</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5937,7 +5928,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5947,7 +5938,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5974,45 +5965,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129044332</v>
+        <v>129038812</v>
       </c>
       <c r="B50" t="n">
-        <v>98704</v>
+        <v>92822</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491049</v>
+        <v>490918</v>
       </c>
       <c r="R50" t="n">
-        <v>6709914</v>
+        <v>6709933</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6081,10 +6081,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129045046</v>
+        <v>129044332</v>
       </c>
       <c r="B51" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>491153</v>
+        <v>491049</v>
       </c>
       <c r="R51" t="n">
-        <v>6710121</v>
+        <v>6709914</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6191,7 +6191,7 @@
         <v>129039883</v>
       </c>
       <c r="B52" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>129044552</v>
       </c>
       <c r="B53" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>129040369</v>
       </c>
       <c r="B54" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>129037776</v>
       </c>
       <c r="B56" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6728,32 +6728,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129038411</v>
+        <v>129040007</v>
       </c>
       <c r="B57" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490873</v>
+        <v>491180</v>
       </c>
       <c r="R57" t="n">
-        <v>6709909</v>
+        <v>6710139</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6835,32 +6835,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129044061</v>
+        <v>129039941</v>
       </c>
       <c r="B58" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491110</v>
+        <v>491158</v>
       </c>
       <c r="R58" t="n">
-        <v>6709915</v>
+        <v>6710160</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,10 +6942,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129045420</v>
+        <v>129044061</v>
       </c>
       <c r="B59" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>491009</v>
+        <v>491110</v>
       </c>
       <c r="R59" t="n">
-        <v>6709991</v>
+        <v>6709915</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7049,10 +7049,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129038173</v>
+        <v>129045420</v>
       </c>
       <c r="B60" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7077,31 +7077,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490877</v>
+        <v>491009</v>
       </c>
       <c r="R60" t="n">
-        <v>6709889</v>
+        <v>6709991</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7133,7 +7119,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7143,7 +7129,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7173,7 +7159,7 @@
         <v>129043992</v>
       </c>
       <c r="B61" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7277,32 +7263,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129040007</v>
+        <v>129038411</v>
       </c>
       <c r="B62" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7312,10 +7298,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>491180</v>
+        <v>490873</v>
       </c>
       <c r="R62" t="n">
-        <v>6710139</v>
+        <v>6709909</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7347,7 +7333,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7357,7 +7343,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7384,45 +7370,59 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129039941</v>
+        <v>129038173</v>
       </c>
       <c r="B63" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>491158</v>
+        <v>490877</v>
       </c>
       <c r="R63" t="n">
-        <v>6710160</v>
+        <v>6709889</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7710,10 +7710,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129039716</v>
+        <v>129044189</v>
       </c>
       <c r="B66" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7739,21 +7739,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491118</v>
+        <v>491025</v>
       </c>
       <c r="R66" t="n">
-        <v>6710111</v>
+        <v>6709886</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7785,7 +7780,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7795,12 +7790,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7827,10 +7817,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129044189</v>
+        <v>129043659</v>
       </c>
       <c r="B67" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7862,10 +7852,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>491025</v>
+        <v>491126</v>
       </c>
       <c r="R67" t="n">
-        <v>6709886</v>
+        <v>6709977</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7897,7 +7887,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7907,7 +7897,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7934,10 +7924,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129043659</v>
+        <v>129045555</v>
       </c>
       <c r="B68" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7969,10 +7959,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>491126</v>
+        <v>490955</v>
       </c>
       <c r="R68" t="n">
-        <v>6709977</v>
+        <v>6709969</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8004,7 +7994,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8014,7 +8004,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8041,10 +8031,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129045555</v>
+        <v>129039716</v>
       </c>
       <c r="B69" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8070,16 +8060,21 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490955</v>
+        <v>491118</v>
       </c>
       <c r="R69" t="n">
-        <v>6709969</v>
+        <v>6710111</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8111,7 +8106,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8121,7 +8116,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8151,7 +8151,7 @@
         <v>129039681</v>
       </c>
       <c r="B70" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>129038944</v>
       </c>
       <c r="B71" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8367,32 +8367,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129042724</v>
+        <v>129040356</v>
       </c>
       <c r="B72" t="n">
-        <v>92857</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>491257</v>
+        <v>491211</v>
       </c>
       <c r="R72" t="n">
-        <v>6710085</v>
+        <v>6710165</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8474,10 +8474,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129043183</v>
+        <v>129038053</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8485,34 +8485,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>491200</v>
+        <v>490886</v>
       </c>
       <c r="R73" t="n">
-        <v>6709983</v>
+        <v>6709872</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8544,7 +8549,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8554,12 +8559,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8586,10 +8591,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129038053</v>
+        <v>129043183</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8597,39 +8602,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490886</v>
+        <v>491200</v>
       </c>
       <c r="R74" t="n">
-        <v>6709872</v>
+        <v>6709983</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8703,50 +8703,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129038223</v>
+        <v>129042724</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>92858</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>490878</v>
+        <v>491257</v>
       </c>
       <c r="R75" t="n">
-        <v>6709889</v>
+        <v>6710085</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8778,7 +8773,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8788,7 +8783,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8815,45 +8810,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129040051</v>
+        <v>129038223</v>
       </c>
       <c r="B76" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>491183</v>
+        <v>490878</v>
       </c>
       <c r="R76" t="n">
-        <v>6710141</v>
+        <v>6709889</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8922,32 +8922,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129040356</v>
+        <v>129040051</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8957,10 +8957,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>491211</v>
+        <v>491183</v>
       </c>
       <c r="R77" t="n">
-        <v>6710165</v>
+        <v>6710141</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9029,10 +9029,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129040173</v>
+        <v>129043352</v>
       </c>
       <c r="B78" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>491201</v>
+        <v>491188</v>
       </c>
       <c r="R78" t="n">
-        <v>6710139</v>
+        <v>6709988</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9136,10 +9136,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129039515</v>
+        <v>129040173</v>
       </c>
       <c r="B79" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9165,21 +9165,16 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>491104</v>
+        <v>491201</v>
       </c>
       <c r="R79" t="n">
-        <v>6710105</v>
+        <v>6710139</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9211,7 +9206,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9221,7 +9216,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9248,10 +9243,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129043352</v>
+        <v>129039515</v>
       </c>
       <c r="B80" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9277,16 +9272,21 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>491188</v>
+        <v>491104</v>
       </c>
       <c r="R80" t="n">
-        <v>6709988</v>
+        <v>6710105</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9816,7 +9816,7 @@
         <v>129039994</v>
       </c>
       <c r="B85" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>129045737</v>
       </c>
       <c r="B86" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10027,10 +10027,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129043457</v>
+        <v>129043286</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>91561</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10038,34 +10038,43 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491159</v>
+        <v>491185</v>
       </c>
       <c r="R87" t="n">
-        <v>6709989</v>
+        <v>6710038</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10097,7 +10106,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10107,12 +10116,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10139,32 +10143,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129039427</v>
+        <v>129040273</v>
       </c>
       <c r="B88" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10174,10 +10178,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491089</v>
+        <v>491210</v>
       </c>
       <c r="R88" t="n">
-        <v>6710079</v>
+        <v>6710152</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10209,7 +10213,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10219,7 +10223,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10246,59 +10255,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129039369</v>
+        <v>129042243</v>
       </c>
       <c r="B89" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491082</v>
+        <v>491324</v>
       </c>
       <c r="R89" t="n">
-        <v>6710072</v>
+        <v>6710108</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10330,7 +10325,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10340,7 +10335,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10367,32 +10367,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129040090</v>
+        <v>129043457</v>
       </c>
       <c r="B90" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10402,10 +10402,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491189</v>
+        <v>491159</v>
       </c>
       <c r="R90" t="n">
-        <v>6710146</v>
+        <v>6709989</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10447,7 +10447,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10474,32 +10479,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129043286</v>
+        <v>129039369</v>
       </c>
       <c r="B91" t="n">
-        <v>91560</v>
+        <v>98705</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10509,7 +10514,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10518,10 +10528,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491185</v>
+        <v>491082</v>
       </c>
       <c r="R91" t="n">
-        <v>6710038</v>
+        <v>6710072</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10553,7 +10563,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10563,7 +10573,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10590,32 +10600,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129040273</v>
+        <v>129040090</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10625,10 +10635,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491210</v>
+        <v>491189</v>
       </c>
       <c r="R92" t="n">
-        <v>6710152</v>
+        <v>6710146</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10660,7 +10670,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10670,12 +10680,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10702,45 +10707,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129042243</v>
+        <v>129039427</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491324</v>
+        <v>491089</v>
       </c>
       <c r="R93" t="n">
-        <v>6710108</v>
+        <v>6710079</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10772,7 +10777,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10782,12 +10787,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10814,10 +10814,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129041444</v>
+        <v>129041984</v>
       </c>
       <c r="B94" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10825,39 +10825,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491362</v>
+        <v>491353</v>
       </c>
       <c r="R94" t="n">
-        <v>6710150</v>
+        <v>6710077</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10889,7 +10884,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10899,12 +10894,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10931,10 +10921,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129043344</v>
+        <v>129044713</v>
       </c>
       <c r="B95" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10966,10 +10956,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491176</v>
+        <v>491086</v>
       </c>
       <c r="R95" t="n">
-        <v>6710019</v>
+        <v>6709974</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11001,7 +10991,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11011,7 +11001,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11038,10 +11028,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129044713</v>
+        <v>129045097</v>
       </c>
       <c r="B96" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11067,16 +11057,21 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491086</v>
+        <v>491132</v>
       </c>
       <c r="R96" t="n">
-        <v>6709974</v>
+        <v>6710123</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11108,7 +11103,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11118,7 +11113,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11145,45 +11145,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129044360</v>
+        <v>129041444</v>
       </c>
       <c r="B97" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491050</v>
+        <v>491362</v>
       </c>
       <c r="R97" t="n">
-        <v>6709915</v>
+        <v>6710150</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11215,7 +11220,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11225,7 +11230,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11252,10 +11262,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129041232</v>
+        <v>129043344</v>
       </c>
       <c r="B98" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11281,21 +11291,16 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491336</v>
+        <v>491176</v>
       </c>
       <c r="R98" t="n">
-        <v>6710188</v>
+        <v>6710019</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11327,7 +11332,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11337,7 +11342,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11364,10 +11369,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129045097</v>
+        <v>129044360</v>
       </c>
       <c r="B99" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11393,21 +11398,16 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491132</v>
+        <v>491050</v>
       </c>
       <c r="R99" t="n">
-        <v>6710123</v>
+        <v>6709915</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11449,12 +11449,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11481,45 +11476,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129041984</v>
+        <v>129041232</v>
       </c>
       <c r="B100" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491353</v>
+        <v>491336</v>
       </c>
       <c r="R100" t="n">
-        <v>6710077</v>
+        <v>6710188</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11588,45 +11588,53 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129044617</v>
+        <v>129045506</v>
       </c>
       <c r="B101" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491091</v>
+        <v>490975</v>
       </c>
       <c r="R101" t="n">
-        <v>6709950</v>
+        <v>6709983</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11658,7 +11666,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11668,7 +11676,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Bohål i gran, på ca 2m.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11695,32 +11708,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129043760</v>
+        <v>129040149</v>
       </c>
       <c r="B102" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11730,10 +11743,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491096</v>
+        <v>491192</v>
       </c>
       <c r="R102" t="n">
-        <v>6709954</v>
+        <v>6710147</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11765,7 +11778,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11775,7 +11788,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11802,10 +11815,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129040149</v>
+        <v>129038846</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11813,34 +11826,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491192</v>
+        <v>490903</v>
       </c>
       <c r="R103" t="n">
-        <v>6710147</v>
+        <v>6709932</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11872,7 +11890,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11882,7 +11900,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11909,50 +11932,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129038846</v>
+        <v>129044617</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490903</v>
+        <v>491091</v>
       </c>
       <c r="R104" t="n">
-        <v>6709932</v>
+        <v>6709950</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11984,7 +12002,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11994,12 +12012,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12026,53 +12039,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129045506</v>
+        <v>129043760</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490975</v>
+        <v>491096</v>
       </c>
       <c r="R105" t="n">
-        <v>6709983</v>
+        <v>6709954</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12104,7 +12109,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12114,12 +12119,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Bohål i gran, på ca 2m.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12146,32 +12146,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129042566</v>
+        <v>129039623</v>
       </c>
       <c r="B106" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12181,10 +12181,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491288</v>
+        <v>491117</v>
       </c>
       <c r="R106" t="n">
-        <v>6710104</v>
+        <v>6710091</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12253,32 +12253,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129044243</v>
+        <v>129039646</v>
       </c>
       <c r="B107" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491026</v>
+        <v>491117</v>
       </c>
       <c r="R107" t="n">
-        <v>6709889</v>
+        <v>6710091</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12333,7 +12333,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12360,32 +12365,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129039646</v>
+        <v>129044243</v>
       </c>
       <c r="B108" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12395,10 +12400,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491117</v>
+        <v>491026</v>
       </c>
       <c r="R108" t="n">
-        <v>6710091</v>
+        <v>6709889</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12430,7 +12435,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12440,12 +12445,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12472,45 +12472,54 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129039623</v>
+        <v>129039218</v>
       </c>
       <c r="B109" t="n">
-        <v>91540</v>
+        <v>92822</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491117</v>
+        <v>491054</v>
       </c>
       <c r="R109" t="n">
-        <v>6710091</v>
+        <v>6710041</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12542,7 +12551,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12552,7 +12561,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12579,54 +12588,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129039218</v>
+        <v>129042566</v>
       </c>
       <c r="B110" t="n">
-        <v>92821</v>
+        <v>98705</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491054</v>
+        <v>491288</v>
       </c>
       <c r="R110" t="n">
-        <v>6710041</v>
+        <v>6710104</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129045855</v>
+        <v>129039783</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491030</v>
+        <v>491113</v>
       </c>
       <c r="R2" t="n">
-        <v>6709895</v>
+        <v>6710132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129042946</v>
+        <v>129041992</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491232</v>
+        <v>491353</v>
       </c>
       <c r="R3" t="n">
-        <v>6710086</v>
+        <v>6710077</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På 2 stående.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129041481</v>
+        <v>129038956</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491361</v>
+        <v>490939</v>
       </c>
       <c r="R4" t="n">
-        <v>6710143</v>
+        <v>6709966</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,50 +1006,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129038956</v>
+        <v>129039226</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490939</v>
+        <v>491060</v>
       </c>
       <c r="R5" t="n">
-        <v>6709966</v>
+        <v>6710037</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,12 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,32 +1113,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129039783</v>
+        <v>129042946</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491113</v>
+        <v>491232</v>
       </c>
       <c r="R6" t="n">
-        <v>6710132</v>
+        <v>6710086</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,45 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129041992</v>
+        <v>129045855</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491353</v>
+        <v>491030</v>
       </c>
       <c r="R7" t="n">
-        <v>6710077</v>
+        <v>6709895</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,45 +1332,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129039226</v>
+        <v>129041481</v>
       </c>
       <c r="B8" t="n">
-        <v>92822</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491060</v>
+        <v>491361</v>
       </c>
       <c r="R8" t="n">
-        <v>6710037</v>
+        <v>6710143</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129040305</v>
+        <v>129039748</v>
       </c>
       <c r="B9" t="n">
-        <v>75159</v>
+        <v>92822</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491221</v>
+        <v>491113</v>
       </c>
       <c r="R9" t="n">
-        <v>6710146</v>
+        <v>6710132</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,50 +1546,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129041053</v>
+        <v>129040595</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491309</v>
+        <v>491251</v>
       </c>
       <c r="R10" t="n">
-        <v>6710192</v>
+        <v>6710146</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,12 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,50 +1653,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129043673</v>
+        <v>129045778</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491125</v>
+        <v>491010</v>
       </c>
       <c r="R11" t="n">
-        <v>6709976</v>
+        <v>6709893</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1748,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129040595</v>
+        <v>129041291</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,14 +1791,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491251</v>
+        <v>491359</v>
       </c>
       <c r="R12" t="n">
-        <v>6710146</v>
+        <v>6710158</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1840,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,45 +1867,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129045778</v>
+        <v>129043673</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491010</v>
+        <v>491125</v>
       </c>
       <c r="R13" t="n">
-        <v>6709893</v>
+        <v>6709976</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,45 +1979,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129041291</v>
+        <v>129040305</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>75159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491359</v>
+        <v>491221</v>
       </c>
       <c r="R14" t="n">
-        <v>6710158</v>
+        <v>6710146</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,45 +2086,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129039748</v>
+        <v>129041053</v>
       </c>
       <c r="B15" t="n">
-        <v>92822</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491113</v>
+        <v>491309</v>
       </c>
       <c r="R15" t="n">
-        <v>6710132</v>
+        <v>6710192</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2161,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2171,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,7 +2206,7 @@
         <v>129043484</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>129043063</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,45 +2748,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129041584</v>
+        <v>129040685</v>
       </c>
       <c r="B21" t="n">
-        <v>91561</v>
+        <v>92822</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491362</v>
+        <v>491251</v>
       </c>
       <c r="R21" t="n">
-        <v>6710143</v>
+        <v>6710146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,45 +2855,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129040685</v>
+        <v>129041584</v>
       </c>
       <c r="B22" t="n">
-        <v>92822</v>
+        <v>91561</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491251</v>
+        <v>491362</v>
       </c>
       <c r="R22" t="n">
-        <v>6710146</v>
+        <v>6710143</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3077,7 +3077,7 @@
         <v>129044129</v>
       </c>
       <c r="B24" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>129045583</v>
       </c>
       <c r="B25" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>129043562</v>
       </c>
       <c r="B26" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>129041242</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,42 +3609,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129042527</v>
+        <v>129040515</v>
       </c>
       <c r="B29" t="n">
-        <v>92822</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3653,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491296</v>
+        <v>491251</v>
       </c>
       <c r="R29" t="n">
-        <v>6710104</v>
+        <v>6710165</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3688,7 +3684,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3698,7 +3694,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3725,38 +3726,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129040515</v>
+        <v>129042527</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3765,10 +3770,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491251</v>
+        <v>491296</v>
       </c>
       <c r="R30" t="n">
-        <v>6710165</v>
+        <v>6710104</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3800,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3810,12 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,50 +3842,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129039814</v>
+        <v>129044587</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>91838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491102</v>
+        <v>491075</v>
       </c>
       <c r="R31" t="n">
-        <v>6710142</v>
+        <v>6709943</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3917,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3927,7 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3954,32 +3949,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129039825</v>
+        <v>129040534</v>
       </c>
       <c r="B32" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3989,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491126</v>
+        <v>491261</v>
       </c>
       <c r="R32" t="n">
-        <v>6710148</v>
+        <v>6710156</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4034,7 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4061,10 +4056,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129038111</v>
+        <v>129044722</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4072,39 +4067,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490874</v>
+        <v>491088</v>
       </c>
       <c r="R33" t="n">
-        <v>6709885</v>
+        <v>6709977</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4136,7 +4126,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4146,12 +4136,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4178,10 +4168,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129044587</v>
+        <v>129038111</v>
       </c>
       <c r="B34" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4189,34 +4179,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491075</v>
+        <v>490874</v>
       </c>
       <c r="R34" t="n">
-        <v>6709943</v>
+        <v>6709885</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4248,7 +4243,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4258,7 +4253,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4285,45 +4285,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129040534</v>
+        <v>129040867</v>
       </c>
       <c r="B35" t="n">
-        <v>91540</v>
+        <v>105770</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491261</v>
+        <v>491332</v>
       </c>
       <c r="R35" t="n">
-        <v>6710156</v>
+        <v>6710175</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,45 +4392,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129044722</v>
+        <v>129039814</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491088</v>
+        <v>491102</v>
       </c>
       <c r="R36" t="n">
-        <v>6709977</v>
+        <v>6710142</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4462,7 +4467,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4472,12 +4477,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4504,45 +4504,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129040867</v>
+        <v>129039825</v>
       </c>
       <c r="B37" t="n">
-        <v>105769</v>
+        <v>98706</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491332</v>
+        <v>491126</v>
       </c>
       <c r="R37" t="n">
-        <v>6710175</v>
+        <v>6710148</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4614,7 +4614,7 @@
         <v>129041725</v>
       </c>
       <c r="B38" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4946,45 +4946,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129044467</v>
+        <v>129038104</v>
       </c>
       <c r="B41" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491036</v>
+        <v>490880</v>
       </c>
       <c r="R41" t="n">
-        <v>6709945</v>
+        <v>6709882</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5016,7 +5024,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5026,7 +5034,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5053,53 +5066,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129038104</v>
+        <v>129044467</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490880</v>
+        <v>491036</v>
       </c>
       <c r="R42" t="n">
-        <v>6709882</v>
+        <v>6709945</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5131,7 +5136,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5141,12 +5146,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5507,7 +5507,7 @@
         <v>129039795</v>
       </c>
       <c r="B46" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>129042338</v>
       </c>
       <c r="B47" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5858,45 +5858,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129045046</v>
+        <v>129038812</v>
       </c>
       <c r="B49" t="n">
-        <v>98705</v>
+        <v>92822</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491153</v>
+        <v>490918</v>
       </c>
       <c r="R49" t="n">
-        <v>6710121</v>
+        <v>6709933</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5928,7 +5937,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5938,7 +5947,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5965,54 +5974,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129038812</v>
+        <v>129044332</v>
       </c>
       <c r="B50" t="n">
-        <v>92822</v>
+        <v>98706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490918</v>
+        <v>491049</v>
       </c>
       <c r="R50" t="n">
-        <v>6709933</v>
+        <v>6709914</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6081,10 +6081,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129044332</v>
+        <v>129045046</v>
       </c>
       <c r="B51" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>491049</v>
+        <v>491153</v>
       </c>
       <c r="R51" t="n">
-        <v>6709914</v>
+        <v>6710121</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6191,7 +6191,7 @@
         <v>129039883</v>
       </c>
       <c r="B52" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6295,45 +6295,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129044552</v>
+        <v>129038692</v>
       </c>
       <c r="B53" t="n">
-        <v>98705</v>
+        <v>57887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>491075</v>
+        <v>490892</v>
       </c>
       <c r="R53" t="n">
-        <v>6709942</v>
+        <v>6709919</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6365,7 +6370,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6375,7 +6380,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6402,10 +6407,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129040369</v>
+        <v>129044552</v>
       </c>
       <c r="B54" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6437,10 +6442,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>491194</v>
+        <v>491075</v>
       </c>
       <c r="R54" t="n">
-        <v>6710167</v>
+        <v>6709942</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6472,7 +6477,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6482,7 +6487,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6509,50 +6514,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129038692</v>
+        <v>129040369</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>98706</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490892</v>
+        <v>491194</v>
       </c>
       <c r="R55" t="n">
-        <v>6709919</v>
+        <v>6710167</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6621,10 +6621,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129037776</v>
+        <v>129039941</v>
       </c>
       <c r="B56" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490952</v>
+        <v>491158</v>
       </c>
       <c r="R56" t="n">
-        <v>6709889</v>
+        <v>6710160</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6835,10 +6835,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129039941</v>
+        <v>129037776</v>
       </c>
       <c r="B58" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491158</v>
+        <v>490952</v>
       </c>
       <c r="R58" t="n">
-        <v>6710160</v>
+        <v>6709889</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,10 +6942,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129044061</v>
+        <v>129038411</v>
       </c>
       <c r="B59" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>491110</v>
+        <v>490873</v>
       </c>
       <c r="R59" t="n">
-        <v>6709915</v>
+        <v>6709909</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7049,10 +7049,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129045420</v>
+        <v>129044061</v>
       </c>
       <c r="B60" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7084,10 +7084,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>491009</v>
+        <v>491110</v>
       </c>
       <c r="R60" t="n">
-        <v>6709991</v>
+        <v>6709915</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7156,10 +7156,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129043992</v>
+        <v>129045420</v>
       </c>
       <c r="B61" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>491095</v>
+        <v>491009</v>
       </c>
       <c r="R61" t="n">
-        <v>6709906</v>
+        <v>6709991</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129038411</v>
+        <v>129038173</v>
       </c>
       <c r="B62" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,17 +7291,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>490873</v>
+        <v>490877</v>
       </c>
       <c r="R62" t="n">
-        <v>6709909</v>
+        <v>6709889</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7333,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7343,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7370,10 +7384,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129038173</v>
+        <v>129043992</v>
       </c>
       <c r="B63" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7398,31 +7412,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>490877</v>
+        <v>491095</v>
       </c>
       <c r="R63" t="n">
-        <v>6709889</v>
+        <v>6709906</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7710,10 +7710,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129044189</v>
+        <v>129039716</v>
       </c>
       <c r="B66" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7739,16 +7739,21 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491025</v>
+        <v>491118</v>
       </c>
       <c r="R66" t="n">
-        <v>6709886</v>
+        <v>6710111</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7780,7 +7785,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7790,7 +7795,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7817,10 +7827,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129043659</v>
+        <v>129044189</v>
       </c>
       <c r="B67" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7852,10 +7862,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>491126</v>
+        <v>491025</v>
       </c>
       <c r="R67" t="n">
-        <v>6709977</v>
+        <v>6709886</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7887,7 +7897,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7897,7 +7907,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7924,10 +7934,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129045555</v>
+        <v>129043659</v>
       </c>
       <c r="B68" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7959,10 +7969,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490955</v>
+        <v>491126</v>
       </c>
       <c r="R68" t="n">
-        <v>6709969</v>
+        <v>6709977</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7994,7 +8004,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8004,7 +8014,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8031,10 +8041,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129039716</v>
+        <v>129045555</v>
       </c>
       <c r="B69" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8060,21 +8070,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>491118</v>
+        <v>490955</v>
       </c>
       <c r="R69" t="n">
-        <v>6710111</v>
+        <v>6709969</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8106,7 +8111,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8116,12 +8121,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8151,7 +8151,7 @@
         <v>129039681</v>
       </c>
       <c r="B70" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>129038944</v>
       </c>
       <c r="B71" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8474,10 +8474,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129038053</v>
+        <v>129043183</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8485,39 +8485,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490886</v>
+        <v>491200</v>
       </c>
       <c r="R73" t="n">
-        <v>6709872</v>
+        <v>6709983</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8549,7 +8544,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8559,12 +8554,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8591,32 +8586,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129043183</v>
+        <v>129042724</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>92858</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8626,10 +8621,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>491200</v>
+        <v>491257</v>
       </c>
       <c r="R74" t="n">
-        <v>6709983</v>
+        <v>6710085</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8661,7 +8656,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8671,12 +8666,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8703,32 +8693,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129042724</v>
+        <v>129040051</v>
       </c>
       <c r="B75" t="n">
-        <v>92858</v>
+        <v>98706</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8738,10 +8728,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>491257</v>
+        <v>491183</v>
       </c>
       <c r="R75" t="n">
-        <v>6710085</v>
+        <v>6710141</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8773,7 +8763,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8783,7 +8773,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8810,7 +8800,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129038223</v>
+        <v>129038053</v>
       </c>
       <c r="B76" t="n">
         <v>57727</v>
@@ -8841,7 +8831,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8850,10 +8840,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490878</v>
+        <v>490886</v>
       </c>
       <c r="R76" t="n">
-        <v>6709889</v>
+        <v>6709872</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8885,7 +8875,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8895,7 +8885,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8922,45 +8917,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129040051</v>
+        <v>129038223</v>
       </c>
       <c r="B77" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>491183</v>
+        <v>490878</v>
       </c>
       <c r="R77" t="n">
-        <v>6710141</v>
+        <v>6709889</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9029,10 +9029,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129043352</v>
+        <v>129040173</v>
       </c>
       <c r="B78" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>491188</v>
+        <v>491201</v>
       </c>
       <c r="R78" t="n">
-        <v>6709988</v>
+        <v>6710139</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9136,10 +9136,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129040173</v>
+        <v>129039515</v>
       </c>
       <c r="B79" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9165,16 +9165,21 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>491201</v>
+        <v>491104</v>
       </c>
       <c r="R79" t="n">
-        <v>6710139</v>
+        <v>6710105</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9206,7 +9211,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9216,7 +9221,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9243,10 +9248,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129039515</v>
+        <v>129043352</v>
       </c>
       <c r="B80" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9272,21 +9277,16 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>491104</v>
+        <v>491188</v>
       </c>
       <c r="R80" t="n">
-        <v>6710105</v>
+        <v>6709988</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9318,7 +9318,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9355,10 +9355,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129044818</v>
+        <v>129039011</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9366,34 +9366,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>491116</v>
+        <v>490936</v>
       </c>
       <c r="R81" t="n">
-        <v>6710020</v>
+        <v>6709979</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9425,7 +9430,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9435,12 +9440,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9467,50 +9472,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129042971</v>
+        <v>129038137</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>491193</v>
+        <v>490876</v>
       </c>
       <c r="R82" t="n">
-        <v>6710074</v>
+        <v>6709883</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9542,7 +9547,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9552,12 +9557,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9584,50 +9584,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129039011</v>
+        <v>129039994</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490936</v>
+        <v>491173</v>
       </c>
       <c r="R83" t="n">
-        <v>6709979</v>
+        <v>6710152</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9659,7 +9654,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9669,12 +9664,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:21</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9701,50 +9691,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129038137</v>
+        <v>129044818</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>490876</v>
+        <v>491116</v>
       </c>
       <c r="R84" t="n">
-        <v>6709883</v>
+        <v>6710020</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9776,7 +9761,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9786,7 +9771,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9813,45 +9803,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129039994</v>
+        <v>129042971</v>
       </c>
       <c r="B85" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>491173</v>
+        <v>491193</v>
       </c>
       <c r="R85" t="n">
-        <v>6710152</v>
+        <v>6710074</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9883,7 +9878,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9893,7 +9888,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10027,10 +10027,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129043286</v>
+        <v>129040273</v>
       </c>
       <c r="B87" t="n">
-        <v>91561</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10038,43 +10038,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491185</v>
+        <v>491210</v>
       </c>
       <c r="R87" t="n">
-        <v>6710038</v>
+        <v>6710152</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10106,7 +10097,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10116,7 +10107,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10143,7 +10139,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129040273</v>
+        <v>129042243</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -10174,14 +10170,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491210</v>
+        <v>491324</v>
       </c>
       <c r="R88" t="n">
-        <v>6710152</v>
+        <v>6710108</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10213,7 +10209,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10223,12 +10219,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10255,7 +10251,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129042243</v>
+        <v>129043457</v>
       </c>
       <c r="B89" t="n">
         <v>79041</v>
@@ -10286,14 +10282,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491324</v>
+        <v>491159</v>
       </c>
       <c r="R89" t="n">
-        <v>6710108</v>
+        <v>6709989</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10325,7 +10321,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10335,7 +10331,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10367,10 +10363,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129043457</v>
+        <v>129043286</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>91561</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10378,34 +10374,43 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491159</v>
+        <v>491185</v>
       </c>
       <c r="R90" t="n">
-        <v>6709989</v>
+        <v>6710038</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10437,7 +10442,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10447,12 +10452,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10479,10 +10479,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129039369</v>
+        <v>129039427</v>
       </c>
       <c r="B91" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10507,31 +10507,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491082</v>
+        <v>491089</v>
       </c>
       <c r="R91" t="n">
-        <v>6710072</v>
+        <v>6710079</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10563,7 +10549,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10573,7 +10559,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10600,10 +10586,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129040090</v>
+        <v>129039369</v>
       </c>
       <c r="B92" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10628,17 +10614,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491189</v>
+        <v>491082</v>
       </c>
       <c r="R92" t="n">
-        <v>6710146</v>
+        <v>6710072</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10707,10 +10707,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129039427</v>
+        <v>129040090</v>
       </c>
       <c r="B93" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10742,10 +10742,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491089</v>
+        <v>491189</v>
       </c>
       <c r="R93" t="n">
-        <v>6710079</v>
+        <v>6710146</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10921,45 +10921,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129044713</v>
+        <v>129041444</v>
       </c>
       <c r="B95" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491086</v>
+        <v>491362</v>
       </c>
       <c r="R95" t="n">
-        <v>6709974</v>
+        <v>6710150</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10991,7 +10996,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11001,7 +11006,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11028,10 +11038,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129045097</v>
+        <v>129043344</v>
       </c>
       <c r="B96" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11057,21 +11067,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491132</v>
+        <v>491176</v>
       </c>
       <c r="R96" t="n">
-        <v>6710123</v>
+        <v>6710019</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11103,7 +11108,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11113,12 +11118,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11145,50 +11145,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129041444</v>
+        <v>129044713</v>
       </c>
       <c r="B97" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491362</v>
+        <v>491086</v>
       </c>
       <c r="R97" t="n">
-        <v>6710150</v>
+        <v>6709974</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11220,7 +11215,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11230,12 +11225,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11262,10 +11252,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129043344</v>
+        <v>129044360</v>
       </c>
       <c r="B98" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11297,10 +11287,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491176</v>
+        <v>491050</v>
       </c>
       <c r="R98" t="n">
-        <v>6710019</v>
+        <v>6709915</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11332,7 +11322,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11342,7 +11332,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11369,10 +11359,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129044360</v>
+        <v>129041232</v>
       </c>
       <c r="B99" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11398,16 +11388,21 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491050</v>
+        <v>491336</v>
       </c>
       <c r="R99" t="n">
-        <v>6709915</v>
+        <v>6710188</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11439,7 +11434,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11449,7 +11444,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11476,10 +11471,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129041232</v>
+        <v>129045097</v>
       </c>
       <c r="B100" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11512,14 +11507,14 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491336</v>
+        <v>491132</v>
       </c>
       <c r="R100" t="n">
-        <v>6710188</v>
+        <v>6710123</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11551,7 +11546,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11561,7 +11556,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11708,32 +11708,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129040149</v>
+        <v>129044617</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11743,10 +11743,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491192</v>
+        <v>491091</v>
       </c>
       <c r="R102" t="n">
-        <v>6710147</v>
+        <v>6709950</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11815,50 +11815,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129038846</v>
+        <v>129043760</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>490903</v>
+        <v>491096</v>
       </c>
       <c r="R103" t="n">
-        <v>6709932</v>
+        <v>6709954</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11890,7 +11885,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11900,12 +11895,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11932,32 +11922,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129044617</v>
+        <v>129040149</v>
       </c>
       <c r="B104" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11967,10 +11957,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491091</v>
+        <v>491192</v>
       </c>
       <c r="R104" t="n">
-        <v>6709950</v>
+        <v>6710147</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12002,7 +11992,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12012,7 +12002,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12039,45 +12029,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129043760</v>
+        <v>129038846</v>
       </c>
       <c r="B105" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491096</v>
+        <v>490903</v>
       </c>
       <c r="R105" t="n">
-        <v>6709954</v>
+        <v>6709932</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12109,7 +12104,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12119,7 +12114,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12253,45 +12253,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129039646</v>
+        <v>129039218</v>
       </c>
       <c r="B107" t="n">
-        <v>91838</v>
+        <v>92822</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491117</v>
+        <v>491054</v>
       </c>
       <c r="R107" t="n">
-        <v>6710091</v>
+        <v>6710041</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12323,7 +12332,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12333,12 +12342,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12365,10 +12369,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129044243</v>
+        <v>129042566</v>
       </c>
       <c r="B108" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12400,10 +12404,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491026</v>
+        <v>491288</v>
       </c>
       <c r="R108" t="n">
-        <v>6709889</v>
+        <v>6710104</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12435,7 +12439,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12445,7 +12449,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12472,54 +12476,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129039218</v>
+        <v>129044243</v>
       </c>
       <c r="B109" t="n">
-        <v>92822</v>
+        <v>98706</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491054</v>
+        <v>491026</v>
       </c>
       <c r="R109" t="n">
-        <v>6710041</v>
+        <v>6709889</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12551,7 +12546,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12561,7 +12556,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12588,32 +12583,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129042566</v>
+        <v>129039646</v>
       </c>
       <c r="B110" t="n">
-        <v>98705</v>
+        <v>91838</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12623,10 +12618,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491288</v>
+        <v>491117</v>
       </c>
       <c r="R110" t="n">
-        <v>6710104</v>
+        <v>6710091</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12658,7 +12653,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12668,7 +12663,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129039783</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129041992</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>129039226</v>
       </c>
       <c r="B5" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>129045855</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129041481</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129039748</v>
+        <v>129040305</v>
       </c>
       <c r="B9" t="n">
-        <v>92822</v>
+        <v>75161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491113</v>
+        <v>491221</v>
       </c>
       <c r="R9" t="n">
-        <v>6710132</v>
+        <v>6710146</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129040595</v>
+        <v>129039748</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>92825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491251</v>
+        <v>491113</v>
       </c>
       <c r="R10" t="n">
-        <v>6710146</v>
+        <v>6710132</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,45 +1653,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129045778</v>
+        <v>129041053</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491010</v>
+        <v>491309</v>
       </c>
       <c r="R11" t="n">
-        <v>6709893</v>
+        <v>6710192</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1733,7 +1738,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,45 +1770,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129041291</v>
+        <v>129043673</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491359</v>
+        <v>491125</v>
       </c>
       <c r="R12" t="n">
-        <v>6710158</v>
+        <v>6709976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,50 +1882,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129043673</v>
+        <v>129043484</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491125</v>
+        <v>491159</v>
       </c>
       <c r="R13" t="n">
-        <v>6709976</v>
+        <v>6709989</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,32 +1989,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129040305</v>
+        <v>129040595</v>
       </c>
       <c r="B14" t="n">
-        <v>75159</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,7 +2024,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491221</v>
+        <v>491251</v>
       </c>
       <c r="R14" t="n">
         <v>6710146</v>
@@ -2049,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,50 +2096,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129041053</v>
+        <v>129045778</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491309</v>
+        <v>491010</v>
       </c>
       <c r="R15" t="n">
-        <v>6710192</v>
+        <v>6709893</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2171,12 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129043484</v>
+        <v>129041291</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491159</v>
+        <v>491359</v>
       </c>
       <c r="R16" t="n">
-        <v>6709989</v>
+        <v>6710158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,7 +2313,7 @@
         <v>129039950</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,32 +2417,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129039360</v>
+        <v>129043063</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491080</v>
+        <v>491227</v>
       </c>
       <c r="R18" t="n">
-        <v>6710071</v>
+        <v>6710010</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På stenblock.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,32 +2529,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129043063</v>
+        <v>129039360</v>
       </c>
       <c r="B19" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491227</v>
+        <v>491080</v>
       </c>
       <c r="R19" t="n">
-        <v>6710010</v>
+        <v>6710071</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På stenblock.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,7 +2644,7 @@
         <v>129037863</v>
       </c>
       <c r="B20" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,45 +2748,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129040685</v>
+        <v>129041584</v>
       </c>
       <c r="B21" t="n">
-        <v>92822</v>
+        <v>91564</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491251</v>
+        <v>491362</v>
       </c>
       <c r="R21" t="n">
-        <v>6710146</v>
+        <v>6710143</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,45 +2855,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129041584</v>
+        <v>129040685</v>
       </c>
       <c r="B22" t="n">
-        <v>91561</v>
+        <v>92825</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491362</v>
+        <v>491251</v>
       </c>
       <c r="R22" t="n">
-        <v>6710143</v>
+        <v>6710146</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,50 +2962,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129040720</v>
+        <v>129044129</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>98710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491296</v>
+        <v>491049</v>
       </c>
       <c r="R23" t="n">
-        <v>6710129</v>
+        <v>6709893</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,45 +3069,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129044129</v>
+        <v>129040720</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491049</v>
+        <v>491296</v>
       </c>
       <c r="R24" t="n">
-        <v>6709893</v>
+        <v>6710129</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,32 +3181,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129045583</v>
+        <v>129045240</v>
       </c>
       <c r="B25" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490946</v>
+        <v>491133</v>
       </c>
       <c r="R25" t="n">
-        <v>6709935</v>
+        <v>6710118</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,45 +3288,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129043562</v>
+        <v>129040515</v>
       </c>
       <c r="B26" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491129</v>
+        <v>491251</v>
       </c>
       <c r="R26" t="n">
-        <v>6709987</v>
+        <v>6710165</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3358,7 +3363,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3368,7 +3373,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,45 +3405,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129041242</v>
+        <v>129042527</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>92825</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491341</v>
+        <v>491296</v>
       </c>
       <c r="R27" t="n">
-        <v>6710206</v>
+        <v>6710104</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3465,7 +3484,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3475,7 +3494,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,32 +3521,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129045240</v>
+        <v>129045583</v>
       </c>
       <c r="B28" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3537,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491133</v>
+        <v>490946</v>
       </c>
       <c r="R28" t="n">
-        <v>6710118</v>
+        <v>6709935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3572,7 +3591,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3582,7 +3601,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3609,50 +3628,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129040515</v>
+        <v>129043562</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491251</v>
+        <v>491129</v>
       </c>
       <c r="R29" t="n">
-        <v>6710165</v>
+        <v>6709987</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,7 +3698,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3694,12 +3708,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3726,54 +3735,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129042527</v>
+        <v>129041242</v>
       </c>
       <c r="B30" t="n">
-        <v>92822</v>
+        <v>98710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491296</v>
+        <v>491341</v>
       </c>
       <c r="R30" t="n">
-        <v>6710104</v>
+        <v>6710206</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129044587</v>
+        <v>129040534</v>
       </c>
       <c r="B31" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491075</v>
+        <v>491261</v>
       </c>
       <c r="R31" t="n">
-        <v>6709943</v>
+        <v>6710156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,45 +3949,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129040534</v>
+        <v>129040867</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>105774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491261</v>
+        <v>491332</v>
       </c>
       <c r="R32" t="n">
-        <v>6710156</v>
+        <v>6710175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4056,45 +4056,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129044722</v>
+        <v>129039814</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491088</v>
+        <v>491102</v>
       </c>
       <c r="R33" t="n">
-        <v>6709977</v>
+        <v>6710142</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4126,7 +4131,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4136,12 +4141,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4168,50 +4168,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129038111</v>
+        <v>129039825</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490874</v>
+        <v>491126</v>
       </c>
       <c r="R34" t="n">
-        <v>6709885</v>
+        <v>6710148</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4243,7 +4238,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4253,12 +4248,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4285,45 +4275,59 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129040867</v>
+        <v>129041725</v>
       </c>
       <c r="B35" t="n">
-        <v>105770</v>
+        <v>98710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491332</v>
+        <v>491375</v>
       </c>
       <c r="R35" t="n">
-        <v>6710175</v>
+        <v>6710101</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4355,7 +4359,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4365,7 +4369,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,50 +4396,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129039814</v>
+        <v>129044722</v>
       </c>
       <c r="B36" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491102</v>
+        <v>491088</v>
       </c>
       <c r="R36" t="n">
-        <v>6710142</v>
+        <v>6709977</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4467,7 +4466,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4477,7 +4476,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4504,32 +4508,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129039825</v>
+        <v>129044587</v>
       </c>
       <c r="B37" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4539,10 +4543,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491126</v>
+        <v>491075</v>
       </c>
       <c r="R37" t="n">
-        <v>6710148</v>
+        <v>6709943</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4574,7 +4578,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4584,7 +4588,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4611,59 +4615,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129041725</v>
+        <v>129038111</v>
       </c>
       <c r="B38" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491375</v>
+        <v>490874</v>
       </c>
       <c r="R38" t="n">
-        <v>6710101</v>
+        <v>6709885</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,7 +4690,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4705,7 +4700,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4732,10 +4732,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129045013</v>
+        <v>129040042</v>
       </c>
       <c r="B39" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,21 +4743,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491157</v>
+        <v>491181</v>
       </c>
       <c r="R39" t="n">
-        <v>6710121</v>
+        <v>6710144</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4839,10 +4839,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129040042</v>
+        <v>129045013</v>
       </c>
       <c r="B40" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4850,21 +4850,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491181</v>
+        <v>491157</v>
       </c>
       <c r="R40" t="n">
-        <v>6710144</v>
+        <v>6710121</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5069,7 +5069,7 @@
         <v>129044467</v>
       </c>
       <c r="B42" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>129044319</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>129041044</v>
       </c>
       <c r="B44" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,59 +5504,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129039795</v>
+        <v>129037802</v>
       </c>
       <c r="B46" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491106</v>
+        <v>490941</v>
       </c>
       <c r="R46" t="n">
-        <v>6710124</v>
+        <v>6709886</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5588,7 +5574,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5598,7 +5584,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5625,10 +5611,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129042338</v>
+        <v>129039795</v>
       </c>
       <c r="B47" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5660,24 +5646,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491335</v>
+        <v>491106</v>
       </c>
       <c r="R47" t="n">
-        <v>6710120</v>
+        <v>6710124</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5709,7 +5695,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5719,12 +5705,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5751,45 +5732,59 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129037802</v>
+        <v>129042338</v>
       </c>
       <c r="B48" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490941</v>
+        <v>491335</v>
       </c>
       <c r="R48" t="n">
-        <v>6709886</v>
+        <v>6710120</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5821,7 +5816,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5831,7 +5826,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5861,7 +5861,7 @@
         <v>129038812</v>
       </c>
       <c r="B49" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>129044332</v>
       </c>
       <c r="B50" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>129045046</v>
       </c>
       <c r="B51" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>129039883</v>
       </c>
       <c r="B52" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>129044552</v>
       </c>
       <c r="B54" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>129040369</v>
       </c>
       <c r="B55" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6621,10 +6621,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129039941</v>
+        <v>129037776</v>
       </c>
       <c r="B56" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>491158</v>
+        <v>490952</v>
       </c>
       <c r="R56" t="n">
-        <v>6710160</v>
+        <v>6709889</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6731,7 +6731,7 @@
         <v>129040007</v>
       </c>
       <c r="B57" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6835,10 +6835,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129037776</v>
+        <v>129039941</v>
       </c>
       <c r="B58" t="n">
-        <v>91838</v>
+        <v>91543</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490952</v>
+        <v>491158</v>
       </c>
       <c r="R58" t="n">
-        <v>6709889</v>
+        <v>6710160</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,7 +6945,7 @@
         <v>129038411</v>
       </c>
       <c r="B59" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>129044061</v>
       </c>
       <c r="B60" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>129045420</v>
       </c>
       <c r="B61" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>129038173</v>
       </c>
       <c r="B62" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>129043992</v>
       </c>
       <c r="B63" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7491,10 +7491,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129037762</v>
+        <v>129042106</v>
       </c>
       <c r="B64" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7502,21 +7502,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>490949</v>
+        <v>491327</v>
       </c>
       <c r="R64" t="n">
-        <v>6709885</v>
+        <v>6710067</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7571,7 +7571,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7598,10 +7603,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129042106</v>
+        <v>129037762</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7609,21 +7614,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7633,10 +7638,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>491327</v>
+        <v>490949</v>
       </c>
       <c r="R65" t="n">
-        <v>6710067</v>
+        <v>6709885</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7668,7 +7673,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7678,12 +7683,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7713,7 +7713,7 @@
         <v>129039716</v>
       </c>
       <c r="B66" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>129044189</v>
       </c>
       <c r="B67" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>129043659</v>
       </c>
       <c r="B68" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>129045555</v>
       </c>
       <c r="B69" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>129039681</v>
       </c>
       <c r="B70" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>129038944</v>
       </c>
       <c r="B71" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8367,10 +8367,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129040356</v>
+        <v>129038223</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8378,34 +8378,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>491211</v>
+        <v>490878</v>
       </c>
       <c r="R72" t="n">
-        <v>6710165</v>
+        <v>6709889</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,7 +8442,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8447,7 +8452,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8474,32 +8479,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129043183</v>
+        <v>129040051</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8509,10 +8514,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>491200</v>
+        <v>491183</v>
       </c>
       <c r="R73" t="n">
-        <v>6709983</v>
+        <v>6710141</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8544,7 +8549,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8554,12 +8559,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8589,7 +8589,7 @@
         <v>129042724</v>
       </c>
       <c r="B74" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8693,32 +8693,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129040051</v>
+        <v>129040356</v>
       </c>
       <c r="B75" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8728,10 +8728,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>491183</v>
+        <v>491211</v>
       </c>
       <c r="R75" t="n">
-        <v>6710141</v>
+        <v>6710165</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8800,10 +8800,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129038053</v>
+        <v>129043183</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8811,39 +8811,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>490886</v>
+        <v>491200</v>
       </c>
       <c r="R76" t="n">
-        <v>6709872</v>
+        <v>6709983</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8875,7 +8870,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8885,12 +8880,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8917,7 +8912,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129038223</v>
+        <v>129038053</v>
       </c>
       <c r="B77" t="n">
         <v>57727</v>
@@ -8948,7 +8943,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8957,10 +8952,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490878</v>
+        <v>490886</v>
       </c>
       <c r="R77" t="n">
-        <v>6709889</v>
+        <v>6709872</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8992,7 +8987,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9002,7 +8997,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9032,7 +9032,7 @@
         <v>129040173</v>
       </c>
       <c r="B78" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>129039515</v>
       </c>
       <c r="B79" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>129043352</v>
       </c>
       <c r="B80" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9355,10 +9355,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129039011</v>
+        <v>129044818</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9366,39 +9366,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>490936</v>
+        <v>491116</v>
       </c>
       <c r="R81" t="n">
-        <v>6709979</v>
+        <v>6710020</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9430,7 +9425,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9440,12 +9435,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9472,50 +9467,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129038137</v>
+        <v>129042971</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>490876</v>
+        <v>491193</v>
       </c>
       <c r="R82" t="n">
-        <v>6709883</v>
+        <v>6710074</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9547,7 +9542,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9557,7 +9552,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9584,45 +9584,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129039994</v>
+        <v>129039011</v>
       </c>
       <c r="B83" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>491173</v>
+        <v>490936</v>
       </c>
       <c r="R83" t="n">
-        <v>6710152</v>
+        <v>6709979</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9654,7 +9659,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9664,7 +9669,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9691,45 +9701,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129044818</v>
+        <v>129038137</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>491116</v>
+        <v>490876</v>
       </c>
       <c r="R84" t="n">
-        <v>6710020</v>
+        <v>6709883</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9761,7 +9776,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9771,12 +9786,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9803,50 +9813,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129042971</v>
+        <v>129039994</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>491193</v>
+        <v>491173</v>
       </c>
       <c r="R85" t="n">
-        <v>6710074</v>
+        <v>6710152</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9878,7 +9883,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9888,12 +9893,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9920,32 +9920,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129045737</v>
+        <v>129040273</v>
       </c>
       <c r="B86" t="n">
-        <v>92822</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>491006</v>
+        <v>491210</v>
       </c>
       <c r="R86" t="n">
-        <v>6709889</v>
+        <v>6710152</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10000,7 +10000,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10027,10 +10032,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129040273</v>
+        <v>129042243</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10058,14 +10063,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491210</v>
+        <v>491324</v>
       </c>
       <c r="R87" t="n">
-        <v>6710152</v>
+        <v>6710108</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10097,7 +10102,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10107,12 +10112,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10139,10 +10144,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129042243</v>
+        <v>129043457</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10170,14 +10175,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491324</v>
+        <v>491159</v>
       </c>
       <c r="R88" t="n">
-        <v>6710108</v>
+        <v>6709989</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10209,7 +10214,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10219,7 +10224,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10251,32 +10256,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129043457</v>
+        <v>129039427</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10286,10 +10291,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491159</v>
+        <v>491089</v>
       </c>
       <c r="R89" t="n">
-        <v>6709989</v>
+        <v>6710079</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10321,7 +10326,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10331,12 +10336,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10363,32 +10363,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129043286</v>
+        <v>129039369</v>
       </c>
       <c r="B90" t="n">
-        <v>91561</v>
+        <v>98710</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10398,7 +10398,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10407,10 +10412,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491185</v>
+        <v>491082</v>
       </c>
       <c r="R90" t="n">
-        <v>6710038</v>
+        <v>6710072</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10442,7 +10447,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10452,7 +10457,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10479,10 +10484,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129039427</v>
+        <v>129040090</v>
       </c>
       <c r="B91" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10514,10 +10519,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491089</v>
+        <v>491189</v>
       </c>
       <c r="R91" t="n">
-        <v>6710079</v>
+        <v>6710146</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10549,7 +10554,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10559,7 +10564,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10586,32 +10591,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129039369</v>
+        <v>129043286</v>
       </c>
       <c r="B92" t="n">
-        <v>98706</v>
+        <v>91564</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10621,12 +10626,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491082</v>
+        <v>491185</v>
       </c>
       <c r="R92" t="n">
-        <v>6710072</v>
+        <v>6710038</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10707,32 +10707,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129040090</v>
+        <v>129045737</v>
       </c>
       <c r="B93" t="n">
-        <v>98706</v>
+        <v>92825</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10742,10 +10742,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491189</v>
+        <v>491006</v>
       </c>
       <c r="R93" t="n">
-        <v>6710146</v>
+        <v>6709889</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10817,7 +10817,7 @@
         <v>129041984</v>
       </c>
       <c r="B94" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>129043344</v>
       </c>
       <c r="B96" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>129044713</v>
       </c>
       <c r="B97" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>129044360</v>
       </c>
       <c r="B98" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>129041232</v>
       </c>
       <c r="B99" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>129045097</v>
       </c>
       <c r="B100" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11588,53 +11588,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129045506</v>
+        <v>129044617</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>490975</v>
+        <v>491091</v>
       </c>
       <c r="R101" t="n">
-        <v>6709983</v>
+        <v>6709950</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11666,7 +11658,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11676,12 +11668,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Bohål i gran, på ca 2m.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11708,10 +11695,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129044617</v>
+        <v>129043760</v>
       </c>
       <c r="B102" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11743,10 +11730,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491091</v>
+        <v>491096</v>
       </c>
       <c r="R102" t="n">
-        <v>6709950</v>
+        <v>6709954</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11778,7 +11765,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11788,7 +11775,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11815,32 +11802,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129043760</v>
+        <v>129040149</v>
       </c>
       <c r="B103" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11850,10 +11837,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491096</v>
+        <v>491192</v>
       </c>
       <c r="R103" t="n">
-        <v>6709954</v>
+        <v>6710147</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11885,7 +11872,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11895,7 +11882,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11922,10 +11909,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129040149</v>
+        <v>129038846</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11933,34 +11920,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491192</v>
+        <v>490903</v>
       </c>
       <c r="R104" t="n">
-        <v>6710147</v>
+        <v>6709932</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11992,7 +11984,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12002,7 +11994,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12029,7 +12026,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129038846</v>
+        <v>129045506</v>
       </c>
       <c r="B105" t="n">
         <v>57727</v>
@@ -12058,21 +12055,24 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490903</v>
+        <v>490975</v>
       </c>
       <c r="R105" t="n">
-        <v>6709932</v>
+        <v>6709983</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Bohål i gran, på ca 2m.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12149,7 +12149,7 @@
         <v>129039623</v>
       </c>
       <c r="B106" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>129039218</v>
       </c>
       <c r="B107" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>129042566</v>
       </c>
       <c r="B108" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>129044243</v>
       </c>
       <c r="B109" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>129039646</v>
       </c>
       <c r="B110" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129040305</v>
+        <v>129043673</v>
       </c>
       <c r="B9" t="n">
-        <v>75161</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,34 +1450,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491221</v>
+        <v>491125</v>
       </c>
       <c r="R9" t="n">
-        <v>6710146</v>
+        <v>6709976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1519,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1551,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129039748</v>
+        <v>129043484</v>
       </c>
       <c r="B10" t="n">
-        <v>92825</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491113</v>
+        <v>491159</v>
       </c>
       <c r="R10" t="n">
-        <v>6710132</v>
+        <v>6709989</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,50 +1658,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129041053</v>
+        <v>129040595</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491309</v>
+        <v>491251</v>
       </c>
       <c r="R11" t="n">
-        <v>6710192</v>
+        <v>6710146</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,12 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,50 +1765,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129043673</v>
+        <v>129045778</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491125</v>
+        <v>491010</v>
       </c>
       <c r="R12" t="n">
-        <v>6709976</v>
+        <v>6709893</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129043484</v>
+        <v>129041291</v>
       </c>
       <c r="B13" t="n">
         <v>98710</v>
@@ -1913,14 +1903,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491159</v>
+        <v>491359</v>
       </c>
       <c r="R13" t="n">
-        <v>6709989</v>
+        <v>6710158</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,32 +1979,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129040595</v>
+        <v>129040305</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>75161</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,7 +2014,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491251</v>
+        <v>491221</v>
       </c>
       <c r="R14" t="n">
         <v>6710146</v>
@@ -2059,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2096,32 +2086,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129045778</v>
+        <v>129039748</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>92825</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491010</v>
+        <v>491113</v>
       </c>
       <c r="R15" t="n">
-        <v>6709893</v>
+        <v>6710132</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,45 +2193,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129041291</v>
+        <v>129041053</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491359</v>
+        <v>491309</v>
       </c>
       <c r="R16" t="n">
-        <v>6710158</v>
+        <v>6710192</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2278,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,45 +2641,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129037863</v>
+        <v>129040720</v>
       </c>
       <c r="B20" t="n">
-        <v>91996</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490942</v>
+        <v>491296</v>
       </c>
       <c r="R20" t="n">
-        <v>6709873</v>
+        <v>6710129</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2721,7 +2726,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2748,45 +2753,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129041584</v>
+        <v>129037863</v>
       </c>
       <c r="B21" t="n">
-        <v>91564</v>
+        <v>91996</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491362</v>
+        <v>490942</v>
       </c>
       <c r="R21" t="n">
-        <v>6710143</v>
+        <v>6709873</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,7 +2823,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2828,7 +2833,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,45 +2860,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129040685</v>
+        <v>129041584</v>
       </c>
       <c r="B22" t="n">
-        <v>92825</v>
+        <v>91564</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491251</v>
+        <v>491362</v>
       </c>
       <c r="R22" t="n">
-        <v>6710146</v>
+        <v>6710143</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2925,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2935,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2962,32 +2967,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129044129</v>
+        <v>129040685</v>
       </c>
       <c r="B23" t="n">
-        <v>98710</v>
+        <v>92825</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2997,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491049</v>
+        <v>491251</v>
       </c>
       <c r="R23" t="n">
-        <v>6709893</v>
+        <v>6710146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3069,50 +3074,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129040720</v>
+        <v>129044129</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491296</v>
+        <v>491049</v>
       </c>
       <c r="R24" t="n">
-        <v>6710129</v>
+        <v>6709893</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,45 +3181,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129045240</v>
+        <v>129042527</v>
       </c>
       <c r="B25" t="n">
-        <v>91841</v>
+        <v>92825</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491133</v>
+        <v>491296</v>
       </c>
       <c r="R25" t="n">
-        <v>6710118</v>
+        <v>6710104</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,7 +3260,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3261,7 +3270,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,10 +3297,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129040515</v>
+        <v>129045240</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,39 +3308,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491251</v>
+        <v>491133</v>
       </c>
       <c r="R26" t="n">
-        <v>6710165</v>
+        <v>6710118</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3363,7 +3367,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3373,12 +3377,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3405,42 +3404,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129042527</v>
+        <v>129040515</v>
       </c>
       <c r="B27" t="n">
-        <v>92825</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3449,10 +3444,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491296</v>
+        <v>491251</v>
       </c>
       <c r="R27" t="n">
-        <v>6710104</v>
+        <v>6710165</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3484,7 +3479,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3494,7 +3489,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4732,10 +4732,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129040042</v>
+        <v>129038104</v>
       </c>
       <c r="B39" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,34 +4743,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491181</v>
+        <v>490880</v>
       </c>
       <c r="R39" t="n">
-        <v>6710144</v>
+        <v>6709882</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4802,7 +4810,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4812,7 +4820,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4946,10 +4959,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129038104</v>
+        <v>129040042</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4957,42 +4970,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490880</v>
+        <v>491181</v>
       </c>
       <c r="R41" t="n">
-        <v>6709882</v>
+        <v>6710144</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5024,7 +5029,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5034,12 +5039,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6295,50 +6295,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129038692</v>
+        <v>129044552</v>
       </c>
       <c r="B53" t="n">
-        <v>57887</v>
+        <v>98710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490892</v>
+        <v>491075</v>
       </c>
       <c r="R53" t="n">
-        <v>6709919</v>
+        <v>6709942</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6370,7 +6365,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6380,7 +6375,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6407,7 +6402,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129044552</v>
+        <v>129040369</v>
       </c>
       <c r="B54" t="n">
         <v>98710</v>
@@ -6442,10 +6437,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>491075</v>
+        <v>491194</v>
       </c>
       <c r="R54" t="n">
-        <v>6709942</v>
+        <v>6710167</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6477,7 +6472,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6487,7 +6482,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6514,45 +6509,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129040369</v>
+        <v>129038692</v>
       </c>
       <c r="B55" t="n">
-        <v>98710</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>491194</v>
+        <v>490892</v>
       </c>
       <c r="R55" t="n">
-        <v>6710167</v>
+        <v>6709919</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7603,45 +7603,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129037762</v>
+        <v>129039716</v>
       </c>
       <c r="B65" t="n">
-        <v>91543</v>
+        <v>98710</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>490949</v>
+        <v>491118</v>
       </c>
       <c r="R65" t="n">
-        <v>6709885</v>
+        <v>6710111</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7673,7 +7678,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7683,7 +7688,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7710,7 +7720,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129039716</v>
+        <v>129044189</v>
       </c>
       <c r="B66" t="n">
         <v>98710</v>
@@ -7739,21 +7749,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491118</v>
+        <v>491025</v>
       </c>
       <c r="R66" t="n">
-        <v>6710111</v>
+        <v>6709886</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7785,7 +7790,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7795,12 +7800,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7827,7 +7827,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129044189</v>
+        <v>129043659</v>
       </c>
       <c r="B67" t="n">
         <v>98710</v>
@@ -7862,10 +7862,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>491025</v>
+        <v>491126</v>
       </c>
       <c r="R67" t="n">
-        <v>6709886</v>
+        <v>6709977</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7934,7 +7934,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129043659</v>
+        <v>129045555</v>
       </c>
       <c r="B68" t="n">
         <v>98710</v>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>491126</v>
+        <v>490955</v>
       </c>
       <c r="R68" t="n">
-        <v>6709977</v>
+        <v>6709969</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8041,7 +8041,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129045555</v>
+        <v>129039681</v>
       </c>
       <c r="B69" t="n">
         <v>98710</v>
@@ -8070,16 +8070,21 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490955</v>
+        <v>491120</v>
       </c>
       <c r="R69" t="n">
-        <v>6709969</v>
+        <v>6710111</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8111,7 +8116,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8121,7 +8126,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8148,7 +8153,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129039681</v>
+        <v>129038944</v>
       </c>
       <c r="B70" t="n">
         <v>98710</v>
@@ -8177,21 +8182,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>491120</v>
+        <v>490941</v>
       </c>
       <c r="R70" t="n">
-        <v>6710111</v>
+        <v>6709965</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8260,32 +8260,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129038944</v>
+        <v>129037762</v>
       </c>
       <c r="B71" t="n">
-        <v>98710</v>
+        <v>91543</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8295,10 +8295,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490941</v>
+        <v>490949</v>
       </c>
       <c r="R71" t="n">
-        <v>6709965</v>
+        <v>6709885</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -11588,45 +11588,50 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129044617</v>
+        <v>129038846</v>
       </c>
       <c r="B101" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>491091</v>
+        <v>490903</v>
       </c>
       <c r="R101" t="n">
-        <v>6709950</v>
+        <v>6709932</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11658,7 +11663,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11668,7 +11673,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11695,45 +11705,53 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129043760</v>
+        <v>129045506</v>
       </c>
       <c r="B102" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491096</v>
+        <v>490975</v>
       </c>
       <c r="R102" t="n">
-        <v>6709954</v>
+        <v>6709983</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11765,7 +11783,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11775,7 +11793,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Bohål i gran, på ca 2m.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11802,32 +11825,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129040149</v>
+        <v>129043760</v>
       </c>
       <c r="B103" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11837,10 +11860,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491192</v>
+        <v>491096</v>
       </c>
       <c r="R103" t="n">
-        <v>6710147</v>
+        <v>6709954</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11872,7 +11895,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11882,7 +11905,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11909,10 +11932,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129038846</v>
+        <v>129040149</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11920,39 +11943,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>490903</v>
+        <v>491192</v>
       </c>
       <c r="R104" t="n">
-        <v>6709932</v>
+        <v>6710147</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11984,7 +12002,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11994,12 +12012,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12026,53 +12039,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129045506</v>
+        <v>129044617</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>490975</v>
+        <v>491091</v>
       </c>
       <c r="R105" t="n">
-        <v>6709983</v>
+        <v>6709950</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12104,7 +12109,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12114,12 +12119,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Bohål i gran, på ca 2m.</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129039783</v>
+        <v>129039226</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>92827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491113</v>
+        <v>491060</v>
       </c>
       <c r="R2" t="n">
-        <v>6710132</v>
+        <v>6710037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129041992</v>
+        <v>129042946</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491353</v>
+        <v>491232</v>
       </c>
       <c r="R3" t="n">
-        <v>6710077</v>
+        <v>6710086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,50 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129038956</v>
+        <v>129045855</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490939</v>
+        <v>491030</v>
       </c>
       <c r="R4" t="n">
-        <v>6709966</v>
+        <v>6709895</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,45 +1001,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129039226</v>
+        <v>129041481</v>
       </c>
       <c r="B5" t="n">
-        <v>92825</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491060</v>
+        <v>491361</v>
       </c>
       <c r="R5" t="n">
-        <v>6710037</v>
+        <v>6710143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129042946</v>
+        <v>129039783</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>91545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491232</v>
+        <v>491113</v>
       </c>
       <c r="R6" t="n">
-        <v>6710086</v>
+        <v>6710132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På 2 stående.</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,45 +1215,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129045855</v>
+        <v>129041992</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491030</v>
+        <v>491353</v>
       </c>
       <c r="R7" t="n">
-        <v>6709895</v>
+        <v>6710077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,45 +1322,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129041481</v>
+        <v>129038956</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491361</v>
+        <v>490939</v>
       </c>
       <c r="R8" t="n">
-        <v>6710143</v>
+        <v>6709966</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1407,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129043673</v>
+        <v>129039748</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>92827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,39 +1450,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491125</v>
+        <v>491113</v>
       </c>
       <c r="R9" t="n">
-        <v>6709976</v>
+        <v>6710132</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,32 +1546,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129043484</v>
+        <v>129040305</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>75161</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491159</v>
+        <v>491221</v>
       </c>
       <c r="R10" t="n">
-        <v>6709989</v>
+        <v>6710146</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,45 +1653,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129040595</v>
+        <v>129041053</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491251</v>
+        <v>491309</v>
       </c>
       <c r="R11" t="n">
-        <v>6710146</v>
+        <v>6710192</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1738,7 +1738,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,45 +1770,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129045778</v>
+        <v>129043673</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491010</v>
+        <v>491125</v>
       </c>
       <c r="R12" t="n">
-        <v>6709893</v>
+        <v>6709976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129041291</v>
+        <v>129043484</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,14 +1913,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491359</v>
+        <v>491159</v>
       </c>
       <c r="R13" t="n">
-        <v>6710158</v>
+        <v>6709989</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,32 +1989,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129040305</v>
+        <v>129040595</v>
       </c>
       <c r="B14" t="n">
-        <v>75161</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,7 +2024,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491221</v>
+        <v>491251</v>
       </c>
       <c r="R14" t="n">
         <v>6710146</v>
@@ -2049,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,32 +2096,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129039748</v>
+        <v>129045778</v>
       </c>
       <c r="B15" t="n">
-        <v>92825</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491113</v>
+        <v>491010</v>
       </c>
       <c r="R15" t="n">
-        <v>6710132</v>
+        <v>6709893</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,50 +2203,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129041053</v>
+        <v>129041291</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491309</v>
+        <v>491359</v>
       </c>
       <c r="R16" t="n">
-        <v>6710192</v>
+        <v>6710158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2278,12 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129039950</v>
+        <v>129039360</v>
       </c>
       <c r="B17" t="n">
-        <v>91841</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491157</v>
+        <v>491080</v>
       </c>
       <c r="R17" t="n">
-        <v>6710161</v>
+        <v>6710071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,7 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,32 +2422,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129043063</v>
+        <v>129039950</v>
       </c>
       <c r="B18" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491227</v>
+        <v>491157</v>
       </c>
       <c r="R18" t="n">
-        <v>6710010</v>
+        <v>6710161</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,12 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På stenblock.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,32 +2529,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129039360</v>
+        <v>129043063</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491080</v>
+        <v>491227</v>
       </c>
       <c r="R19" t="n">
-        <v>6710071</v>
+        <v>6710010</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På stenblock.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2641,10 +2641,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129040720</v>
+        <v>129040685</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>92827</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,39 +2652,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491296</v>
+        <v>491251</v>
       </c>
       <c r="R20" t="n">
-        <v>6710129</v>
+        <v>6710146</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2716,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,7 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2756,7 +2751,7 @@
         <v>129037863</v>
       </c>
       <c r="B21" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,45 +2855,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129041584</v>
+        <v>129040720</v>
       </c>
       <c r="B22" t="n">
-        <v>91564</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491362</v>
+        <v>491296</v>
       </c>
       <c r="R22" t="n">
-        <v>6710143</v>
+        <v>6710129</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,45 +2967,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129040685</v>
+        <v>129041584</v>
       </c>
       <c r="B23" t="n">
-        <v>92825</v>
+        <v>91566</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491251</v>
+        <v>491362</v>
       </c>
       <c r="R23" t="n">
-        <v>6710146</v>
+        <v>6710143</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,7 +3077,7 @@
         <v>129044129</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,42 +3181,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129042527</v>
+        <v>129040515</v>
       </c>
       <c r="B25" t="n">
-        <v>92825</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3225,10 +3221,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491296</v>
+        <v>491251</v>
       </c>
       <c r="R25" t="n">
-        <v>6710104</v>
+        <v>6710165</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3260,7 +3256,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3270,7 +3266,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,7 +3301,7 @@
         <v>129045240</v>
       </c>
       <c r="B26" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3404,38 +3405,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129040515</v>
+        <v>129042527</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>92827</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3444,10 +3449,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491251</v>
+        <v>491296</v>
       </c>
       <c r="R27" t="n">
-        <v>6710165</v>
+        <v>6710104</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3479,7 +3484,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3489,12 +3494,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,7 +3524,7 @@
         <v>129045583</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>129043562</v>
       </c>
       <c r="B29" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>129041242</v>
       </c>
       <c r="B30" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129040534</v>
+        <v>129044722</v>
       </c>
       <c r="B31" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491261</v>
+        <v>491088</v>
       </c>
       <c r="R31" t="n">
-        <v>6710156</v>
+        <v>6709977</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3922,7 +3922,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,45 +3954,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129040867</v>
+        <v>129040534</v>
       </c>
       <c r="B32" t="n">
-        <v>105774</v>
+        <v>91545</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491332</v>
+        <v>491261</v>
       </c>
       <c r="R32" t="n">
-        <v>6710175</v>
+        <v>6710156</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4019,7 +4024,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4029,7 +4034,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4056,50 +4061,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129039814</v>
+        <v>129038111</v>
       </c>
       <c r="B33" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491102</v>
+        <v>490874</v>
       </c>
       <c r="R33" t="n">
-        <v>6710142</v>
+        <v>6709885</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4131,7 +4136,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4141,7 +4146,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4168,32 +4178,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129039825</v>
+        <v>129044587</v>
       </c>
       <c r="B34" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4203,10 +4213,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491126</v>
+        <v>491075</v>
       </c>
       <c r="R34" t="n">
-        <v>6710148</v>
+        <v>6709943</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,7 +4248,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4248,7 +4258,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4275,59 +4285,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129041725</v>
+        <v>129040867</v>
       </c>
       <c r="B35" t="n">
-        <v>98710</v>
+        <v>105776</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491375</v>
+        <v>491332</v>
       </c>
       <c r="R35" t="n">
-        <v>6710101</v>
+        <v>6710175</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4359,7 +4355,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4369,7 +4365,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4396,45 +4392,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129044722</v>
+        <v>129039814</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491088</v>
+        <v>491102</v>
       </c>
       <c r="R36" t="n">
-        <v>6709977</v>
+        <v>6710142</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4466,7 +4467,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4476,12 +4477,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4508,32 +4504,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129044587</v>
+        <v>129039825</v>
       </c>
       <c r="B37" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4543,10 +4539,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491075</v>
+        <v>491126</v>
       </c>
       <c r="R37" t="n">
-        <v>6709943</v>
+        <v>6710148</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4578,7 +4574,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4588,7 +4584,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4615,50 +4611,59 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129038111</v>
+        <v>129041725</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490874</v>
+        <v>491375</v>
       </c>
       <c r="R38" t="n">
-        <v>6709885</v>
+        <v>6710101</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4690,7 +4695,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4700,12 +4705,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4732,10 +4732,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129038104</v>
+        <v>129045013</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4743,42 +4743,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490880</v>
+        <v>491157</v>
       </c>
       <c r="R39" t="n">
-        <v>6709882</v>
+        <v>6710121</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4810,7 +4802,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4820,12 +4812,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4852,10 +4839,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129045013</v>
+        <v>129040042</v>
       </c>
       <c r="B40" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4863,21 +4850,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4887,10 +4874,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491157</v>
+        <v>491181</v>
       </c>
       <c r="R40" t="n">
-        <v>6710121</v>
+        <v>6710144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4922,7 +4909,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4932,7 +4919,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4959,10 +4946,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129040042</v>
+        <v>129038104</v>
       </c>
       <c r="B41" t="n">
-        <v>91841</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4970,34 +4957,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491181</v>
+        <v>490880</v>
       </c>
       <c r="R41" t="n">
-        <v>6710144</v>
+        <v>6709882</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5029,7 +5024,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5039,7 +5034,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt. Äldre längre ner och färska högre upp på stam.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5069,7 +5069,7 @@
         <v>129044467</v>
       </c>
       <c r="B42" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>129044319</v>
       </c>
       <c r="B43" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5280,45 +5280,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129041044</v>
+        <v>129045330</v>
       </c>
       <c r="B44" t="n">
-        <v>92825</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491306</v>
+        <v>491085</v>
       </c>
       <c r="R44" t="n">
-        <v>6710197</v>
+        <v>6710033</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5350,7 +5355,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5360,7 +5365,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5387,50 +5397,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129045330</v>
+        <v>129041044</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>92827</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491085</v>
+        <v>491306</v>
       </c>
       <c r="R45" t="n">
-        <v>6710033</v>
+        <v>6710197</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5462,7 +5467,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5472,12 +5477,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5504,45 +5504,59 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129037802</v>
+        <v>129039795</v>
       </c>
       <c r="B46" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490941</v>
+        <v>491106</v>
       </c>
       <c r="R46" t="n">
-        <v>6709886</v>
+        <v>6710124</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5574,7 +5588,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5584,7 +5598,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5611,10 +5625,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129039795</v>
+        <v>129042338</v>
       </c>
       <c r="B47" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5646,24 +5660,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491106</v>
+        <v>491335</v>
       </c>
       <c r="R47" t="n">
-        <v>6710124</v>
+        <v>6710120</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5695,7 +5709,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5705,7 +5719,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5732,59 +5751,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129042338</v>
+        <v>129037802</v>
       </c>
       <c r="B48" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491335</v>
+        <v>490941</v>
       </c>
       <c r="R48" t="n">
-        <v>6710120</v>
+        <v>6709886</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5816,7 +5821,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5826,12 +5831,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5861,7 +5861,7 @@
         <v>129038812</v>
       </c>
       <c r="B49" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>129044332</v>
       </c>
       <c r="B50" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>129045046</v>
       </c>
       <c r="B51" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>129039883</v>
       </c>
       <c r="B52" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6295,45 +6295,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129044552</v>
+        <v>129038692</v>
       </c>
       <c r="B53" t="n">
-        <v>98710</v>
+        <v>57887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>491075</v>
+        <v>490892</v>
       </c>
       <c r="R53" t="n">
-        <v>6709942</v>
+        <v>6709919</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6365,7 +6370,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6375,7 +6380,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6402,10 +6407,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129040369</v>
+        <v>129044552</v>
       </c>
       <c r="B54" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6437,10 +6442,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>491194</v>
+        <v>491075</v>
       </c>
       <c r="R54" t="n">
-        <v>6710167</v>
+        <v>6709942</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6472,7 +6477,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6482,7 +6487,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6509,50 +6514,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129038692</v>
+        <v>129040369</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>98712</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490892</v>
+        <v>491194</v>
       </c>
       <c r="R55" t="n">
-        <v>6709919</v>
+        <v>6710167</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6621,10 +6621,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129037776</v>
+        <v>129039941</v>
       </c>
       <c r="B56" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490952</v>
+        <v>491158</v>
       </c>
       <c r="R56" t="n">
-        <v>6709889</v>
+        <v>6710160</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6731,7 +6731,7 @@
         <v>129040007</v>
       </c>
       <c r="B57" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6835,10 +6835,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129039941</v>
+        <v>129037776</v>
       </c>
       <c r="B58" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>491158</v>
+        <v>490952</v>
       </c>
       <c r="R58" t="n">
-        <v>6710160</v>
+        <v>6709889</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,7 +6945,7 @@
         <v>129038411</v>
       </c>
       <c r="B59" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>129044061</v>
       </c>
       <c r="B60" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>129045420</v>
       </c>
       <c r="B61" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>129038173</v>
       </c>
       <c r="B62" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>129043992</v>
       </c>
       <c r="B63" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7491,45 +7491,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129042106</v>
+        <v>129039716</v>
       </c>
       <c r="B64" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>491327</v>
+        <v>491118</v>
       </c>
       <c r="R64" t="n">
-        <v>6710067</v>
+        <v>6710111</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7561,7 +7566,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7571,12 +7576,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7603,10 +7608,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129039716</v>
+        <v>129044189</v>
       </c>
       <c r="B65" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7632,21 +7637,16 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>491118</v>
+        <v>491025</v>
       </c>
       <c r="R65" t="n">
-        <v>6710111</v>
+        <v>6709886</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7688,12 +7688,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7720,10 +7715,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129044189</v>
+        <v>129043659</v>
       </c>
       <c r="B66" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7755,10 +7750,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491025</v>
+        <v>491126</v>
       </c>
       <c r="R66" t="n">
-        <v>6709886</v>
+        <v>6709977</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7790,7 +7785,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7800,7 +7795,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7827,10 +7822,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129043659</v>
+        <v>129045555</v>
       </c>
       <c r="B67" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7862,10 +7857,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>491126</v>
+        <v>490955</v>
       </c>
       <c r="R67" t="n">
-        <v>6709977</v>
+        <v>6709969</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7897,7 +7892,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7907,7 +7902,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7934,10 +7929,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129045555</v>
+        <v>129039681</v>
       </c>
       <c r="B68" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7963,16 +7958,21 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>490955</v>
+        <v>491120</v>
       </c>
       <c r="R68" t="n">
-        <v>6709969</v>
+        <v>6710111</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8041,10 +8041,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129039681</v>
+        <v>129038944</v>
       </c>
       <c r="B69" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8070,21 +8070,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>491120</v>
+        <v>490941</v>
       </c>
       <c r="R69" t="n">
-        <v>6710111</v>
+        <v>6709965</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8116,7 +8111,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8126,7 +8121,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8153,32 +8148,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129038944</v>
+        <v>129037762</v>
       </c>
       <c r="B70" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8188,10 +8183,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490941</v>
+        <v>490949</v>
       </c>
       <c r="R70" t="n">
-        <v>6709965</v>
+        <v>6709885</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8223,7 +8218,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8233,7 +8228,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8260,10 +8255,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129037762</v>
+        <v>129042106</v>
       </c>
       <c r="B71" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8271,21 +8266,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8295,10 +8290,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>490949</v>
+        <v>491327</v>
       </c>
       <c r="R71" t="n">
-        <v>6709885</v>
+        <v>6710067</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8330,7 +8325,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8340,7 +8335,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8367,50 +8367,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129038223</v>
+        <v>129040051</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>490878</v>
+        <v>491183</v>
       </c>
       <c r="R72" t="n">
-        <v>6709889</v>
+        <v>6710141</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8442,7 +8437,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8452,7 +8447,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8479,45 +8474,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129040051</v>
+        <v>129038053</v>
       </c>
       <c r="B73" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>491183</v>
+        <v>490886</v>
       </c>
       <c r="R73" t="n">
-        <v>6710141</v>
+        <v>6709872</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8559,7 +8559,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8586,45 +8591,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129042724</v>
+        <v>129038223</v>
       </c>
       <c r="B74" t="n">
-        <v>92861</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>491257</v>
+        <v>490878</v>
       </c>
       <c r="R74" t="n">
-        <v>6710085</v>
+        <v>6709889</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8656,7 +8666,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8666,7 +8676,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8696,7 +8706,7 @@
         <v>129040356</v>
       </c>
       <c r="B75" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8803,7 +8813,7 @@
         <v>129043183</v>
       </c>
       <c r="B76" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8912,50 +8922,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129038053</v>
+        <v>129042724</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>92863</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>490886</v>
+        <v>491257</v>
       </c>
       <c r="R77" t="n">
-        <v>6709872</v>
+        <v>6710085</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8987,7 +8992,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8997,12 +9002,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:46</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9032,7 +9032,7 @@
         <v>129040173</v>
       </c>
       <c r="B78" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>129039515</v>
       </c>
       <c r="B79" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>129043352</v>
       </c>
       <c r="B80" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>129044818</v>
       </c>
       <c r="B81" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>129039994</v>
       </c>
       <c r="B85" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9920,32 +9920,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129040273</v>
+        <v>129039427</v>
       </c>
       <c r="B86" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9955,10 +9955,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>491210</v>
+        <v>491089</v>
       </c>
       <c r="R86" t="n">
-        <v>6710152</v>
+        <v>6710079</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10000,12 +10000,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10032,45 +10027,59 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129042243</v>
+        <v>129039369</v>
       </c>
       <c r="B87" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491324</v>
+        <v>491082</v>
       </c>
       <c r="R87" t="n">
-        <v>6710108</v>
+        <v>6710072</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10102,7 +10111,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10112,12 +10121,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10144,32 +10148,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129043457</v>
+        <v>129040090</v>
       </c>
       <c r="B88" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10179,10 +10183,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491159</v>
+        <v>491189</v>
       </c>
       <c r="R88" t="n">
-        <v>6709989</v>
+        <v>6710146</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10214,7 +10218,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10224,12 +10228,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10256,32 +10255,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129039427</v>
+        <v>129045737</v>
       </c>
       <c r="B89" t="n">
-        <v>98710</v>
+        <v>92827</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10291,10 +10290,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491089</v>
+        <v>491006</v>
       </c>
       <c r="R89" t="n">
-        <v>6710079</v>
+        <v>6709889</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10326,7 +10325,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10336,7 +10335,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10363,59 +10362,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129039369</v>
+        <v>129040273</v>
       </c>
       <c r="B90" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491082</v>
+        <v>491210</v>
       </c>
       <c r="R90" t="n">
-        <v>6710072</v>
+        <v>6710152</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10447,7 +10432,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10457,7 +10442,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10484,45 +10474,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129040090</v>
+        <v>129042243</v>
       </c>
       <c r="B91" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491189</v>
+        <v>491324</v>
       </c>
       <c r="R91" t="n">
-        <v>6710146</v>
+        <v>6710108</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10554,7 +10544,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10564,7 +10554,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10591,10 +10586,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129043286</v>
+        <v>129043457</v>
       </c>
       <c r="B92" t="n">
-        <v>91564</v>
+        <v>79044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10602,43 +10597,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491185</v>
+        <v>491159</v>
       </c>
       <c r="R92" t="n">
-        <v>6710038</v>
+        <v>6709989</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10670,7 +10656,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10680,7 +10666,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10707,45 +10698,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129045737</v>
+        <v>129043286</v>
       </c>
       <c r="B93" t="n">
-        <v>92825</v>
+        <v>91566</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491006</v>
+        <v>491185</v>
       </c>
       <c r="R93" t="n">
-        <v>6709889</v>
+        <v>6710038</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10814,45 +10814,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129041984</v>
+        <v>129043344</v>
       </c>
       <c r="B94" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>491353</v>
+        <v>491176</v>
       </c>
       <c r="R94" t="n">
-        <v>6710077</v>
+        <v>6710019</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10884,7 +10884,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10921,50 +10921,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129041444</v>
+        <v>129044713</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>491362</v>
+        <v>491086</v>
       </c>
       <c r="R95" t="n">
-        <v>6710150</v>
+        <v>6709974</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10996,7 +10991,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11006,12 +11001,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11038,10 +11028,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129043344</v>
+        <v>129044360</v>
       </c>
       <c r="B96" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11073,10 +11063,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>491176</v>
+        <v>491050</v>
       </c>
       <c r="R96" t="n">
-        <v>6710019</v>
+        <v>6709915</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11108,7 +11098,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11118,7 +11108,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11145,10 +11135,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129044713</v>
+        <v>129041232</v>
       </c>
       <c r="B97" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11174,16 +11164,21 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>491086</v>
+        <v>491336</v>
       </c>
       <c r="R97" t="n">
-        <v>6709974</v>
+        <v>6710188</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11215,7 +11210,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11225,7 +11220,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11252,10 +11247,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129044360</v>
+        <v>129045097</v>
       </c>
       <c r="B98" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11281,16 +11276,21 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491050</v>
+        <v>491132</v>
       </c>
       <c r="R98" t="n">
-        <v>6709915</v>
+        <v>6710123</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11332,7 +11332,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11359,50 +11364,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129041232</v>
+        <v>129041984</v>
       </c>
       <c r="B99" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491336</v>
+        <v>491353</v>
       </c>
       <c r="R99" t="n">
-        <v>6710188</v>
+        <v>6710077</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11434,7 +11434,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11471,50 +11471,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129045097</v>
+        <v>129041444</v>
       </c>
       <c r="B100" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491132</v>
+        <v>491362</v>
       </c>
       <c r="R100" t="n">
-        <v>6710123</v>
+        <v>6710150</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11556,12 +11556,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11825,32 +11825,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129043760</v>
+        <v>129040149</v>
       </c>
       <c r="B103" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491096</v>
+        <v>491192</v>
       </c>
       <c r="R103" t="n">
-        <v>6709954</v>
+        <v>6710147</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11932,32 +11932,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129040149</v>
+        <v>129044617</v>
       </c>
       <c r="B104" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11967,10 +11967,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491192</v>
+        <v>491091</v>
       </c>
       <c r="R104" t="n">
-        <v>6710147</v>
+        <v>6709950</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12039,10 +12039,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129044617</v>
+        <v>129043760</v>
       </c>
       <c r="B105" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12074,10 +12074,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491091</v>
+        <v>491096</v>
       </c>
       <c r="R105" t="n">
-        <v>6709950</v>
+        <v>6709954</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12146,45 +12146,54 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129039623</v>
+        <v>129039218</v>
       </c>
       <c r="B106" t="n">
-        <v>91543</v>
+        <v>92827</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491117</v>
+        <v>491054</v>
       </c>
       <c r="R106" t="n">
-        <v>6710091</v>
+        <v>6710041</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12216,7 +12225,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12226,7 +12235,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12253,54 +12262,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129039218</v>
+        <v>129039623</v>
       </c>
       <c r="B107" t="n">
-        <v>92825</v>
+        <v>91545</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491054</v>
+        <v>491117</v>
       </c>
       <c r="R107" t="n">
-        <v>6710041</v>
+        <v>6710091</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12369,32 +12369,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129042566</v>
+        <v>129039646</v>
       </c>
       <c r="B108" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12404,10 +12404,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>491288</v>
+        <v>491117</v>
       </c>
       <c r="R108" t="n">
-        <v>6710104</v>
+        <v>6710091</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12449,7 +12449,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12476,10 +12481,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129044243</v>
+        <v>129042566</v>
       </c>
       <c r="B109" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12511,10 +12516,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491026</v>
+        <v>491288</v>
       </c>
       <c r="R109" t="n">
-        <v>6709889</v>
+        <v>6710104</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12546,7 +12551,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12556,7 +12561,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12583,32 +12588,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129039646</v>
+        <v>129044243</v>
       </c>
       <c r="B110" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12618,10 +12623,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491117</v>
+        <v>491026</v>
       </c>
       <c r="R110" t="n">
-        <v>6710091</v>
+        <v>6709889</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12653,7 +12658,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12663,12 +12668,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129039226</v>
       </c>
       <c r="B2" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129042946</v>
+        <v>129038956</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491232</v>
+        <v>490939</v>
       </c>
       <c r="R3" t="n">
-        <v>6710086</v>
+        <v>6709966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På 2 stående.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129045855</v>
+        <v>129042946</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491030</v>
+        <v>491232</v>
       </c>
       <c r="R4" t="n">
-        <v>6709895</v>
+        <v>6710086</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På 2 stående.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129041481</v>
+        <v>129045855</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,14 +1042,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491361</v>
+        <v>491030</v>
       </c>
       <c r="R5" t="n">
-        <v>6710143</v>
+        <v>6709895</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,45 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129039783</v>
+        <v>129041481</v>
       </c>
       <c r="B6" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491113</v>
+        <v>491361</v>
       </c>
       <c r="R6" t="n">
-        <v>6710132</v>
+        <v>6710143</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129041992</v>
+        <v>129039783</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,14 +1256,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491353</v>
+        <v>491113</v>
       </c>
       <c r="R7" t="n">
-        <v>6710077</v>
+        <v>6710132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129038956</v>
+        <v>129041992</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,39 +1343,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490939</v>
+        <v>491353</v>
       </c>
       <c r="R8" t="n">
-        <v>6709966</v>
+        <v>6710077</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,12 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1442,7 @@
         <v>129039748</v>
       </c>
       <c r="B9" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>129043484</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>129040595</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>129045778</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129041291</v>
       </c>
       <c r="B16" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129039360</v>
+        <v>129039950</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>91847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,21 +2321,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491080</v>
+        <v>491157</v>
       </c>
       <c r="R17" t="n">
-        <v>6710071</v>
+        <v>6710161</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2390,12 +2390,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129039950</v>
+        <v>129039360</v>
       </c>
       <c r="B18" t="n">
-        <v>91843</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,21 +2428,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491157</v>
+        <v>491080</v>
       </c>
       <c r="R18" t="n">
-        <v>6710161</v>
+        <v>6710071</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2502,7 +2497,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,7 +2532,7 @@
         <v>129043063</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>129040685</v>
       </c>
       <c r="B20" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>129037863</v>
       </c>
       <c r="B21" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,50 +2855,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129040720</v>
+        <v>129041584</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>91570</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491296</v>
+        <v>491362</v>
       </c>
       <c r="R22" t="n">
-        <v>6710129</v>
+        <v>6710143</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,7 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,45 +2962,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129041584</v>
+        <v>129044129</v>
       </c>
       <c r="B23" t="n">
-        <v>91566</v>
+        <v>98716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491362</v>
+        <v>491049</v>
       </c>
       <c r="R23" t="n">
-        <v>6710143</v>
+        <v>6709893</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,7 +3032,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3047,7 +3042,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,45 +3069,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129044129</v>
+        <v>129040720</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491049</v>
+        <v>491296</v>
       </c>
       <c r="R24" t="n">
-        <v>6709893</v>
+        <v>6710129</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129040515</v>
+        <v>129045240</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,39 +3192,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491251</v>
+        <v>491133</v>
       </c>
       <c r="R25" t="n">
-        <v>6710165</v>
+        <v>6710118</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,7 +3251,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3266,12 +3261,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:39</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3298,45 +3288,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129045240</v>
+        <v>129042527</v>
       </c>
       <c r="B26" t="n">
-        <v>91843</v>
+        <v>92831</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491133</v>
+        <v>491296</v>
       </c>
       <c r="R26" t="n">
-        <v>6710118</v>
+        <v>6710104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3368,7 +3367,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3378,7 +3377,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3405,54 +3404,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129042527</v>
+        <v>129045583</v>
       </c>
       <c r="B27" t="n">
-        <v>92827</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491296</v>
+        <v>490946</v>
       </c>
       <c r="R27" t="n">
-        <v>6710104</v>
+        <v>6709935</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3484,7 +3474,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3494,7 +3484,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,10 +3511,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129045583</v>
+        <v>129043562</v>
       </c>
       <c r="B28" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,10 +3546,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490946</v>
+        <v>491129</v>
       </c>
       <c r="R28" t="n">
-        <v>6709935</v>
+        <v>6709987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3591,7 +3581,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3601,7 +3591,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3628,10 +3618,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129043562</v>
+        <v>129041242</v>
       </c>
       <c r="B29" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,14 +3649,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491129</v>
+        <v>491341</v>
       </c>
       <c r="R29" t="n">
-        <v>6709987</v>
+        <v>6710206</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3688,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3708,7 +3698,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,45 +3725,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129041242</v>
+        <v>129040515</v>
       </c>
       <c r="B30" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491341</v>
+        <v>491251</v>
       </c>
       <c r="R30" t="n">
-        <v>6710206</v>
+        <v>6710165</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3805,7 +3800,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3815,7 +3810,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3957,7 +3957,7 @@
         <v>129040534</v>
       </c>
       <c r="B32" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,10 +4061,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129038111</v>
+        <v>129044587</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>91847</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4072,39 +4072,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490874</v>
+        <v>491075</v>
       </c>
       <c r="R33" t="n">
-        <v>6709885</v>
+        <v>6709943</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4136,7 +4131,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4146,12 +4141,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4178,45 +4168,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129044587</v>
+        <v>129040867</v>
       </c>
       <c r="B34" t="n">
-        <v>91843</v>
+        <v>105780</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491075</v>
+        <v>491332</v>
       </c>
       <c r="R34" t="n">
-        <v>6709943</v>
+        <v>6710175</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4248,7 +4238,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4258,7 +4248,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4285,45 +4275,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129040867</v>
+        <v>129039814</v>
       </c>
       <c r="B35" t="n">
-        <v>105776</v>
+        <v>98716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491332</v>
+        <v>491102</v>
       </c>
       <c r="R35" t="n">
-        <v>6710175</v>
+        <v>6710142</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4355,7 +4350,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4365,7 +4360,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4392,10 +4387,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129039814</v>
+        <v>129039825</v>
       </c>
       <c r="B36" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4421,21 +4416,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491102</v>
+        <v>491126</v>
       </c>
       <c r="R36" t="n">
-        <v>6710142</v>
+        <v>6710148</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4467,7 +4457,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4477,7 +4467,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4504,10 +4494,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129039825</v>
+        <v>129041725</v>
       </c>
       <c r="B37" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4532,17 +4522,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491126</v>
+        <v>491375</v>
       </c>
       <c r="R37" t="n">
-        <v>6710148</v>
+        <v>6710101</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4574,7 +4578,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4584,7 +4588,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4611,59 +4615,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129041725</v>
+        <v>129038111</v>
       </c>
       <c r="B38" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491375</v>
+        <v>490874</v>
       </c>
       <c r="R38" t="n">
-        <v>6710101</v>
+        <v>6709885</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4695,7 +4690,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4705,7 +4700,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4735,7 +4735,7 @@
         <v>129045013</v>
       </c>
       <c r="B39" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>129040042</v>
       </c>
       <c r="B40" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>129044467</v>
       </c>
       <c r="B42" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>129044319</v>
       </c>
       <c r="B43" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5280,50 +5280,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129045330</v>
+        <v>129041044</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>92831</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491085</v>
+        <v>491306</v>
       </c>
       <c r="R44" t="n">
-        <v>6710033</v>
+        <v>6710197</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5355,7 +5350,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5365,12 +5360,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5397,45 +5387,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129041044</v>
+        <v>129045330</v>
       </c>
       <c r="B45" t="n">
-        <v>92827</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491306</v>
+        <v>491085</v>
       </c>
       <c r="R45" t="n">
-        <v>6710197</v>
+        <v>6710033</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5467,7 +5462,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5477,7 +5472,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5504,59 +5504,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129039795</v>
+        <v>129037802</v>
       </c>
       <c r="B46" t="n">
-        <v>98712</v>
+        <v>91847</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491106</v>
+        <v>490941</v>
       </c>
       <c r="R46" t="n">
-        <v>6710124</v>
+        <v>6709886</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5588,7 +5574,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5598,7 +5584,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5625,10 +5611,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129042338</v>
+        <v>129039795</v>
       </c>
       <c r="B47" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5660,24 +5646,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491335</v>
+        <v>491106</v>
       </c>
       <c r="R47" t="n">
-        <v>6710120</v>
+        <v>6710124</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5709,7 +5695,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5719,12 +5705,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:03</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5751,45 +5732,59 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129037802</v>
+        <v>129042338</v>
       </c>
       <c r="B48" t="n">
-        <v>91843</v>
+        <v>98716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490941</v>
+        <v>491335</v>
       </c>
       <c r="R48" t="n">
-        <v>6709886</v>
+        <v>6710120</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5821,7 +5816,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5831,7 +5826,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5858,54 +5858,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129038812</v>
+        <v>129044332</v>
       </c>
       <c r="B49" t="n">
-        <v>92827</v>
+        <v>98716</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490918</v>
+        <v>491049</v>
       </c>
       <c r="R49" t="n">
-        <v>6709933</v>
+        <v>6709914</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5937,7 +5928,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5947,7 +5938,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5974,10 +5965,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129044332</v>
+        <v>129045046</v>
       </c>
       <c r="B50" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6009,10 +6000,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491049</v>
+        <v>491153</v>
       </c>
       <c r="R50" t="n">
-        <v>6709914</v>
+        <v>6710121</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6044,7 +6035,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6054,7 +6045,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6081,10 +6072,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129045046</v>
+        <v>129039883</v>
       </c>
       <c r="B51" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6116,10 +6107,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>491153</v>
+        <v>491128</v>
       </c>
       <c r="R51" t="n">
-        <v>6710121</v>
+        <v>6710150</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6151,7 +6142,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6161,7 +6152,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6188,45 +6179,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129039883</v>
+        <v>129038812</v>
       </c>
       <c r="B52" t="n">
-        <v>98712</v>
+        <v>92831</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>491128</v>
+        <v>490918</v>
       </c>
       <c r="R52" t="n">
-        <v>6710150</v>
+        <v>6709933</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6295,50 +6295,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129038692</v>
+        <v>129044552</v>
       </c>
       <c r="B53" t="n">
-        <v>57887</v>
+        <v>98716</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490892</v>
+        <v>491075</v>
       </c>
       <c r="R53" t="n">
-        <v>6709919</v>
+        <v>6709942</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6370,7 +6365,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6380,7 +6375,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6407,10 +6402,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129044552</v>
+        <v>129040369</v>
       </c>
       <c r="B54" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6442,10 +6437,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>491075</v>
+        <v>491194</v>
       </c>
       <c r="R54" t="n">
-        <v>6709942</v>
+        <v>6710167</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6477,7 +6472,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6487,7 +6482,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6514,45 +6509,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129040369</v>
+        <v>129038692</v>
       </c>
       <c r="B55" t="n">
-        <v>98712</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>491194</v>
+        <v>490892</v>
       </c>
       <c r="R55" t="n">
-        <v>6710167</v>
+        <v>6709919</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6621,10 +6621,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129039941</v>
+        <v>129037776</v>
       </c>
       <c r="B56" t="n">
-        <v>91545</v>
+        <v>91847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>491158</v>
+        <v>490952</v>
       </c>
       <c r="R56" t="n">
-        <v>6710160</v>
+        <v>6709889</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6731,7 +6731,7 @@
         <v>129040007</v>
       </c>
       <c r="B57" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6835,10 +6835,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129037776</v>
+        <v>129039941</v>
       </c>
       <c r="B58" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490952</v>
+        <v>491158</v>
       </c>
       <c r="R58" t="n">
-        <v>6709889</v>
+        <v>6710160</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,7 +6945,7 @@
         <v>129038411</v>
       </c>
       <c r="B59" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>129044061</v>
       </c>
       <c r="B60" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>129045420</v>
       </c>
       <c r="B61" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>129038173</v>
       </c>
       <c r="B62" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>129043992</v>
       </c>
       <c r="B63" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7491,50 +7491,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129039716</v>
+        <v>129037762</v>
       </c>
       <c r="B64" t="n">
-        <v>98712</v>
+        <v>91549</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>491118</v>
+        <v>490949</v>
       </c>
       <c r="R64" t="n">
-        <v>6710111</v>
+        <v>6709885</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7566,7 +7561,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7576,12 +7571,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7608,32 +7598,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129044189</v>
+        <v>129042106</v>
       </c>
       <c r="B65" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7643,10 +7633,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>491025</v>
+        <v>491327</v>
       </c>
       <c r="R65" t="n">
-        <v>6709886</v>
+        <v>6710067</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7678,7 +7668,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7688,7 +7678,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7715,10 +7710,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129043659</v>
+        <v>129039716</v>
       </c>
       <c r="B66" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7744,16 +7739,21 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491126</v>
+        <v>491118</v>
       </c>
       <c r="R66" t="n">
-        <v>6709977</v>
+        <v>6710111</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7795,7 +7795,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Små blockingt, med ett surdråg sydväst denna höjd.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7822,10 +7827,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129045555</v>
+        <v>129044189</v>
       </c>
       <c r="B67" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7857,10 +7862,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>490955</v>
+        <v>491025</v>
       </c>
       <c r="R67" t="n">
-        <v>6709969</v>
+        <v>6709886</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7892,7 +7897,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7902,7 +7907,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7929,10 +7934,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129039681</v>
+        <v>129043659</v>
       </c>
       <c r="B68" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7958,21 +7963,16 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>491120</v>
+        <v>491126</v>
       </c>
       <c r="R68" t="n">
-        <v>6710111</v>
+        <v>6709977</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8041,10 +8041,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129038944</v>
+        <v>129045555</v>
       </c>
       <c r="B69" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8076,10 +8076,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>490941</v>
+        <v>490955</v>
       </c>
       <c r="R69" t="n">
-        <v>6709965</v>
+        <v>6709969</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8148,45 +8148,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129037762</v>
+        <v>129039681</v>
       </c>
       <c r="B70" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>490949</v>
+        <v>491120</v>
       </c>
       <c r="R70" t="n">
-        <v>6709885</v>
+        <v>6710111</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8218,7 +8223,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8228,7 +8233,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8255,32 +8260,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129042106</v>
+        <v>129038944</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8290,10 +8295,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>491327</v>
+        <v>490941</v>
       </c>
       <c r="R71" t="n">
-        <v>6710067</v>
+        <v>6709965</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8325,7 +8330,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8335,12 +8340,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8367,45 +8367,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129040051</v>
+        <v>129038053</v>
       </c>
       <c r="B72" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>491183</v>
+        <v>490886</v>
       </c>
       <c r="R72" t="n">
-        <v>6710141</v>
+        <v>6709872</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8437,7 +8442,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8447,7 +8452,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, rikligt.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8474,50 +8484,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129038053</v>
+        <v>129042724</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>92867</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>490886</v>
+        <v>491257</v>
       </c>
       <c r="R73" t="n">
-        <v>6709872</v>
+        <v>6710085</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8549,7 +8554,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8559,12 +8564,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:46</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, rikligt.</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8591,10 +8591,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129038223</v>
+        <v>129040356</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8602,39 +8602,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lissan, Lissan, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>490878</v>
+        <v>491211</v>
       </c>
       <c r="R74" t="n">
-        <v>6709889</v>
+        <v>6710165</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8666,7 +8661,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8676,7 +8671,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8703,7 +8698,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129040356</v>
+        <v>129043183</v>
       </c>
       <c r="B75" t="n">
         <v>79044</v>
@@ -8738,10 +8733,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>491211</v>
+        <v>491200</v>
       </c>
       <c r="R75" t="n">
-        <v>6710165</v>
+        <v>6709983</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8773,7 +8768,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8783,7 +8778,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8810,10 +8810,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129043183</v>
+        <v>129038223</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8821,34 +8821,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Lissan, Lissan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>491200</v>
+        <v>490878</v>
       </c>
       <c r="R76" t="n">
-        <v>6709983</v>
+        <v>6709889</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8880,7 +8885,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8890,12 +8895,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8922,32 +8922,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129042724</v>
+        <v>129040051</v>
       </c>
       <c r="B77" t="n">
-        <v>92863</v>
+        <v>98716</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8957,10 +8957,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>491257</v>
+        <v>491183</v>
       </c>
       <c r="R77" t="n">
-        <v>6710085</v>
+        <v>6710141</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9032,7 +9032,7 @@
         <v>129040173</v>
       </c>
       <c r="B78" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>129039515</v>
       </c>
       <c r="B79" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>129043352</v>
       </c>
       <c r="B80" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9355,10 +9355,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129044818</v>
+        <v>129042971</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9366,34 +9366,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>491116</v>
+        <v>491193</v>
       </c>
       <c r="R81" t="n">
-        <v>6710020</v>
+        <v>6710074</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9425,7 +9430,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9435,12 +9440,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9467,7 +9472,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129042971</v>
+        <v>129039011</v>
       </c>
       <c r="B82" t="n">
         <v>57727</v>
@@ -9507,10 +9512,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>491193</v>
+        <v>490936</v>
       </c>
       <c r="R82" t="n">
-        <v>6710074</v>
+        <v>6709979</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9542,7 +9547,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9552,7 +9557,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9584,10 +9589,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129039011</v>
+        <v>129044818</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9595,39 +9600,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>490936</v>
+        <v>491116</v>
       </c>
       <c r="R83" t="n">
-        <v>6709979</v>
+        <v>6710020</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9816,7 +9816,7 @@
         <v>129039994</v>
       </c>
       <c r="B85" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9920,45 +9920,54 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129039427</v>
+        <v>129043286</v>
       </c>
       <c r="B86" t="n">
-        <v>98712</v>
+        <v>91570</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>491089</v>
+        <v>491185</v>
       </c>
       <c r="R86" t="n">
-        <v>6710079</v>
+        <v>6710038</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9990,7 +9999,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10000,7 +10009,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10027,59 +10036,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129039369</v>
+        <v>129040273</v>
       </c>
       <c r="B87" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>491082</v>
+        <v>491210</v>
       </c>
       <c r="R87" t="n">
-        <v>6710072</v>
+        <v>6710152</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10111,7 +10106,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10121,7 +10116,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Hänglavsrikt, opåverkat.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10148,45 +10148,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129040090</v>
+        <v>129042243</v>
       </c>
       <c r="B88" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491189</v>
+        <v>491324</v>
       </c>
       <c r="R88" t="n">
-        <v>6710146</v>
+        <v>6710108</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10228,7 +10228,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10255,32 +10260,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129045737</v>
+        <v>129043457</v>
       </c>
       <c r="B89" t="n">
-        <v>92827</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10290,10 +10295,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>491006</v>
+        <v>491159</v>
       </c>
       <c r="R89" t="n">
-        <v>6709889</v>
+        <v>6709989</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10325,7 +10330,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10335,7 +10340,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10362,32 +10372,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129040273</v>
+        <v>129039427</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10397,10 +10407,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>491210</v>
+        <v>491089</v>
       </c>
       <c r="R90" t="n">
-        <v>6710152</v>
+        <v>6710079</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10432,7 +10442,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10442,12 +10452,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Hänglavsrikt, opåverkat.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10474,45 +10479,59 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129042243</v>
+        <v>129039369</v>
       </c>
       <c r="B91" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sivikstad, Sivikstad, Dlr</t>
+          <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491324</v>
+        <v>491082</v>
       </c>
       <c r="R91" t="n">
-        <v>6710108</v>
+        <v>6710072</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10544,7 +10563,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10554,12 +10573,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10586,32 +10600,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129043457</v>
+        <v>129040090</v>
       </c>
       <c r="B92" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10621,10 +10635,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>491159</v>
+        <v>491189</v>
       </c>
       <c r="R92" t="n">
-        <v>6709989</v>
+        <v>6710146</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10656,7 +10670,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10666,12 +10680,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10698,54 +10707,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129043286</v>
+        <v>129045737</v>
       </c>
       <c r="B93" t="n">
-        <v>91566</v>
+        <v>92831</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>491185</v>
+        <v>491006</v>
       </c>
       <c r="R93" t="n">
-        <v>6710038</v>
+        <v>6709889</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10817,7 +10817,7 @@
         <v>129043344</v>
       </c>
       <c r="B94" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>129044713</v>
       </c>
       <c r="B95" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>129044360</v>
       </c>
       <c r="B96" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>129041232</v>
       </c>
       <c r="B97" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>129045097</v>
       </c>
       <c r="B98" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11364,10 +11364,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129041984</v>
+        <v>129041444</v>
       </c>
       <c r="B99" t="n">
-        <v>91843</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11375,34 +11375,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>491353</v>
+        <v>491362</v>
       </c>
       <c r="R99" t="n">
-        <v>6710077</v>
+        <v>6710150</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11434,7 +11439,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11444,7 +11449,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11471,10 +11481,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129041444</v>
+        <v>129041984</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>91847</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11482,39 +11492,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>491362</v>
+        <v>491353</v>
       </c>
       <c r="R100" t="n">
-        <v>6710150</v>
+        <v>6710077</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11546,7 +11551,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11556,12 +11561,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11825,32 +11825,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129040149</v>
+        <v>129044617</v>
       </c>
       <c r="B103" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11860,10 +11860,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>491192</v>
+        <v>491091</v>
       </c>
       <c r="R103" t="n">
-        <v>6710147</v>
+        <v>6709950</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11932,10 +11932,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129044617</v>
+        <v>129043760</v>
       </c>
       <c r="B104" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11967,10 +11967,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491091</v>
+        <v>491096</v>
       </c>
       <c r="R104" t="n">
-        <v>6709950</v>
+        <v>6709954</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12039,32 +12039,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129043760</v>
+        <v>129040149</v>
       </c>
       <c r="B105" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12074,10 +12074,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491096</v>
+        <v>491192</v>
       </c>
       <c r="R105" t="n">
-        <v>6709954</v>
+        <v>6710147</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12146,54 +12146,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129039218</v>
+        <v>129042566</v>
       </c>
       <c r="B106" t="n">
-        <v>92827</v>
+        <v>98716</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>491054</v>
+        <v>491288</v>
       </c>
       <c r="R106" t="n">
-        <v>6710041</v>
+        <v>6710104</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12225,7 +12216,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12235,7 +12226,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12262,32 +12253,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129039623</v>
+        <v>129044243</v>
       </c>
       <c r="B107" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12297,10 +12288,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491117</v>
+        <v>491026</v>
       </c>
       <c r="R107" t="n">
-        <v>6710091</v>
+        <v>6709889</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12332,7 +12323,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12342,7 +12333,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12369,10 +12360,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129039646</v>
+        <v>129039623</v>
       </c>
       <c r="B108" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12380,21 +12371,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12439,7 +12430,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12449,12 +12440,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12481,32 +12467,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129042566</v>
+        <v>129039646</v>
       </c>
       <c r="B109" t="n">
-        <v>98712</v>
+        <v>91847</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12516,10 +12502,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>491288</v>
+        <v>491117</v>
       </c>
       <c r="R109" t="n">
-        <v>6710104</v>
+        <v>6710091</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12551,7 +12537,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12561,7 +12547,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12588,45 +12579,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129044243</v>
+        <v>129039218</v>
       </c>
       <c r="B110" t="n">
-        <v>98712</v>
+        <v>92831</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>491026</v>
+        <v>491054</v>
       </c>
       <c r="R110" t="n">
-        <v>6709889</v>
+        <v>6710041</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 46085-2025 artfynd.xlsx
+++ b/artfynd/A 46085-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129039226</v>
+        <v>129039783</v>
       </c>
       <c r="B2" t="n">
-        <v>92831</v>
+        <v>91550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491060</v>
+        <v>491113</v>
       </c>
       <c r="R2" t="n">
-        <v>6710037</v>
+        <v>6710132</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129038956</v>
+        <v>129041992</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bocknäset, Bocknäset, Dlr</t>
+          <t>Sivikstad, Sivikstad, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490939</v>
+        <v>491353</v>
       </c>
       <c r="R3" t="n">
-        <v>6709966</v>
+        <v>6710077</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129042946</v>
+        <v>129038956</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bocknäset, Bocknäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491232</v>
+        <v>490939</v>
       </c>
       <c r="R4" t="n">
-        <v>6710086</v>
+        <v>6709966</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:23</t>
+   